--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="F14" t="n">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="G14" t="n">
-        <v>166.3</v>
+        <v>165.7</v>
       </c>
       <c r="H14" t="n">
-        <v>90.8</v>
+        <v>87.8</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-86.18000000000001</v>
+        <v>-107.65</v>
       </c>
       <c r="K14" t="n">
-        <v>17.14</v>
+        <v>3.81</v>
       </c>
       <c r="L14" t="n">
-        <v>87.87</v>
+        <v>107.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:33:25</t>
+          <t>04:34:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="F15" t="n">
-        <v>4.38</v>
+        <v>5.81</v>
       </c>
       <c r="G15" t="n">
-        <v>162</v>
+        <v>164.5</v>
       </c>
       <c r="H15" t="n">
-        <v>91.5</v>
+        <v>79.8</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>41.82</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-30.19</v>
+        <v>-26.7</v>
       </c>
       <c r="L15" t="n">
-        <v>51.58</v>
+        <v>84.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:16</t>
+          <t>04:36:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.19</v>
+        <v>0.91</v>
       </c>
       <c r="F16" t="n">
-        <v>6.41</v>
+        <v>6.01</v>
       </c>
       <c r="G16" t="n">
-        <v>165.5</v>
+        <v>176.3</v>
       </c>
       <c r="H16" t="n">
-        <v>83.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>56.15</v>
+        <v>25.19</v>
       </c>
       <c r="K16" t="n">
-        <v>-32.99</v>
+        <v>32.68</v>
       </c>
       <c r="L16" t="n">
-        <v>65.13</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:39:56</t>
+          <t>04:41:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="F17" t="n">
-        <v>5.3</v>
+        <v>5.88</v>
       </c>
       <c r="G17" t="n">
-        <v>168.7</v>
+        <v>161.1</v>
       </c>
       <c r="H17" t="n">
-        <v>90.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>128.69</v>
+        <v>23.94</v>
       </c>
       <c r="K17" t="n">
-        <v>-93.56</v>
+        <v>-18.75</v>
       </c>
       <c r="L17" t="n">
-        <v>159.1</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:40:48</t>
+          <t>04:43:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="F18" t="n">
-        <v>5.98</v>
+        <v>5.92</v>
       </c>
       <c r="G18" t="n">
-        <v>158.7</v>
+        <v>160.7</v>
       </c>
       <c r="H18" t="n">
-        <v>95.5</v>
+        <v>95.2</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-75.77</v>
+        <v>14.64</v>
       </c>
       <c r="K18" t="n">
-        <v>-72.28</v>
+        <v>79.45</v>
       </c>
       <c r="L18" t="n">
-        <v>104.72</v>
+        <v>80.79000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:42:22</t>
+          <t>04:45:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.23</v>
+        <v>0.87</v>
       </c>
       <c r="F19" t="n">
-        <v>6.28</v>
+        <v>6.14</v>
       </c>
       <c r="G19" t="n">
-        <v>167</v>
+        <v>170.9</v>
       </c>
       <c r="H19" t="n">
-        <v>86.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-55.6</v>
+        <v>-56.13</v>
       </c>
       <c r="K19" t="n">
-        <v>106.48</v>
+        <v>-56.46</v>
       </c>
       <c r="L19" t="n">
-        <v>120.12</v>
+        <v>79.62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:47:36</t>
+          <t>04:49:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="F20" t="n">
-        <v>4.88</v>
+        <v>6.12</v>
       </c>
       <c r="G20" t="n">
-        <v>173.9</v>
+        <v>164.4</v>
       </c>
       <c r="H20" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>142.97</v>
+        <v>59.12</v>
       </c>
       <c r="K20" t="n">
-        <v>-255.23</v>
+        <v>-219.95</v>
       </c>
       <c r="L20" t="n">
-        <v>292.54</v>
+        <v>227.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:48:13</t>
+          <t>04:50:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="F21" t="n">
-        <v>5.5</v>
+        <v>5.37</v>
       </c>
       <c r="G21" t="n">
-        <v>159.6</v>
+        <v>155.2</v>
       </c>
       <c r="H21" t="n">
-        <v>79.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>17.71</v>
+        <v>-150.02</v>
       </c>
       <c r="K21" t="n">
-        <v>88.95</v>
+        <v>-123.59</v>
       </c>
       <c r="L21" t="n">
-        <v>90.7</v>
+        <v>194.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:50:28</t>
+          <t>04:52:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="F22" t="n">
-        <v>6.02</v>
+        <v>5.05</v>
       </c>
       <c r="G22" t="n">
-        <v>160.1</v>
+        <v>153.7</v>
       </c>
       <c r="H22" t="n">
-        <v>86.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>92.01000000000001</v>
+        <v>-115.49</v>
       </c>
       <c r="K22" t="n">
-        <v>80.91</v>
+        <v>150.57</v>
       </c>
       <c r="L22" t="n">
-        <v>122.53</v>
+        <v>189.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:56:01</t>
+          <t>04:56:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="F23" t="n">
-        <v>4.64</v>
+        <v>6.43</v>
       </c>
       <c r="G23" t="n">
-        <v>160.9</v>
+        <v>159</v>
       </c>
       <c r="H23" t="n">
-        <v>82.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-32.51</v>
+        <v>144.99</v>
       </c>
       <c r="K23" t="n">
-        <v>117.45</v>
+        <v>-62.2</v>
       </c>
       <c r="L23" t="n">
-        <v>121.87</v>
+        <v>157.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:56:42</t>
+          <t>04:58:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="F24" t="n">
-        <v>5.51</v>
+        <v>5.04</v>
       </c>
       <c r="G24" t="n">
-        <v>162.7</v>
+        <v>157.4</v>
       </c>
       <c r="H24" t="n">
-        <v>83.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-52.43</v>
+        <v>18.01</v>
       </c>
       <c r="K24" t="n">
-        <v>120.11</v>
+        <v>-210.38</v>
       </c>
       <c r="L24" t="n">
-        <v>131.06</v>
+        <v>211.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:58:02</t>
+          <t>05:00:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="F25" t="n">
-        <v>6.12</v>
+        <v>5.96</v>
       </c>
       <c r="G25" t="n">
-        <v>149.5</v>
+        <v>169.8</v>
       </c>
       <c r="H25" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-161.89</v>
+        <v>119.1</v>
       </c>
       <c r="K25" t="n">
-        <v>93.02</v>
+        <v>32.77</v>
       </c>
       <c r="L25" t="n">
-        <v>186.71</v>
+        <v>123.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:03:36</t>
+          <t>05:05:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3</v>
+        <v>2.76</v>
       </c>
       <c r="F26" t="n">
-        <v>5.94</v>
+        <v>6.25</v>
       </c>
       <c r="G26" t="n">
-        <v>159.7</v>
+        <v>141.3</v>
       </c>
       <c r="H26" t="n">
-        <v>90.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-269.59</v>
+        <v>183.45</v>
       </c>
       <c r="K26" t="n">
-        <v>386.17</v>
+        <v>488.69</v>
       </c>
       <c r="L26" t="n">
-        <v>470.96</v>
+        <v>521.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:05:22</t>
+          <t>05:07:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="F27" t="n">
-        <v>5.68</v>
+        <v>5.78</v>
       </c>
       <c r="G27" t="n">
-        <v>149.9</v>
+        <v>178.5</v>
       </c>
       <c r="H27" t="n">
-        <v>88.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>344.64</v>
+        <v>-103.29</v>
       </c>
       <c r="K27" t="n">
-        <v>309.74</v>
+        <v>-6.88</v>
       </c>
       <c r="L27" t="n">
-        <v>463.37</v>
+        <v>103.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:06:47</t>
+          <t>05:08:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="F28" t="n">
-        <v>5.95</v>
+        <v>5.71</v>
       </c>
       <c r="G28" t="n">
-        <v>177</v>
+        <v>168.2</v>
       </c>
       <c r="H28" t="n">
-        <v>93.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>5.56</v>
+        <v>227.32</v>
       </c>
       <c r="K28" t="n">
-        <v>51.65</v>
+        <v>268.81</v>
       </c>
       <c r="L28" t="n">
-        <v>51.95</v>
+        <v>352.04</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:17:05</t>
+          <t>05:18:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.95</v>
+        <v>1.49</v>
       </c>
       <c r="F29" t="n">
-        <v>5.76</v>
+        <v>5.32</v>
       </c>
       <c r="G29" t="n">
-        <v>157.6</v>
+        <v>166.6</v>
       </c>
       <c r="H29" t="n">
-        <v>89.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>43.83</v>
+        <v>91.91</v>
       </c>
       <c r="K29" t="n">
-        <v>-52.85</v>
+        <v>-35.72</v>
       </c>
       <c r="L29" t="n">
-        <v>68.66</v>
+        <v>98.61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:18:36</t>
+          <t>05:20:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="F30" t="n">
-        <v>6.12</v>
+        <v>5.72</v>
       </c>
       <c r="G30" t="n">
-        <v>154.2</v>
+        <v>157</v>
       </c>
       <c r="H30" t="n">
-        <v>84.8</v>
+        <v>89.8</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>27.04</v>
+        <v>-26.39</v>
       </c>
       <c r="K30" t="n">
-        <v>38.09</v>
+        <v>71.83</v>
       </c>
       <c r="L30" t="n">
-        <v>46.71</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:20:44</t>
+          <t>05:22:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="F31" t="n">
-        <v>5.42</v>
+        <v>6.96</v>
       </c>
       <c r="G31" t="n">
-        <v>159.5</v>
+        <v>173.3</v>
       </c>
       <c r="H31" t="n">
-        <v>84.3</v>
+        <v>82</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-141.64</v>
+        <v>64.61</v>
       </c>
       <c r="K31" t="n">
-        <v>-23.39</v>
+        <v>-87.05</v>
       </c>
       <c r="L31" t="n">
-        <v>143.56</v>
+        <v>108.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:25:09</t>
+          <t>05:26:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.26</v>
+        <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>6.59</v>
+        <v>5.73</v>
       </c>
       <c r="G32" t="n">
-        <v>158.8</v>
+        <v>160.9</v>
       </c>
       <c r="H32" t="n">
-        <v>93.7</v>
+        <v>89.8</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>39.93</v>
+        <v>-9.49</v>
       </c>
       <c r="K32" t="n">
-        <v>68.28</v>
+        <v>-50.15</v>
       </c>
       <c r="L32" t="n">
-        <v>79.09999999999999</v>
+        <v>51.04</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:27:21</t>
+          <t>05:28:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="F33" t="n">
-        <v>5.58</v>
+        <v>5.09</v>
       </c>
       <c r="G33" t="n">
-        <v>171.7</v>
+        <v>160.8</v>
       </c>
       <c r="H33" t="n">
-        <v>85.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>235.77</v>
+        <v>25.81</v>
       </c>
       <c r="K33" t="n">
-        <v>-146.36</v>
+        <v>-25.66</v>
       </c>
       <c r="L33" t="n">
-        <v>277.5</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:28:45</t>
+          <t>05:30:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0.97</v>
+        <v>1.25</v>
       </c>
       <c r="F34" t="n">
-        <v>6.42</v>
+        <v>5.28</v>
       </c>
       <c r="G34" t="n">
-        <v>166.8</v>
+        <v>161.4</v>
       </c>
       <c r="H34" t="n">
-        <v>94.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-14.56</v>
+        <v>-30.6</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.96</v>
+        <v>-4.76</v>
       </c>
       <c r="L34" t="n">
-        <v>14.59</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:34:33</t>
+          <t>05:34:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="F35" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>151.3</v>
+        <v>166.5</v>
       </c>
       <c r="H35" t="n">
-        <v>82.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-161.78</v>
+        <v>24.3</v>
       </c>
       <c r="K35" t="n">
-        <v>13.96</v>
+        <v>-32.08</v>
       </c>
       <c r="L35" t="n">
-        <v>162.38</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:36:06</t>
+          <t>05:36:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="F36" t="n">
-        <v>5.55</v>
+        <v>6.18</v>
       </c>
       <c r="G36" t="n">
-        <v>173.4</v>
+        <v>157.7</v>
       </c>
       <c r="H36" t="n">
-        <v>84.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-36.55</v>
+        <v>37.69</v>
       </c>
       <c r="K36" t="n">
-        <v>20.39</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>41.86</v>
+        <v>80.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:38:22</t>
+          <t>05:37:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8</v>
+        <v>1.47</v>
       </c>
       <c r="F37" t="n">
-        <v>5.68</v>
+        <v>6.48</v>
       </c>
       <c r="G37" t="n">
-        <v>146</v>
+        <v>157.5</v>
       </c>
       <c r="H37" t="n">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-60.68</v>
+        <v>117.75</v>
       </c>
       <c r="K37" t="n">
-        <v>-53.28</v>
+        <v>-55.69</v>
       </c>
       <c r="L37" t="n">
-        <v>80.75</v>
+        <v>130.26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:42:28</t>
+          <t>05:42:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,28 +1633,28 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="F38" t="n">
-        <v>6.18</v>
+        <v>5.54</v>
       </c>
       <c r="G38" t="n">
-        <v>162.9</v>
+        <v>162.6</v>
       </c>
       <c r="H38" t="n">
-        <v>86.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>36.34</v>
+        <v>-183.35</v>
       </c>
       <c r="K38" t="n">
-        <v>16.53</v>
+        <v>-63.76</v>
       </c>
       <c r="L38" t="n">
-        <v>39.92</v>
+        <v>194.12</v>
       </c>
     </row>
     <row r="39">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="F39" t="n">
-        <v>6.38</v>
+        <v>5.73</v>
       </c>
       <c r="G39" t="n">
-        <v>165.2</v>
+        <v>159.9</v>
       </c>
       <c r="H39" t="n">
-        <v>87.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>46.8</v>
+        <v>7.96</v>
       </c>
       <c r="K39" t="n">
-        <v>-233.21</v>
+        <v>-144.83</v>
       </c>
       <c r="L39" t="n">
-        <v>237.86</v>
+        <v>145.04</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:45:31</t>
+          <t>05:44:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.23</v>
+        <v>0.95</v>
       </c>
       <c r="F40" t="n">
-        <v>5.18</v>
+        <v>5.43</v>
       </c>
       <c r="G40" t="n">
-        <v>172.5</v>
+        <v>164.1</v>
       </c>
       <c r="H40" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>72.98</v>
+        <v>-25.12</v>
       </c>
       <c r="K40" t="n">
-        <v>142.13</v>
+        <v>-10.52</v>
       </c>
       <c r="L40" t="n">
-        <v>159.77</v>
+        <v>27.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:48:56</t>
+          <t>05:49:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="F41" t="n">
-        <v>5.28</v>
+        <v>5.54</v>
       </c>
       <c r="G41" t="n">
-        <v>171.9</v>
+        <v>148.6</v>
       </c>
       <c r="H41" t="n">
-        <v>90.3</v>
+        <v>91.2</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-203.3</v>
+        <v>183.62</v>
       </c>
       <c r="K41" t="n">
-        <v>198.6</v>
+        <v>279.34</v>
       </c>
       <c r="L41" t="n">
-        <v>284.21</v>
+        <v>334.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:49:36</t>
+          <t>05:51:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="G42" t="n">
-        <v>155.5</v>
+        <v>158.5</v>
       </c>
       <c r="H42" t="n">
-        <v>87.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-52.68</v>
+        <v>-78.41</v>
       </c>
       <c r="K42" t="n">
-        <v>117.87</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>129.1</v>
+        <v>116.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:52:23</t>
+          <t>05:53:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.41</v>
+        <v>2.63</v>
       </c>
       <c r="F43" t="n">
-        <v>5.34</v>
+        <v>5.64</v>
       </c>
       <c r="G43" t="n">
-        <v>150.9</v>
+        <v>152.4</v>
       </c>
       <c r="H43" t="n">
-        <v>82</v>
+        <v>90.7</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>60.99</v>
+        <v>-324.4</v>
       </c>
       <c r="K43" t="n">
-        <v>2.41</v>
+        <v>75.38</v>
       </c>
       <c r="L43" t="n">
-        <v>61.04</v>
+        <v>333.04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:03:32</t>
+          <t>06:03:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="F44" t="n">
-        <v>5.82</v>
+        <v>6.01</v>
       </c>
       <c r="G44" t="n">
-        <v>168.6</v>
+        <v>158.2</v>
       </c>
       <c r="H44" t="n">
-        <v>90.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.71</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-32.98</v>
+        <v>104.77</v>
       </c>
       <c r="L44" t="n">
-        <v>33.66</v>
+        <v>134.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:05:34</t>
+          <t>06:05:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.23</v>
+        <v>0.98</v>
       </c>
       <c r="F45" t="n">
-        <v>5.57</v>
+        <v>5.13</v>
       </c>
       <c r="G45" t="n">
-        <v>151.4</v>
+        <v>164.2</v>
       </c>
       <c r="H45" t="n">
-        <v>85.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.7</v>
+        <v>16.46</v>
       </c>
       <c r="K45" t="n">
-        <v>67.54000000000001</v>
+        <v>-31.98</v>
       </c>
       <c r="L45" t="n">
-        <v>67.97</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:06:34</t>
+          <t>06:07:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="F46" t="n">
-        <v>6.04</v>
+        <v>6.42</v>
       </c>
       <c r="G46" t="n">
-        <v>169.1</v>
+        <v>150.2</v>
       </c>
       <c r="H46" t="n">
-        <v>80.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-38.4</v>
+        <v>43.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-110.48</v>
+        <v>37.84</v>
       </c>
       <c r="L46" t="n">
-        <v>116.97</v>
+        <v>57.93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:11:40</t>
+          <t>06:13:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="F47" t="n">
-        <v>6.16</v>
+        <v>6.01</v>
       </c>
       <c r="G47" t="n">
-        <v>160.2</v>
+        <v>150.5</v>
       </c>
       <c r="H47" t="n">
-        <v>82.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-166.67</v>
+        <v>-7.86</v>
       </c>
       <c r="K47" t="n">
-        <v>109.12</v>
+        <v>72.66</v>
       </c>
       <c r="L47" t="n">
-        <v>199.21</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:13:41</t>
+          <t>06:14:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="F48" t="n">
-        <v>5.8</v>
+        <v>5.52</v>
       </c>
       <c r="G48" t="n">
-        <v>155.6</v>
+        <v>166.2</v>
       </c>
       <c r="H48" t="n">
-        <v>90.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>26.37</v>
+        <v>77.63</v>
       </c>
       <c r="K48" t="n">
-        <v>74.88</v>
+        <v>58.91</v>
       </c>
       <c r="L48" t="n">
-        <v>79.39</v>
+        <v>97.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:15:37</t>
+          <t>06:16:28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.56</v>
+        <v>0.99</v>
       </c>
       <c r="F49" t="n">
-        <v>5.74</v>
+        <v>6.57</v>
       </c>
       <c r="G49" t="n">
-        <v>150.4</v>
+        <v>167.3</v>
       </c>
       <c r="H49" t="n">
-        <v>87.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-90.53</v>
+        <v>-74.20999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-48.49</v>
+        <v>13.27</v>
       </c>
       <c r="L49" t="n">
-        <v>102.7</v>
+        <v>75.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:20:46</t>
+          <t>06:21:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="F50" t="n">
-        <v>6.01</v>
+        <v>5.51</v>
       </c>
       <c r="G50" t="n">
-        <v>161.8</v>
+        <v>154.5</v>
       </c>
       <c r="H50" t="n">
-        <v>76.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.25</v>
+        <v>-75.54000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>89.19</v>
+        <v>-284.03</v>
       </c>
       <c r="L50" t="n">
-        <v>90.03</v>
+        <v>293.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:22:44</t>
+          <t>06:23:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.74</v>
+        <v>1.22</v>
       </c>
       <c r="F51" t="n">
-        <v>5.89</v>
+        <v>6.06</v>
       </c>
       <c r="G51" t="n">
-        <v>156.7</v>
+        <v>161.6</v>
       </c>
       <c r="H51" t="n">
-        <v>83.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>116.52</v>
+        <v>50.78</v>
       </c>
       <c r="K51" t="n">
-        <v>243.41</v>
+        <v>-30.08</v>
       </c>
       <c r="L51" t="n">
-        <v>269.87</v>
+        <v>59.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:24:39</t>
+          <t>06:24:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="F52" t="n">
-        <v>6.15</v>
+        <v>6.03</v>
       </c>
       <c r="G52" t="n">
-        <v>164.7</v>
+        <v>141.8</v>
       </c>
       <c r="H52" t="n">
-        <v>88.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>50.94</v>
+        <v>43.71</v>
       </c>
       <c r="K52" t="n">
-        <v>-154.42</v>
+        <v>-134.87</v>
       </c>
       <c r="L52" t="n">
-        <v>162.6</v>
+        <v>141.78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:29:24</t>
+          <t>06:29:57</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.41</v>
+        <v>0.97</v>
       </c>
       <c r="F53" t="n">
-        <v>5.81</v>
+        <v>5.62</v>
       </c>
       <c r="G53" t="n">
-        <v>163</v>
+        <v>167.3</v>
       </c>
       <c r="H53" t="n">
-        <v>91.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-317.61</v>
+        <v>164.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-147.63</v>
+        <v>-46.46</v>
       </c>
       <c r="L53" t="n">
-        <v>350.25</v>
+        <v>170.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:31:24</t>
+          <t>06:31:09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="F54" t="n">
-        <v>5.5</v>
+        <v>6.56</v>
       </c>
       <c r="G54" t="n">
-        <v>154.5</v>
+        <v>165.3</v>
       </c>
       <c r="H54" t="n">
-        <v>81.8</v>
+        <v>84</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-204.2</v>
+        <v>-146.97</v>
       </c>
       <c r="K54" t="n">
-        <v>-113.14</v>
+        <v>263.21</v>
       </c>
       <c r="L54" t="n">
-        <v>233.45</v>
+        <v>301.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:32:23</t>
+          <t>06:33:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="F55" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="G55" t="n">
-        <v>159.2</v>
+        <v>156.4</v>
       </c>
       <c r="H55" t="n">
-        <v>86.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>10.19</v>
+        <v>4.04</v>
       </c>
       <c r="K55" t="n">
-        <v>189.78</v>
+        <v>165.58</v>
       </c>
       <c r="L55" t="n">
-        <v>190.06</v>
+        <v>165.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:36:32</t>
+          <t>06:37:21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="F56" t="n">
-        <v>6.04</v>
+        <v>6.81</v>
       </c>
       <c r="G56" t="n">
-        <v>153.5</v>
+        <v>158.6</v>
       </c>
       <c r="H56" t="n">
-        <v>89.2</v>
+        <v>79.2</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>134.57</v>
+        <v>258.52</v>
       </c>
       <c r="K56" t="n">
-        <v>-421.67</v>
+        <v>-262.88</v>
       </c>
       <c r="L56" t="n">
-        <v>442.62</v>
+        <v>368.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:38:13</t>
+          <t>06:38:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="F57" t="n">
-        <v>6.04</v>
+        <v>6.07</v>
       </c>
       <c r="G57" t="n">
-        <v>139.8</v>
+        <v>144.5</v>
       </c>
       <c r="H57" t="n">
-        <v>87.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>231.66</v>
+        <v>-148.61</v>
       </c>
       <c r="K57" t="n">
-        <v>-285.02</v>
+        <v>106.41</v>
       </c>
       <c r="L57" t="n">
-        <v>367.29</v>
+        <v>182.78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:46</t>
+          <t>06:39:29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="F58" t="n">
-        <v>6.1</v>
+        <v>6.34</v>
       </c>
       <c r="G58" t="n">
-        <v>167.1</v>
+        <v>163.7</v>
       </c>
       <c r="H58" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-342.51</v>
+        <v>372.15</v>
       </c>
       <c r="K58" t="n">
-        <v>-198.81</v>
+        <v>-162.89</v>
       </c>
       <c r="L58" t="n">
-        <v>396.02</v>
+        <v>406.24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:52:02</t>
+          <t>06:51:34</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="F59" t="n">
-        <v>5.31</v>
+        <v>5.76</v>
       </c>
       <c r="G59" t="n">
-        <v>169.9</v>
+        <v>162.8</v>
       </c>
       <c r="H59" t="n">
-        <v>79.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>51.92</v>
+        <v>73.73</v>
       </c>
       <c r="K59" t="n">
-        <v>31.69</v>
+        <v>105.29</v>
       </c>
       <c r="L59" t="n">
-        <v>60.82</v>
+        <v>128.54</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:53:43</t>
+          <t>06:53:23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="F60" t="n">
-        <v>5.82</v>
+        <v>6.07</v>
       </c>
       <c r="G60" t="n">
-        <v>160.8</v>
+        <v>165.9</v>
       </c>
       <c r="H60" t="n">
-        <v>87.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>60.47</v>
+        <v>-59.7</v>
       </c>
       <c r="K60" t="n">
-        <v>40.48</v>
+        <v>44.01</v>
       </c>
       <c r="L60" t="n">
-        <v>72.77</v>
+        <v>74.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:55:47</t>
+          <t>06:55:39</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="F61" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="G61" t="n">
-        <v>164.4</v>
+        <v>160.1</v>
       </c>
       <c r="H61" t="n">
-        <v>87.7</v>
+        <v>83.3</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-34.09</v>
+        <v>-24.75</v>
       </c>
       <c r="K61" t="n">
-        <v>37.56</v>
+        <v>29.29</v>
       </c>
       <c r="L61" t="n">
-        <v>50.72</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:01:02</t>
+          <t>06:59:17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="F62" t="n">
-        <v>5.53</v>
+        <v>5.36</v>
       </c>
       <c r="G62" t="n">
-        <v>150.4</v>
+        <v>163.8</v>
       </c>
       <c r="H62" t="n">
-        <v>80.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-26.84</v>
+        <v>3.83</v>
       </c>
       <c r="K62" t="n">
-        <v>66.47</v>
+        <v>-75.33</v>
       </c>
       <c r="L62" t="n">
-        <v>71.68000000000001</v>
+        <v>75.43000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:03:04</t>
+          <t>07:00:43</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="F63" t="n">
-        <v>5.75</v>
+        <v>6.14</v>
       </c>
       <c r="G63" t="n">
-        <v>155.6</v>
+        <v>157.5</v>
       </c>
       <c r="H63" t="n">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-68.61</v>
+        <v>102.11</v>
       </c>
       <c r="K63" t="n">
-        <v>-66.59</v>
+        <v>-15.02</v>
       </c>
       <c r="L63" t="n">
-        <v>95.61</v>
+        <v>103.21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:04:37</t>
+          <t>07:02:20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="F64" t="n">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="G64" t="n">
-        <v>153.1</v>
+        <v>166.4</v>
       </c>
       <c r="H64" t="n">
-        <v>78.7</v>
+        <v>80.2</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>73.89</v>
+        <v>-94.66</v>
       </c>
       <c r="K64" t="n">
-        <v>-18.56</v>
+        <v>-26.12</v>
       </c>
       <c r="L64" t="n">
-        <v>76.19</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:08:21</t>
+          <t>07:07:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="F65" t="n">
-        <v>5.41</v>
+        <v>4.94</v>
       </c>
       <c r="G65" t="n">
-        <v>176.7</v>
+        <v>163.5</v>
       </c>
       <c r="H65" t="n">
-        <v>88.5</v>
+        <v>99.7</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-92.51000000000001</v>
+        <v>46.74</v>
       </c>
       <c r="K65" t="n">
-        <v>-160.46</v>
+        <v>-2.74</v>
       </c>
       <c r="L65" t="n">
-        <v>185.21</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:10:29</t>
+          <t>07:08:48</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="F66" t="n">
-        <v>5.75</v>
+        <v>6.36</v>
       </c>
       <c r="G66" t="n">
-        <v>170.3</v>
+        <v>163.9</v>
       </c>
       <c r="H66" t="n">
-        <v>85.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>106.35</v>
+        <v>192.98</v>
       </c>
       <c r="K66" t="n">
-        <v>-155.56</v>
+        <v>-111.15</v>
       </c>
       <c r="L66" t="n">
-        <v>188.44</v>
+        <v>222.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:12:35</t>
+          <t>07:11:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="F67" t="n">
-        <v>5.42</v>
+        <v>6.38</v>
       </c>
       <c r="G67" t="n">
-        <v>154.4</v>
+        <v>159.1</v>
       </c>
       <c r="H67" t="n">
-        <v>89</v>
+        <v>86.2</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-40.87</v>
+        <v>20.56</v>
       </c>
       <c r="K67" t="n">
-        <v>-152.7</v>
+        <v>57.96</v>
       </c>
       <c r="L67" t="n">
-        <v>158.08</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:17:23</t>
+          <t>07:16:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="F68" t="n">
-        <v>5.75</v>
+        <v>5.93</v>
       </c>
       <c r="G68" t="n">
-        <v>154.8</v>
+        <v>150.6</v>
       </c>
       <c r="H68" t="n">
-        <v>87.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>412.62</v>
+        <v>-42.88</v>
       </c>
       <c r="K68" t="n">
-        <v>-27.18</v>
+        <v>111.06</v>
       </c>
       <c r="L68" t="n">
-        <v>413.52</v>
+        <v>119.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:19:18</t>
+          <t>07:19:20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="F69" t="n">
-        <v>5.98</v>
+        <v>5.44</v>
       </c>
       <c r="G69" t="n">
-        <v>142.4</v>
+        <v>165.6</v>
       </c>
       <c r="H69" t="n">
-        <v>81.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.09</v>
+        <v>13.04</v>
       </c>
       <c r="K69" t="n">
-        <v>-67.98999999999999</v>
+        <v>-79.67</v>
       </c>
       <c r="L69" t="n">
-        <v>68.47</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:20:36</t>
+          <t>07:20:04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.53</v>
+        <v>0.8</v>
       </c>
       <c r="F70" t="n">
-        <v>6.04</v>
+        <v>5.7</v>
       </c>
       <c r="G70" t="n">
-        <v>152.1</v>
+        <v>159.6</v>
       </c>
       <c r="H70" t="n">
-        <v>86.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-302.69</v>
+        <v>-225.69</v>
       </c>
       <c r="K70" t="n">
-        <v>-46.48</v>
+        <v>-244.77</v>
       </c>
       <c r="L70" t="n">
-        <v>306.24</v>
+        <v>332.94</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:25:59</t>
+          <t>07:25:12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="F71" t="n">
-        <v>5.95</v>
+        <v>6.09</v>
       </c>
       <c r="G71" t="n">
-        <v>167.5</v>
+        <v>167.2</v>
       </c>
       <c r="H71" t="n">
-        <v>82.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-154.45</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>563.34</v>
+        <v>-112.92</v>
       </c>
       <c r="L71" t="n">
-        <v>584.13</v>
+        <v>134.63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:28:10</t>
+          <t>07:26:13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="F72" t="n">
-        <v>5.71</v>
+        <v>5.7</v>
       </c>
       <c r="G72" t="n">
-        <v>165.4</v>
+        <v>142.1</v>
       </c>
       <c r="H72" t="n">
-        <v>94.7</v>
+        <v>92.8</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-92.16</v>
+        <v>244.3</v>
       </c>
       <c r="K72" t="n">
-        <v>-176.69</v>
+        <v>-305.35</v>
       </c>
       <c r="L72" t="n">
-        <v>199.28</v>
+        <v>391.05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:30:26</t>
+          <t>07:27:55</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.19</v>
+        <v>0.78</v>
       </c>
       <c r="F73" t="n">
-        <v>5.58</v>
+        <v>6.41</v>
       </c>
       <c r="G73" t="n">
-        <v>156.5</v>
+        <v>159.9</v>
       </c>
       <c r="H73" t="n">
-        <v>87.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>278.23</v>
+        <v>27.87</v>
       </c>
       <c r="K73" t="n">
-        <v>70.37</v>
+        <v>115.12</v>
       </c>
       <c r="L73" t="n">
-        <v>286.99</v>
+        <v>118.45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:40:03</t>
+          <t>07:36:51</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="F74" t="n">
-        <v>5.5</v>
+        <v>5.48</v>
       </c>
       <c r="G74" t="n">
-        <v>170.5</v>
+        <v>159.6</v>
       </c>
       <c r="H74" t="n">
-        <v>82.2</v>
+        <v>79.7</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-12.67</v>
+        <v>36.83</v>
       </c>
       <c r="K74" t="n">
-        <v>-190.04</v>
+        <v>79.77</v>
       </c>
       <c r="L74" t="n">
-        <v>190.47</v>
+        <v>87.86</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:42:27</t>
+          <t>07:38:59</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.77</v>
+        <v>1.78</v>
       </c>
       <c r="F75" t="n">
-        <v>5.51</v>
+        <v>5.98</v>
       </c>
       <c r="G75" t="n">
-        <v>169.6</v>
+        <v>153.2</v>
       </c>
       <c r="H75" t="n">
-        <v>86.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-37.36</v>
+        <v>33.98</v>
       </c>
       <c r="K75" t="n">
-        <v>72.01000000000001</v>
+        <v>-61.26</v>
       </c>
       <c r="L75" t="n">
-        <v>81.13</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:44:37</t>
+          <t>07:40:38</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="F76" t="n">
-        <v>6.6</v>
+        <v>5.79</v>
       </c>
       <c r="G76" t="n">
-        <v>161.1</v>
+        <v>145.5</v>
       </c>
       <c r="H76" t="n">
-        <v>83.8</v>
+        <v>86</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>64.47</v>
+        <v>67.66</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.21</v>
+        <v>54.93</v>
       </c>
       <c r="L76" t="n">
-        <v>70.37</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:49:41</t>
+          <t>07:46:28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.46</v>
+        <v>0.93</v>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>5.29</v>
       </c>
       <c r="G77" t="n">
-        <v>168.4</v>
+        <v>167.9</v>
       </c>
       <c r="H77" t="n">
-        <v>83.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>36.64</v>
+        <v>-47.34</v>
       </c>
       <c r="K77" t="n">
-        <v>68.61</v>
+        <v>-112.44</v>
       </c>
       <c r="L77" t="n">
-        <v>77.78</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:50:52</t>
+          <t>07:48:47</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="F78" t="n">
-        <v>6.28</v>
+        <v>5.62</v>
       </c>
       <c r="G78" t="n">
-        <v>157.2</v>
+        <v>156</v>
       </c>
       <c r="H78" t="n">
-        <v>88.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>-75.59</v>
+        <v>5.64</v>
       </c>
       <c r="K78" t="n">
-        <v>64.61</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>99.43000000000001</v>
+        <v>83.43000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:53:14</t>
+          <t>07:49:56</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="F79" t="n">
-        <v>5.73</v>
+        <v>6.63</v>
       </c>
       <c r="G79" t="n">
-        <v>165.8</v>
+        <v>155.9</v>
       </c>
       <c r="H79" t="n">
-        <v>89</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>9.16</v>
+        <v>73.92</v>
       </c>
       <c r="K79" t="n">
-        <v>-3.56</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>9.82</v>
+        <v>105.18</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:56:43</t>
+          <t>07:54:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F80" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="G80" t="n">
-        <v>157.8</v>
+        <v>156.4</v>
       </c>
       <c r="H80" t="n">
-        <v>82</v>
+        <v>87.8</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-88.31999999999999</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-19.02</v>
+        <v>-1.59</v>
       </c>
       <c r="L80" t="n">
-        <v>90.34999999999999</v>
+        <v>74.03</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:58:32</t>
+          <t>07:56:09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="F81" t="n">
-        <v>5.44</v>
+        <v>5.61</v>
       </c>
       <c r="G81" t="n">
-        <v>149.4</v>
+        <v>163.1</v>
       </c>
       <c r="H81" t="n">
-        <v>82.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>225.43</v>
+        <v>-21.76</v>
       </c>
       <c r="K81" t="n">
-        <v>108.6</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>250.22</v>
+        <v>73.77</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:01:15</t>
+          <t>07:58:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="F82" t="n">
-        <v>6.6</v>
+        <v>6.05</v>
       </c>
       <c r="G82" t="n">
-        <v>171.5</v>
+        <v>147.4</v>
       </c>
       <c r="H82" t="n">
-        <v>84.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-22.22</v>
+        <v>85.55</v>
       </c>
       <c r="K82" t="n">
-        <v>29.25</v>
+        <v>-60.37</v>
       </c>
       <c r="L82" t="n">
-        <v>36.73</v>
+        <v>104.71</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:05:55</t>
+          <t>08:04:09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="G83" t="n">
-        <v>169</v>
+        <v>161.6</v>
       </c>
       <c r="H83" t="n">
-        <v>89.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>370.57</v>
+        <v>40.63</v>
       </c>
       <c r="K83" t="n">
-        <v>-232.54</v>
+        <v>-116.96</v>
       </c>
       <c r="L83" t="n">
-        <v>437.49</v>
+        <v>123.82</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:07:13</t>
+          <t>08:06:04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="F84" t="n">
-        <v>5.99</v>
+        <v>5.46</v>
       </c>
       <c r="G84" t="n">
-        <v>155.1</v>
+        <v>149</v>
       </c>
       <c r="H84" t="n">
-        <v>84.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-73.56</v>
+        <v>68.2</v>
       </c>
       <c r="K84" t="n">
-        <v>-74.98</v>
+        <v>-71.62</v>
       </c>
       <c r="L84" t="n">
-        <v>105.04</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:08:43</t>
+          <t>08:08:10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="F85" t="n">
-        <v>5.6</v>
+        <v>5.81</v>
       </c>
       <c r="G85" t="n">
-        <v>160.8</v>
+        <v>162.6</v>
       </c>
       <c r="H85" t="n">
-        <v>90.2</v>
+        <v>88.8</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>53.3</v>
+        <v>-121.06</v>
       </c>
       <c r="K85" t="n">
-        <v>-206.87</v>
+        <v>-152.74</v>
       </c>
       <c r="L85" t="n">
-        <v>213.62</v>
+        <v>194.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:13:33</t>
+          <t>08:12:53</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="F86" t="n">
-        <v>6.08</v>
+        <v>5.62</v>
       </c>
       <c r="G86" t="n">
-        <v>156.1</v>
+        <v>173.3</v>
       </c>
       <c r="H86" t="n">
-        <v>82.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>190.43</v>
+        <v>-99.55</v>
       </c>
       <c r="K86" t="n">
-        <v>-135.7</v>
+        <v>-10.53</v>
       </c>
       <c r="L86" t="n">
-        <v>233.83</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:15:08</t>
+          <t>08:14:53</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="F87" t="n">
-        <v>4.96</v>
+        <v>5.79</v>
       </c>
       <c r="G87" t="n">
-        <v>165.3</v>
+        <v>167.1</v>
       </c>
       <c r="H87" t="n">
-        <v>81</v>
+        <v>88.2</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>70.17</v>
+        <v>-48.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-501.4</v>
+        <v>-185.31</v>
       </c>
       <c r="L87" t="n">
-        <v>506.28</v>
+        <v>191.65</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:16:53</t>
+          <t>08:17:21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.19</v>
+        <v>1.55</v>
       </c>
       <c r="F88" t="n">
-        <v>5.28</v>
+        <v>5.86</v>
       </c>
       <c r="G88" t="n">
-        <v>162.8</v>
+        <v>168.8</v>
       </c>
       <c r="H88" t="n">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>163.5</v>
+        <v>-134.47</v>
       </c>
       <c r="K88" t="n">
-        <v>461.6</v>
+        <v>254.91</v>
       </c>
       <c r="L88" t="n">
-        <v>489.7</v>
+        <v>288.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-107.65</v>
+        <v>-86.84</v>
       </c>
       <c r="K14" t="n">
-        <v>3.81</v>
+        <v>3.08</v>
       </c>
       <c r="L14" t="n">
-        <v>107.72</v>
+        <v>86.89</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-80.59999999999999</v>
+        <v>-73.34999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-26.7</v>
+        <v>-24.3</v>
       </c>
       <c r="L15" t="n">
-        <v>84.91</v>
+        <v>77.27</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>25.19</v>
+        <v>27.62</v>
       </c>
       <c r="K16" t="n">
-        <v>32.68</v>
+        <v>35.83</v>
       </c>
       <c r="L16" t="n">
-        <v>41.26</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>23.94</v>
+        <v>32.91</v>
       </c>
       <c r="K17" t="n">
-        <v>-18.75</v>
+        <v>-25.77</v>
       </c>
       <c r="L17" t="n">
-        <v>30.41</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>14.64</v>
+        <v>12.27</v>
       </c>
       <c r="K18" t="n">
-        <v>79.45</v>
+        <v>66.59</v>
       </c>
       <c r="L18" t="n">
-        <v>80.79000000000001</v>
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-56.13</v>
+        <v>-51.33</v>
       </c>
       <c r="K19" t="n">
-        <v>-56.46</v>
+        <v>-51.64</v>
       </c>
       <c r="L19" t="n">
-        <v>79.62</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>59.12</v>
+        <v>49.98</v>
       </c>
       <c r="K20" t="n">
-        <v>-219.95</v>
+        <v>-185.97</v>
       </c>
       <c r="L20" t="n">
-        <v>227.76</v>
+        <v>192.57</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-150.02</v>
+        <v>-131.72</v>
       </c>
       <c r="K21" t="n">
-        <v>-123.59</v>
+        <v>-108.52</v>
       </c>
       <c r="L21" t="n">
-        <v>194.37</v>
+        <v>170.67</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-115.49</v>
+        <v>-102.79</v>
       </c>
       <c r="K22" t="n">
-        <v>150.57</v>
+        <v>134.01</v>
       </c>
       <c r="L22" t="n">
-        <v>189.76</v>
+        <v>168.89</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>144.99</v>
+        <v>163.57</v>
       </c>
       <c r="K23" t="n">
-        <v>-62.2</v>
+        <v>-70.17</v>
       </c>
       <c r="L23" t="n">
-        <v>157.77</v>
+        <v>177.99</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>18.01</v>
+        <v>19.13</v>
       </c>
       <c r="K24" t="n">
-        <v>-210.38</v>
+        <v>-223.48</v>
       </c>
       <c r="L24" t="n">
-        <v>211.15</v>
+        <v>224.3</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>119.1</v>
+        <v>148.63</v>
       </c>
       <c r="K25" t="n">
-        <v>32.77</v>
+        <v>40.9</v>
       </c>
       <c r="L25" t="n">
-        <v>123.53</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>183.45</v>
+        <v>210.2</v>
       </c>
       <c r="K26" t="n">
-        <v>488.69</v>
+        <v>559.9299999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>521.99</v>
+        <v>598.09</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-103.29</v>
+        <v>-210.84</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.88</v>
+        <v>-14.04</v>
       </c>
       <c r="L27" t="n">
-        <v>103.52</v>
+        <v>211.31</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>227.32</v>
+        <v>224.08</v>
       </c>
       <c r="K28" t="n">
-        <v>268.81</v>
+        <v>264.97</v>
       </c>
       <c r="L28" t="n">
-        <v>352.04</v>
+        <v>347.02</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>91.91</v>
+        <v>68</v>
       </c>
       <c r="K29" t="n">
-        <v>-35.72</v>
+        <v>-26.43</v>
       </c>
       <c r="L29" t="n">
-        <v>98.61</v>
+        <v>72.95999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-26.39</v>
+        <v>-25.28</v>
       </c>
       <c r="K30" t="n">
-        <v>71.83</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>76.53</v>
+        <v>73.31999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>64.61</v>
+        <v>51.03</v>
       </c>
       <c r="K31" t="n">
-        <v>-87.05</v>
+        <v>-68.76000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>108.41</v>
+        <v>85.63</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.49</v>
+        <v>-9.43</v>
       </c>
       <c r="K32" t="n">
-        <v>-50.15</v>
+        <v>-49.83</v>
       </c>
       <c r="L32" t="n">
-        <v>51.04</v>
+        <v>50.72</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>25.81</v>
+        <v>38.54</v>
       </c>
       <c r="K33" t="n">
-        <v>-25.66</v>
+        <v>-38.3</v>
       </c>
       <c r="L33" t="n">
-        <v>36.39</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-30.6</v>
+        <v>-52.44</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.76</v>
+        <v>-8.15</v>
       </c>
       <c r="L34" t="n">
-        <v>30.96</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>24.3</v>
+        <v>51.02</v>
       </c>
       <c r="K35" t="n">
-        <v>-32.08</v>
+        <v>-67.36</v>
       </c>
       <c r="L35" t="n">
-        <v>40.24</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>37.69</v>
+        <v>41.78</v>
       </c>
       <c r="K36" t="n">
-        <v>71.51000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="L36" t="n">
-        <v>80.83</v>
+        <v>89.61</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>117.75</v>
+        <v>125.34</v>
       </c>
       <c r="K37" t="n">
-        <v>-55.69</v>
+        <v>-59.28</v>
       </c>
       <c r="L37" t="n">
-        <v>130.26</v>
+        <v>138.65</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-183.35</v>
+        <v>-222.83</v>
       </c>
       <c r="K38" t="n">
-        <v>-63.76</v>
+        <v>-77.48999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>194.12</v>
+        <v>235.92</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>7.96</v>
+        <v>11.19</v>
       </c>
       <c r="K39" t="n">
-        <v>-144.83</v>
+        <v>-203.43</v>
       </c>
       <c r="L39" t="n">
-        <v>145.04</v>
+        <v>203.74</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-25.12</v>
+        <v>-82.73999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-10.52</v>
+        <v>-34.64</v>
       </c>
       <c r="L40" t="n">
-        <v>27.23</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>183.62</v>
+        <v>197.67</v>
       </c>
       <c r="K41" t="n">
-        <v>279.34</v>
+        <v>300.7</v>
       </c>
       <c r="L41" t="n">
-        <v>334.28</v>
+        <v>359.85</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-78.41</v>
+        <v>-121.74</v>
       </c>
       <c r="K42" t="n">
-        <v>86.29000000000001</v>
+        <v>133.97</v>
       </c>
       <c r="L42" t="n">
-        <v>116.59</v>
+        <v>181.02</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-324.4</v>
+        <v>-380.78</v>
       </c>
       <c r="K43" t="n">
-        <v>75.38</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>333.04</v>
+        <v>390.93</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>84.04000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="K44" t="n">
-        <v>104.77</v>
+        <v>86.37</v>
       </c>
       <c r="L44" t="n">
-        <v>134.31</v>
+        <v>110.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>16.46</v>
+        <v>16.96</v>
       </c>
       <c r="K45" t="n">
-        <v>-31.98</v>
+        <v>-32.95</v>
       </c>
       <c r="L45" t="n">
-        <v>35.97</v>
+        <v>37.06</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>43.86</v>
+        <v>42.38</v>
       </c>
       <c r="K46" t="n">
-        <v>37.84</v>
+        <v>36.56</v>
       </c>
       <c r="L46" t="n">
-        <v>57.93</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-7.86</v>
+        <v>-7.12</v>
       </c>
       <c r="K47" t="n">
-        <v>72.66</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>73.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>77.63</v>
+        <v>70.84</v>
       </c>
       <c r="K48" t="n">
-        <v>58.91</v>
+        <v>53.76</v>
       </c>
       <c r="L48" t="n">
-        <v>97.45</v>
+        <v>88.93000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-74.20999999999999</v>
+        <v>-75.38</v>
       </c>
       <c r="K49" t="n">
-        <v>13.27</v>
+        <v>13.48</v>
       </c>
       <c r="L49" t="n">
-        <v>75.39</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-75.54000000000001</v>
+        <v>-65.36</v>
       </c>
       <c r="K50" t="n">
-        <v>-284.03</v>
+        <v>-245.75</v>
       </c>
       <c r="L50" t="n">
-        <v>293.91</v>
+        <v>254.29</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>50.78</v>
+        <v>78.34</v>
       </c>
       <c r="K51" t="n">
-        <v>-30.08</v>
+        <v>-46.41</v>
       </c>
       <c r="L51" t="n">
-        <v>59.02</v>
+        <v>91.06</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>43.71</v>
+        <v>44.34</v>
       </c>
       <c r="K52" t="n">
-        <v>-134.87</v>
+        <v>-136.79</v>
       </c>
       <c r="L52" t="n">
-        <v>141.78</v>
+        <v>143.8</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>164.47</v>
+        <v>178.96</v>
       </c>
       <c r="K53" t="n">
-        <v>-46.46</v>
+        <v>-50.56</v>
       </c>
       <c r="L53" t="n">
-        <v>170.91</v>
+        <v>185.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-146.97</v>
+        <v>-156.96</v>
       </c>
       <c r="K54" t="n">
-        <v>263.21</v>
+        <v>281.11</v>
       </c>
       <c r="L54" t="n">
-        <v>301.47</v>
+        <v>321.96</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>4.04</v>
+        <v>4.84</v>
       </c>
       <c r="K55" t="n">
-        <v>165.58</v>
+        <v>198.34</v>
       </c>
       <c r="L55" t="n">
-        <v>165.63</v>
+        <v>198.4</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>258.52</v>
+        <v>299.42</v>
       </c>
       <c r="K56" t="n">
-        <v>-262.88</v>
+        <v>-304.47</v>
       </c>
       <c r="L56" t="n">
-        <v>368.7</v>
+        <v>427.03</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-148.61</v>
+        <v>-199.27</v>
       </c>
       <c r="K57" t="n">
-        <v>106.41</v>
+        <v>142.69</v>
       </c>
       <c r="L57" t="n">
-        <v>182.78</v>
+        <v>245.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>372.15</v>
+        <v>352.84</v>
       </c>
       <c r="K58" t="n">
-        <v>-162.89</v>
+        <v>-154.44</v>
       </c>
       <c r="L58" t="n">
-        <v>406.24</v>
+        <v>385.16</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>73.73</v>
+        <v>50.82</v>
       </c>
       <c r="K59" t="n">
-        <v>105.29</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>128.54</v>
+        <v>88.59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-59.7</v>
+        <v>-47.54</v>
       </c>
       <c r="K60" t="n">
-        <v>44.01</v>
+        <v>35.04</v>
       </c>
       <c r="L60" t="n">
-        <v>74.17</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-24.75</v>
+        <v>-31.38</v>
       </c>
       <c r="K61" t="n">
-        <v>29.29</v>
+        <v>37.14</v>
       </c>
       <c r="L61" t="n">
-        <v>38.34</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>3.83</v>
+        <v>3.66</v>
       </c>
       <c r="K62" t="n">
-        <v>-75.33</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>75.43000000000001</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>102.11</v>
+        <v>82.69</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.02</v>
+        <v>-12.17</v>
       </c>
       <c r="L63" t="n">
-        <v>103.21</v>
+        <v>83.58</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-94.66</v>
+        <v>-71.8</v>
       </c>
       <c r="K64" t="n">
-        <v>-26.12</v>
+        <v>-19.81</v>
       </c>
       <c r="L64" t="n">
-        <v>98.2</v>
+        <v>74.48</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>46.74</v>
+        <v>69.97</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.74</v>
+        <v>-4.1</v>
       </c>
       <c r="L65" t="n">
-        <v>46.82</v>
+        <v>70.09</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>192.98</v>
+        <v>175.4</v>
       </c>
       <c r="K66" t="n">
-        <v>-111.15</v>
+        <v>-101.02</v>
       </c>
       <c r="L66" t="n">
-        <v>222.7</v>
+        <v>202.42</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>20.56</v>
+        <v>32.96</v>
       </c>
       <c r="K67" t="n">
-        <v>57.96</v>
+        <v>92.95</v>
       </c>
       <c r="L67" t="n">
-        <v>61.5</v>
+        <v>98.62</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-42.88</v>
+        <v>-57.3</v>
       </c>
       <c r="K68" t="n">
-        <v>111.06</v>
+        <v>148.39</v>
       </c>
       <c r="L68" t="n">
-        <v>119.05</v>
+        <v>159.07</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>13.04</v>
+        <v>20.11</v>
       </c>
       <c r="K69" t="n">
-        <v>-79.67</v>
+        <v>-122.85</v>
       </c>
       <c r="L69" t="n">
-        <v>80.73</v>
+        <v>124.48</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-225.69</v>
+        <v>-210.93</v>
       </c>
       <c r="K70" t="n">
-        <v>-244.77</v>
+        <v>-228.76</v>
       </c>
       <c r="L70" t="n">
-        <v>332.94</v>
+        <v>311.17</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>73.31999999999999</v>
+        <v>137.63</v>
       </c>
       <c r="K71" t="n">
-        <v>-112.92</v>
+        <v>-211.94</v>
       </c>
       <c r="L71" t="n">
-        <v>134.63</v>
+        <v>252.71</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>244.3</v>
+        <v>233.38</v>
       </c>
       <c r="K72" t="n">
-        <v>-305.35</v>
+        <v>-291.7</v>
       </c>
       <c r="L72" t="n">
-        <v>391.05</v>
+        <v>373.57</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>27.87</v>
+        <v>41.73</v>
       </c>
       <c r="K73" t="n">
-        <v>115.12</v>
+        <v>172.37</v>
       </c>
       <c r="L73" t="n">
-        <v>118.45</v>
+        <v>177.35</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>36.83</v>
+        <v>33.86</v>
       </c>
       <c r="K74" t="n">
-        <v>79.77</v>
+        <v>73.34</v>
       </c>
       <c r="L74" t="n">
-        <v>87.86</v>
+        <v>80.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>33.98</v>
+        <v>28.35</v>
       </c>
       <c r="K75" t="n">
-        <v>-61.26</v>
+        <v>-51.11</v>
       </c>
       <c r="L75" t="n">
-        <v>70.05</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>67.66</v>
+        <v>61.23</v>
       </c>
       <c r="K76" t="n">
-        <v>54.93</v>
+        <v>49.71</v>
       </c>
       <c r="L76" t="n">
-        <v>87.15000000000001</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-47.34</v>
+        <v>-37.9</v>
       </c>
       <c r="K77" t="n">
-        <v>-112.44</v>
+        <v>-90.02</v>
       </c>
       <c r="L77" t="n">
-        <v>122</v>
+        <v>97.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>5.64</v>
+        <v>4.97</v>
       </c>
       <c r="K78" t="n">
-        <v>83.23999999999999</v>
+        <v>73.37</v>
       </c>
       <c r="L78" t="n">
-        <v>83.43000000000001</v>
+        <v>73.53</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>73.92</v>
+        <v>64.27</v>
       </c>
       <c r="K79" t="n">
-        <v>74.81999999999999</v>
+        <v>65.06</v>
       </c>
       <c r="L79" t="n">
-        <v>105.18</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>74.01000000000001</v>
+        <v>91.69</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.59</v>
+        <v>-1.97</v>
       </c>
       <c r="L80" t="n">
-        <v>74.03</v>
+        <v>91.70999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-21.76</v>
+        <v>-24.79</v>
       </c>
       <c r="K81" t="n">
-        <v>-70.48999999999999</v>
+        <v>-80.31</v>
       </c>
       <c r="L81" t="n">
-        <v>73.77</v>
+        <v>84.05</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>85.55</v>
+        <v>97.05</v>
       </c>
       <c r="K82" t="n">
-        <v>-60.37</v>
+        <v>-68.48999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>104.71</v>
+        <v>118.79</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>40.63</v>
+        <v>53.24</v>
       </c>
       <c r="K83" t="n">
-        <v>-116.96</v>
+        <v>-153.26</v>
       </c>
       <c r="L83" t="n">
-        <v>123.82</v>
+        <v>162.24</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>68.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>-71.62</v>
+        <v>-95.45999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>98.90000000000001</v>
+        <v>131.82</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-121.06</v>
+        <v>-122.9</v>
       </c>
       <c r="K85" t="n">
-        <v>-152.74</v>
+        <v>-155.07</v>
       </c>
       <c r="L85" t="n">
-        <v>194.9</v>
+        <v>197.86</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-99.55</v>
+        <v>-197.81</v>
       </c>
       <c r="K86" t="n">
-        <v>-10.53</v>
+        <v>-20.92</v>
       </c>
       <c r="L86" t="n">
-        <v>100.1</v>
+        <v>198.91</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-48.91</v>
+        <v>-71.38</v>
       </c>
       <c r="K87" t="n">
-        <v>-185.31</v>
+        <v>-270.46</v>
       </c>
       <c r="L87" t="n">
-        <v>191.65</v>
+        <v>279.72</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-134.47</v>
+        <v>-176.54</v>
       </c>
       <c r="K88" t="n">
-        <v>254.91</v>
+        <v>334.67</v>
       </c>
       <c r="L88" t="n">
-        <v>288.2</v>
+        <v>378.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-86.84</v>
+        <v>-74.67</v>
       </c>
       <c r="K14" t="n">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="L14" t="n">
-        <v>86.89</v>
+        <v>74.72</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-73.34999999999999</v>
+        <v>-59.08</v>
       </c>
       <c r="K15" t="n">
-        <v>-24.3</v>
+        <v>-19.57</v>
       </c>
       <c r="L15" t="n">
-        <v>77.27</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>27.62</v>
+        <v>24.07</v>
       </c>
       <c r="K16" t="n">
-        <v>35.83</v>
+        <v>31.23</v>
       </c>
       <c r="L16" t="n">
-        <v>45.24</v>
+        <v>39.43</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>32.91</v>
+        <v>30.78</v>
       </c>
       <c r="K17" t="n">
-        <v>-25.77</v>
+        <v>-24.1</v>
       </c>
       <c r="L17" t="n">
-        <v>41.8</v>
+        <v>39.09</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>12.27</v>
+        <v>11.86</v>
       </c>
       <c r="K18" t="n">
-        <v>66.59</v>
+        <v>64.36</v>
       </c>
       <c r="L18" t="n">
-        <v>67.70999999999999</v>
+        <v>65.44</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-51.33</v>
+        <v>-43.53</v>
       </c>
       <c r="K19" t="n">
-        <v>-51.64</v>
+        <v>-43.79</v>
       </c>
       <c r="L19" t="n">
-        <v>72.81</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>49.98</v>
+        <v>35.76</v>
       </c>
       <c r="K20" t="n">
-        <v>-185.97</v>
+        <v>-133.04</v>
       </c>
       <c r="L20" t="n">
-        <v>192.57</v>
+        <v>137.76</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-131.72</v>
+        <v>-96.48999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-108.52</v>
+        <v>-79.48999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>170.67</v>
+        <v>125.01</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-102.79</v>
+        <v>-73.43000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>134.01</v>
+        <v>95.73</v>
       </c>
       <c r="L22" t="n">
-        <v>168.89</v>
+        <v>120.65</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>163.57</v>
+        <v>108.69</v>
       </c>
       <c r="K23" t="n">
-        <v>-70.17</v>
+        <v>-46.63</v>
       </c>
       <c r="L23" t="n">
-        <v>177.99</v>
+        <v>118.27</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>19.13</v>
+        <v>12.19</v>
       </c>
       <c r="K24" t="n">
-        <v>-223.48</v>
+        <v>-142.47</v>
       </c>
       <c r="L24" t="n">
-        <v>224.3</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>148.63</v>
+        <v>98.7</v>
       </c>
       <c r="K25" t="n">
-        <v>40.9</v>
+        <v>27.16</v>
       </c>
       <c r="L25" t="n">
-        <v>154.16</v>
+        <v>102.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>210.2</v>
+        <v>111.54</v>
       </c>
       <c r="K26" t="n">
-        <v>559.9299999999999</v>
+        <v>297.12</v>
       </c>
       <c r="L26" t="n">
-        <v>598.09</v>
+        <v>317.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-210.84</v>
+        <v>-112.01</v>
       </c>
       <c r="K27" t="n">
-        <v>-14.04</v>
+        <v>-7.46</v>
       </c>
       <c r="L27" t="n">
-        <v>211.31</v>
+        <v>112.26</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>224.08</v>
+        <v>144.17</v>
       </c>
       <c r="K28" t="n">
-        <v>264.97</v>
+        <v>170.48</v>
       </c>
       <c r="L28" t="n">
-        <v>347.02</v>
+        <v>223.26</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>68</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-26.43</v>
+        <v>-25.73</v>
       </c>
       <c r="L29" t="n">
-        <v>72.95999999999999</v>
+        <v>71.03</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-25.28</v>
+        <v>-19.84</v>
       </c>
       <c r="K30" t="n">
-        <v>68.81999999999999</v>
+        <v>54</v>
       </c>
       <c r="L30" t="n">
-        <v>73.31999999999999</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>51.03</v>
+        <v>44.25</v>
       </c>
       <c r="K31" t="n">
-        <v>-68.76000000000001</v>
+        <v>-59.62</v>
       </c>
       <c r="L31" t="n">
-        <v>85.63</v>
+        <v>74.23999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.43</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-49.83</v>
+        <v>-47.38</v>
       </c>
       <c r="L32" t="n">
-        <v>50.72</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>38.54</v>
+        <v>30.27</v>
       </c>
       <c r="K33" t="n">
-        <v>-38.3</v>
+        <v>-30.09</v>
       </c>
       <c r="L33" t="n">
-        <v>54.33</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-52.44</v>
+        <v>-40.68</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.15</v>
+        <v>-6.33</v>
       </c>
       <c r="L34" t="n">
-        <v>53.07</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>51.02</v>
+        <v>33.53</v>
       </c>
       <c r="K35" t="n">
-        <v>-67.36</v>
+        <v>-44.27</v>
       </c>
       <c r="L35" t="n">
-        <v>84.5</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>41.78</v>
+        <v>34.32</v>
       </c>
       <c r="K36" t="n">
-        <v>79.27</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>89.61</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>125.34</v>
+        <v>87.64</v>
       </c>
       <c r="K37" t="n">
-        <v>-59.28</v>
+        <v>-41.45</v>
       </c>
       <c r="L37" t="n">
-        <v>138.65</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-222.83</v>
+        <v>-127.36</v>
       </c>
       <c r="K38" t="n">
-        <v>-77.48999999999999</v>
+        <v>-44.29</v>
       </c>
       <c r="L38" t="n">
-        <v>235.92</v>
+        <v>134.84</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>11.19</v>
+        <v>6.19</v>
       </c>
       <c r="K39" t="n">
-        <v>-203.43</v>
+        <v>-112.63</v>
       </c>
       <c r="L39" t="n">
-        <v>203.74</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-82.73999999999999</v>
+        <v>-52.82</v>
       </c>
       <c r="K40" t="n">
-        <v>-34.64</v>
+        <v>-22.11</v>
       </c>
       <c r="L40" t="n">
-        <v>89.7</v>
+        <v>57.26</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>197.67</v>
+        <v>116.99</v>
       </c>
       <c r="K41" t="n">
-        <v>300.7</v>
+        <v>177.97</v>
       </c>
       <c r="L41" t="n">
-        <v>359.85</v>
+        <v>212.97</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-121.74</v>
+        <v>-78.5</v>
       </c>
       <c r="K42" t="n">
-        <v>133.97</v>
+        <v>86.39</v>
       </c>
       <c r="L42" t="n">
-        <v>181.02</v>
+        <v>116.72</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-380.78</v>
+        <v>-227.32</v>
       </c>
       <c r="K43" t="n">
-        <v>88.48999999999999</v>
+        <v>52.83</v>
       </c>
       <c r="L43" t="n">
-        <v>390.93</v>
+        <v>233.38</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>69.28</v>
+        <v>54.14</v>
       </c>
       <c r="K44" t="n">
-        <v>86.37</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>110.72</v>
+        <v>86.52</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>16.96</v>
+        <v>16.72</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.95</v>
+        <v>-32.48</v>
       </c>
       <c r="L45" t="n">
-        <v>37.06</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>42.38</v>
+        <v>36.67</v>
       </c>
       <c r="K46" t="n">
-        <v>36.56</v>
+        <v>31.64</v>
       </c>
       <c r="L46" t="n">
-        <v>55.97</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-7.12</v>
+        <v>-6.42</v>
       </c>
       <c r="K47" t="n">
-        <v>65.81999999999999</v>
+        <v>59.36</v>
       </c>
       <c r="L47" t="n">
-        <v>66.2</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>70.84</v>
+        <v>58.3</v>
       </c>
       <c r="K48" t="n">
-        <v>53.76</v>
+        <v>44.24</v>
       </c>
       <c r="L48" t="n">
-        <v>88.93000000000001</v>
+        <v>73.19</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-75.38</v>
+        <v>-59.39</v>
       </c>
       <c r="K49" t="n">
-        <v>13.48</v>
+        <v>10.62</v>
       </c>
       <c r="L49" t="n">
-        <v>76.56999999999999</v>
+        <v>60.33</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-65.36</v>
+        <v>-44.18</v>
       </c>
       <c r="K50" t="n">
-        <v>-245.75</v>
+        <v>-166.11</v>
       </c>
       <c r="L50" t="n">
-        <v>254.29</v>
+        <v>171.88</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>78.34</v>
+        <v>53.53</v>
       </c>
       <c r="K51" t="n">
-        <v>-46.41</v>
+        <v>-31.71</v>
       </c>
       <c r="L51" t="n">
-        <v>91.06</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>44.34</v>
+        <v>31.16</v>
       </c>
       <c r="K52" t="n">
-        <v>-136.79</v>
+        <v>-96.13</v>
       </c>
       <c r="L52" t="n">
-        <v>143.8</v>
+        <v>101.06</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>178.96</v>
+        <v>119.07</v>
       </c>
       <c r="K53" t="n">
-        <v>-50.56</v>
+        <v>-33.64</v>
       </c>
       <c r="L53" t="n">
-        <v>185.97</v>
+        <v>123.74</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-156.96</v>
+        <v>-89.58</v>
       </c>
       <c r="K54" t="n">
-        <v>281.11</v>
+        <v>160.43</v>
       </c>
       <c r="L54" t="n">
-        <v>321.96</v>
+        <v>183.74</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>4.84</v>
+        <v>2.96</v>
       </c>
       <c r="K55" t="n">
-        <v>198.34</v>
+        <v>121.58</v>
       </c>
       <c r="L55" t="n">
-        <v>198.4</v>
+        <v>121.62</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>299.42</v>
+        <v>157.88</v>
       </c>
       <c r="K56" t="n">
-        <v>-304.47</v>
+        <v>-160.54</v>
       </c>
       <c r="L56" t="n">
-        <v>427.03</v>
+        <v>225.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-199.27</v>
+        <v>-118.03</v>
       </c>
       <c r="K57" t="n">
-        <v>142.69</v>
+        <v>84.52</v>
       </c>
       <c r="L57" t="n">
-        <v>245.09</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>352.84</v>
+        <v>226.38</v>
       </c>
       <c r="K58" t="n">
-        <v>-154.44</v>
+        <v>-99.09</v>
       </c>
       <c r="L58" t="n">
-        <v>385.16</v>
+        <v>247.11</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>50.82</v>
+        <v>49.64</v>
       </c>
       <c r="K59" t="n">
-        <v>72.56999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="L59" t="n">
-        <v>88.59</v>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-47.54</v>
+        <v>-46.23</v>
       </c>
       <c r="K60" t="n">
-        <v>35.04</v>
+        <v>34.08</v>
       </c>
       <c r="L60" t="n">
-        <v>59.06</v>
+        <v>57.43</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-31.38</v>
+        <v>-25.07</v>
       </c>
       <c r="K61" t="n">
-        <v>37.14</v>
+        <v>29.67</v>
       </c>
       <c r="L61" t="n">
-        <v>48.62</v>
+        <v>38.84</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>3.66</v>
+        <v>3.23</v>
       </c>
       <c r="K62" t="n">
-        <v>-71.90000000000001</v>
+        <v>-63.41</v>
       </c>
       <c r="L62" t="n">
-        <v>71.98999999999999</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>82.69</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.17</v>
+        <v>-11.22</v>
       </c>
       <c r="L63" t="n">
-        <v>83.58</v>
+        <v>77.08</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-71.8</v>
+        <v>-70.38</v>
       </c>
       <c r="K64" t="n">
-        <v>-19.81</v>
+        <v>-19.42</v>
       </c>
       <c r="L64" t="n">
-        <v>74.48</v>
+        <v>73.01000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>69.97</v>
+        <v>57.23</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.1</v>
+        <v>-3.35</v>
       </c>
       <c r="L65" t="n">
-        <v>70.09</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>175.4</v>
+        <v>119.47</v>
       </c>
       <c r="K66" t="n">
-        <v>-101.02</v>
+        <v>-68.81</v>
       </c>
       <c r="L66" t="n">
-        <v>202.42</v>
+        <v>137.87</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>32.96</v>
+        <v>21.72</v>
       </c>
       <c r="K67" t="n">
-        <v>92.95</v>
+        <v>61.25</v>
       </c>
       <c r="L67" t="n">
-        <v>98.62</v>
+        <v>64.98</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-57.3</v>
+        <v>-36.47</v>
       </c>
       <c r="K68" t="n">
-        <v>148.39</v>
+        <v>94.45</v>
       </c>
       <c r="L68" t="n">
-        <v>159.07</v>
+        <v>101.24</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>20.11</v>
+        <v>13.34</v>
       </c>
       <c r="K69" t="n">
-        <v>-122.85</v>
+        <v>-81.45</v>
       </c>
       <c r="L69" t="n">
-        <v>124.48</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-210.93</v>
+        <v>-134.77</v>
       </c>
       <c r="K70" t="n">
-        <v>-228.76</v>
+        <v>-146.16</v>
       </c>
       <c r="L70" t="n">
-        <v>311.17</v>
+        <v>198.81</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>137.63</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-211.94</v>
+        <v>-108.46</v>
       </c>
       <c r="L71" t="n">
-        <v>252.71</v>
+        <v>129.32</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>233.38</v>
+        <v>150.34</v>
       </c>
       <c r="K72" t="n">
-        <v>-291.7</v>
+        <v>-187.91</v>
       </c>
       <c r="L72" t="n">
-        <v>373.57</v>
+        <v>240.65</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>41.73</v>
+        <v>27.11</v>
       </c>
       <c r="K73" t="n">
-        <v>172.37</v>
+        <v>111.98</v>
       </c>
       <c r="L73" t="n">
-        <v>177.35</v>
+        <v>115.21</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>33.86</v>
+        <v>26.53</v>
       </c>
       <c r="K74" t="n">
-        <v>73.34</v>
+        <v>57.47</v>
       </c>
       <c r="L74" t="n">
-        <v>80.78</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>28.35</v>
+        <v>25.15</v>
       </c>
       <c r="K75" t="n">
-        <v>-51.11</v>
+        <v>-45.35</v>
       </c>
       <c r="L75" t="n">
-        <v>58.45</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>61.23</v>
+        <v>49.31</v>
       </c>
       <c r="K76" t="n">
-        <v>49.71</v>
+        <v>40.03</v>
       </c>
       <c r="L76" t="n">
-        <v>78.87</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-37.9</v>
+        <v>-32.01</v>
       </c>
       <c r="K77" t="n">
-        <v>-90.02</v>
+        <v>-76.03</v>
       </c>
       <c r="L77" t="n">
-        <v>97.67</v>
+        <v>82.48999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>4.97</v>
+        <v>4.51</v>
       </c>
       <c r="K78" t="n">
-        <v>73.37</v>
+        <v>66.56</v>
       </c>
       <c r="L78" t="n">
-        <v>73.53</v>
+        <v>66.70999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>64.27</v>
+        <v>54.67</v>
       </c>
       <c r="K79" t="n">
-        <v>65.06</v>
+        <v>55.34</v>
       </c>
       <c r="L79" t="n">
-        <v>91.45</v>
+        <v>77.79000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>91.69</v>
+        <v>69.63</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.97</v>
+        <v>-1.49</v>
       </c>
       <c r="L80" t="n">
-        <v>91.70999999999999</v>
+        <v>69.64</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-24.79</v>
+        <v>-20.49</v>
       </c>
       <c r="K81" t="n">
-        <v>-80.31</v>
+        <v>-66.38</v>
       </c>
       <c r="L81" t="n">
-        <v>84.05</v>
+        <v>69.47</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>97.05</v>
+        <v>68.5</v>
       </c>
       <c r="K82" t="n">
-        <v>-68.48999999999999</v>
+        <v>-48.35</v>
       </c>
       <c r="L82" t="n">
-        <v>118.79</v>
+        <v>83.84999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>53.24</v>
+        <v>33.9</v>
       </c>
       <c r="K83" t="n">
-        <v>-153.26</v>
+        <v>-97.58</v>
       </c>
       <c r="L83" t="n">
-        <v>162.24</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>90.90000000000001</v>
+        <v>63.08</v>
       </c>
       <c r="K84" t="n">
-        <v>-95.45999999999999</v>
+        <v>-66.23999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>131.82</v>
+        <v>91.47</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-122.9</v>
+        <v>-85.26000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-155.07</v>
+        <v>-107.57</v>
       </c>
       <c r="L85" t="n">
-        <v>197.86</v>
+        <v>137.26</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-197.81</v>
+        <v>-112.11</v>
       </c>
       <c r="K86" t="n">
-        <v>-20.92</v>
+        <v>-11.86</v>
       </c>
       <c r="L86" t="n">
-        <v>198.91</v>
+        <v>112.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-71.38</v>
+        <v>-39.01</v>
       </c>
       <c r="K87" t="n">
-        <v>-270.46</v>
+        <v>-147.81</v>
       </c>
       <c r="L87" t="n">
-        <v>279.72</v>
+        <v>152.88</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-176.54</v>
+        <v>-90.26000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>334.67</v>
+        <v>171.11</v>
       </c>
       <c r="L88" t="n">
-        <v>378.38</v>
+        <v>193.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-74.67</v>
+        <v>-75.43000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="L14" t="n">
-        <v>74.72</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-59.08</v>
+        <v>-59.01</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.57</v>
+        <v>-19.55</v>
       </c>
       <c r="L15" t="n">
-        <v>62.23</v>
+        <v>62.16</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>24.07</v>
+        <v>23.67</v>
       </c>
       <c r="K16" t="n">
-        <v>31.23</v>
+        <v>30.71</v>
       </c>
       <c r="L16" t="n">
-        <v>39.43</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>30.78</v>
+        <v>31.77</v>
       </c>
       <c r="K17" t="n">
-        <v>-24.1</v>
+        <v>-24.88</v>
       </c>
       <c r="L17" t="n">
-        <v>39.09</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>11.86</v>
+        <v>12.33</v>
       </c>
       <c r="K18" t="n">
-        <v>64.36</v>
+        <v>66.92</v>
       </c>
       <c r="L18" t="n">
-        <v>65.44</v>
+        <v>68.04000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-43.53</v>
+        <v>-45.75</v>
       </c>
       <c r="K19" t="n">
-        <v>-43.79</v>
+        <v>-46.02</v>
       </c>
       <c r="L19" t="n">
-        <v>61.74</v>
+        <v>64.89</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>35.76</v>
+        <v>40.16</v>
       </c>
       <c r="K20" t="n">
-        <v>-133.04</v>
+        <v>-149.4</v>
       </c>
       <c r="L20" t="n">
-        <v>137.76</v>
+        <v>154.71</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-96.48999999999999</v>
+        <v>-107.1</v>
       </c>
       <c r="K21" t="n">
-        <v>-79.48999999999999</v>
+        <v>-88.23</v>
       </c>
       <c r="L21" t="n">
-        <v>125.01</v>
+        <v>138.76</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-73.43000000000001</v>
+        <v>-82.05</v>
       </c>
       <c r="K22" t="n">
-        <v>95.73</v>
+        <v>106.96</v>
       </c>
       <c r="L22" t="n">
-        <v>120.65</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>108.69</v>
+        <v>123.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-46.63</v>
+        <v>-53.1</v>
       </c>
       <c r="L23" t="n">
-        <v>118.27</v>
+        <v>134.69</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>12.19</v>
+        <v>13.91</v>
       </c>
       <c r="K24" t="n">
-        <v>-142.47</v>
+        <v>-162.5</v>
       </c>
       <c r="L24" t="n">
-        <v>142.99</v>
+        <v>163.09</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>98.7</v>
+        <v>111.89</v>
       </c>
       <c r="K25" t="n">
-        <v>27.16</v>
+        <v>30.79</v>
       </c>
       <c r="L25" t="n">
-        <v>102.37</v>
+        <v>116.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>111.54</v>
+        <v>130.16</v>
       </c>
       <c r="K26" t="n">
-        <v>297.12</v>
+        <v>346.73</v>
       </c>
       <c r="L26" t="n">
-        <v>317.37</v>
+        <v>370.36</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-112.01</v>
+        <v>-130.93</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.46</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>112.26</v>
+        <v>131.22</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>144.17</v>
+        <v>165.03</v>
       </c>
       <c r="K28" t="n">
-        <v>170.48</v>
+        <v>195.16</v>
       </c>
       <c r="L28" t="n">
-        <v>223.26</v>
+        <v>255.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>66.20999999999999</v>
+        <v>65.66</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.73</v>
+        <v>-25.51</v>
       </c>
       <c r="L29" t="n">
-        <v>71.03</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-19.84</v>
+        <v>-19.9</v>
       </c>
       <c r="K30" t="n">
-        <v>54</v>
+        <v>54.17</v>
       </c>
       <c r="L30" t="n">
-        <v>57.52</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>44.25</v>
+        <v>43.5</v>
       </c>
       <c r="K31" t="n">
-        <v>-59.62</v>
+        <v>-58.61</v>
       </c>
       <c r="L31" t="n">
-        <v>74.23999999999999</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-8.960000000000001</v>
+        <v>-9.25</v>
       </c>
       <c r="K32" t="n">
-        <v>-47.38</v>
+        <v>-48.9</v>
       </c>
       <c r="L32" t="n">
-        <v>48.22</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>30.27</v>
+        <v>31.84</v>
       </c>
       <c r="K33" t="n">
-        <v>-30.09</v>
+        <v>-31.65</v>
       </c>
       <c r="L33" t="n">
-        <v>42.68</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-40.68</v>
+        <v>-42.74</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.33</v>
+        <v>-6.65</v>
       </c>
       <c r="L34" t="n">
-        <v>41.17</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>33.53</v>
+        <v>37.64</v>
       </c>
       <c r="K35" t="n">
-        <v>-44.27</v>
+        <v>-49.7</v>
       </c>
       <c r="L35" t="n">
-        <v>55.54</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>34.32</v>
+        <v>37.36</v>
       </c>
       <c r="K36" t="n">
-        <v>65.09999999999999</v>
+        <v>70.88</v>
       </c>
       <c r="L36" t="n">
-        <v>73.59</v>
+        <v>80.12</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>87.64</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-41.45</v>
+        <v>-46.3</v>
       </c>
       <c r="L37" t="n">
-        <v>96.95</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-127.36</v>
+        <v>-146.58</v>
       </c>
       <c r="K38" t="n">
-        <v>-44.29</v>
+        <v>-50.97</v>
       </c>
       <c r="L38" t="n">
-        <v>134.84</v>
+        <v>155.18</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>6.19</v>
+        <v>7.14</v>
       </c>
       <c r="K39" t="n">
-        <v>-112.63</v>
+        <v>-129.91</v>
       </c>
       <c r="L39" t="n">
-        <v>112.8</v>
+        <v>130.1</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-52.82</v>
+        <v>-60.15</v>
       </c>
       <c r="K40" t="n">
-        <v>-22.11</v>
+        <v>-25.19</v>
       </c>
       <c r="L40" t="n">
-        <v>57.26</v>
+        <v>65.20999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>116.99</v>
+        <v>136.51</v>
       </c>
       <c r="K41" t="n">
-        <v>177.97</v>
+        <v>207.67</v>
       </c>
       <c r="L41" t="n">
-        <v>212.97</v>
+        <v>248.52</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-78.5</v>
+        <v>-89.47</v>
       </c>
       <c r="K42" t="n">
-        <v>86.39</v>
+        <v>98.47</v>
       </c>
       <c r="L42" t="n">
-        <v>116.72</v>
+        <v>133.04</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-227.32</v>
+        <v>-261.49</v>
       </c>
       <c r="K43" t="n">
-        <v>52.83</v>
+        <v>60.77</v>
       </c>
       <c r="L43" t="n">
-        <v>233.38</v>
+        <v>268.46</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>54.14</v>
+        <v>55.11</v>
       </c>
       <c r="K44" t="n">
-        <v>67.48999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="L44" t="n">
-        <v>86.52</v>
+        <v>88.06999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>16.72</v>
+        <v>16.1</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.48</v>
+        <v>-31.28</v>
       </c>
       <c r="L45" t="n">
-        <v>36.54</v>
+        <v>35.18</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>36.67</v>
+        <v>36.57</v>
       </c>
       <c r="K46" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="L46" t="n">
-        <v>48.43</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-6.42</v>
+        <v>-6.64</v>
       </c>
       <c r="K47" t="n">
-        <v>59.36</v>
+        <v>61.34</v>
       </c>
       <c r="L47" t="n">
-        <v>59.7</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>58.3</v>
+        <v>61.57</v>
       </c>
       <c r="K48" t="n">
-        <v>44.24</v>
+        <v>46.72</v>
       </c>
       <c r="L48" t="n">
-        <v>73.19</v>
+        <v>77.29000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-59.39</v>
+        <v>-62.28</v>
       </c>
       <c r="K49" t="n">
-        <v>10.62</v>
+        <v>11.14</v>
       </c>
       <c r="L49" t="n">
-        <v>60.33</v>
+        <v>63.27</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-44.18</v>
+        <v>-49.59</v>
       </c>
       <c r="K50" t="n">
-        <v>-166.11</v>
+        <v>-186.47</v>
       </c>
       <c r="L50" t="n">
-        <v>171.88</v>
+        <v>192.95</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>53.53</v>
+        <v>60.46</v>
       </c>
       <c r="K51" t="n">
-        <v>-31.71</v>
+        <v>-35.82</v>
       </c>
       <c r="L51" t="n">
-        <v>62.21</v>
+        <v>70.27</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>31.16</v>
+        <v>35.08</v>
       </c>
       <c r="K52" t="n">
-        <v>-96.13</v>
+        <v>-108.24</v>
       </c>
       <c r="L52" t="n">
-        <v>101.06</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>119.07</v>
+        <v>135.75</v>
       </c>
       <c r="K53" t="n">
-        <v>-33.64</v>
+        <v>-38.35</v>
       </c>
       <c r="L53" t="n">
-        <v>123.74</v>
+        <v>141.07</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-89.58</v>
+        <v>-103.74</v>
       </c>
       <c r="K54" t="n">
-        <v>160.43</v>
+        <v>185.79</v>
       </c>
       <c r="L54" t="n">
-        <v>183.74</v>
+        <v>212.79</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="K55" t="n">
-        <v>121.58</v>
+        <v>140.01</v>
       </c>
       <c r="L55" t="n">
-        <v>121.62</v>
+        <v>140.05</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>157.88</v>
+        <v>183.55</v>
       </c>
       <c r="K56" t="n">
-        <v>-160.54</v>
+        <v>-186.64</v>
       </c>
       <c r="L56" t="n">
-        <v>225.16</v>
+        <v>261.77</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-118.03</v>
+        <v>-137.73</v>
       </c>
       <c r="K57" t="n">
-        <v>84.52</v>
+        <v>98.62</v>
       </c>
       <c r="L57" t="n">
-        <v>145.17</v>
+        <v>169.4</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>226.38</v>
+        <v>259.4</v>
       </c>
       <c r="K58" t="n">
-        <v>-99.09</v>
+        <v>-113.54</v>
       </c>
       <c r="L58" t="n">
-        <v>247.11</v>
+        <v>283.16</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>49.64</v>
+        <v>49.08</v>
       </c>
       <c r="K59" t="n">
-        <v>70.89</v>
+        <v>70.09</v>
       </c>
       <c r="L59" t="n">
-        <v>86.54000000000001</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-46.23</v>
+        <v>-45.69</v>
       </c>
       <c r="K60" t="n">
-        <v>34.08</v>
+        <v>33.68</v>
       </c>
       <c r="L60" t="n">
-        <v>57.43</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-25.07</v>
+        <v>-25.63</v>
       </c>
       <c r="K61" t="n">
-        <v>29.67</v>
+        <v>30.34</v>
       </c>
       <c r="L61" t="n">
-        <v>38.84</v>
+        <v>39.72</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="K62" t="n">
-        <v>-63.41</v>
+        <v>-65.75</v>
       </c>
       <c r="L62" t="n">
-        <v>63.49</v>
+        <v>65.84</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>76.26000000000001</v>
+        <v>79.38</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.22</v>
+        <v>-11.68</v>
       </c>
       <c r="L63" t="n">
-        <v>77.08</v>
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-70.38</v>
+        <v>-71.53</v>
       </c>
       <c r="K64" t="n">
-        <v>-19.42</v>
+        <v>-19.74</v>
       </c>
       <c r="L64" t="n">
-        <v>73.01000000000001</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>57.23</v>
+        <v>63.51</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.35</v>
+        <v>-3.72</v>
       </c>
       <c r="L65" t="n">
-        <v>57.33</v>
+        <v>63.62</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>119.47</v>
+        <v>133.23</v>
       </c>
       <c r="K66" t="n">
-        <v>-68.81</v>
+        <v>-76.73</v>
       </c>
       <c r="L66" t="n">
-        <v>137.87</v>
+        <v>153.75</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>21.72</v>
+        <v>24.43</v>
       </c>
       <c r="K67" t="n">
-        <v>61.25</v>
+        <v>68.88</v>
       </c>
       <c r="L67" t="n">
-        <v>64.98</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-36.47</v>
+        <v>-42.08</v>
       </c>
       <c r="K68" t="n">
-        <v>94.45</v>
+        <v>108.97</v>
       </c>
       <c r="L68" t="n">
-        <v>101.24</v>
+        <v>116.81</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>13.34</v>
+        <v>15.06</v>
       </c>
       <c r="K69" t="n">
-        <v>-81.45</v>
+        <v>-91.98999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>82.54000000000001</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-134.77</v>
+        <v>-154.96</v>
       </c>
       <c r="K70" t="n">
-        <v>-146.16</v>
+        <v>-168.06</v>
       </c>
       <c r="L70" t="n">
-        <v>198.81</v>
+        <v>228.6</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>70.43000000000001</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-108.46</v>
+        <v>-128.3</v>
       </c>
       <c r="L71" t="n">
-        <v>129.32</v>
+        <v>152.98</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>150.34</v>
+        <v>173.73</v>
       </c>
       <c r="K72" t="n">
-        <v>-187.91</v>
+        <v>-217.14</v>
       </c>
       <c r="L72" t="n">
-        <v>240.65</v>
+        <v>278.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>27.11</v>
+        <v>30.89</v>
       </c>
       <c r="K73" t="n">
-        <v>111.98</v>
+        <v>127.6</v>
       </c>
       <c r="L73" t="n">
-        <v>115.21</v>
+        <v>131.29</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>26.53</v>
+        <v>26.34</v>
       </c>
       <c r="K74" t="n">
-        <v>57.47</v>
+        <v>57.06</v>
       </c>
       <c r="L74" t="n">
-        <v>63.3</v>
+        <v>62.85</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>25.15</v>
+        <v>25.62</v>
       </c>
       <c r="K75" t="n">
-        <v>-45.35</v>
+        <v>-46.2</v>
       </c>
       <c r="L75" t="n">
-        <v>51.85</v>
+        <v>52.83</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>49.31</v>
+        <v>49.66</v>
       </c>
       <c r="K76" t="n">
-        <v>40.03</v>
+        <v>40.32</v>
       </c>
       <c r="L76" t="n">
-        <v>63.51</v>
+        <v>63.96</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-32.01</v>
+        <v>-33.17</v>
       </c>
       <c r="K77" t="n">
-        <v>-76.03</v>
+        <v>-78.78</v>
       </c>
       <c r="L77" t="n">
-        <v>82.48999999999999</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>4.51</v>
+        <v>4.66</v>
       </c>
       <c r="K78" t="n">
-        <v>66.56</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>66.70999999999999</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>54.67</v>
+        <v>57.23</v>
       </c>
       <c r="K79" t="n">
-        <v>55.34</v>
+        <v>57.93</v>
       </c>
       <c r="L79" t="n">
-        <v>77.79000000000001</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>69.63</v>
+        <v>76.92</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.49</v>
+        <v>-1.65</v>
       </c>
       <c r="L80" t="n">
-        <v>69.64</v>
+        <v>76.93000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-20.49</v>
+        <v>-22.52</v>
       </c>
       <c r="K81" t="n">
-        <v>-66.38</v>
+        <v>-72.98</v>
       </c>
       <c r="L81" t="n">
-        <v>69.47</v>
+        <v>76.38</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>68.5</v>
+        <v>76.36</v>
       </c>
       <c r="K82" t="n">
-        <v>-48.35</v>
+        <v>-53.89</v>
       </c>
       <c r="L82" t="n">
-        <v>83.84999999999999</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>33.9</v>
+        <v>38.83</v>
       </c>
       <c r="K83" t="n">
-        <v>-97.58</v>
+        <v>-111.79</v>
       </c>
       <c r="L83" t="n">
-        <v>103.3</v>
+        <v>118.34</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>63.08</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-66.23999999999999</v>
+        <v>-75.42</v>
       </c>
       <c r="L84" t="n">
-        <v>91.47</v>
+        <v>104.15</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-85.26000000000001</v>
+        <v>-96.77</v>
       </c>
       <c r="K85" t="n">
-        <v>-107.57</v>
+        <v>-122.1</v>
       </c>
       <c r="L85" t="n">
-        <v>137.26</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-112.11</v>
+        <v>-130.74</v>
       </c>
       <c r="K86" t="n">
-        <v>-11.86</v>
+        <v>-13.83</v>
       </c>
       <c r="L86" t="n">
-        <v>112.73</v>
+        <v>131.47</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-39.01</v>
+        <v>-45.72</v>
       </c>
       <c r="K87" t="n">
-        <v>-147.81</v>
+        <v>-173.22</v>
       </c>
       <c r="L87" t="n">
-        <v>152.88</v>
+        <v>179.15</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-90.26000000000001</v>
+        <v>-106.66</v>
       </c>
       <c r="K88" t="n">
-        <v>171.11</v>
+        <v>202.2</v>
       </c>
       <c r="L88" t="n">
-        <v>193.46</v>
+        <v>228.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-75.43000000000001</v>
+        <v>-56.57</v>
       </c>
       <c r="K14" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>75.48</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-59.01</v>
+        <v>-44.25</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.55</v>
+        <v>-14.66</v>
       </c>
       <c r="L15" t="n">
-        <v>62.16</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>23.67</v>
+        <v>17.75</v>
       </c>
       <c r="K16" t="n">
-        <v>30.71</v>
+        <v>23.04</v>
       </c>
       <c r="L16" t="n">
-        <v>38.78</v>
+        <v>29.08</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>31.77</v>
+        <v>23.83</v>
       </c>
       <c r="K17" t="n">
-        <v>-24.88</v>
+        <v>-18.66</v>
       </c>
       <c r="L17" t="n">
-        <v>40.36</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>12.33</v>
+        <v>9.25</v>
       </c>
       <c r="K18" t="n">
-        <v>66.92</v>
+        <v>50.19</v>
       </c>
       <c r="L18" t="n">
-        <v>68.04000000000001</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-45.75</v>
+        <v>-34.31</v>
       </c>
       <c r="K19" t="n">
-        <v>-46.02</v>
+        <v>-34.52</v>
       </c>
       <c r="L19" t="n">
-        <v>64.89</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>40.16</v>
+        <v>30.12</v>
       </c>
       <c r="K20" t="n">
-        <v>-149.4</v>
+        <v>-112.05</v>
       </c>
       <c r="L20" t="n">
-        <v>154.71</v>
+        <v>116.03</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-107.1</v>
+        <v>-80.31999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-88.23</v>
+        <v>-66.17</v>
       </c>
       <c r="L21" t="n">
-        <v>138.76</v>
+        <v>104.07</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-82.05</v>
+        <v>-61.54</v>
       </c>
       <c r="K22" t="n">
-        <v>106.96</v>
+        <v>80.22</v>
       </c>
       <c r="L22" t="n">
-        <v>134.81</v>
+        <v>101.11</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>123.78</v>
+        <v>92.84</v>
       </c>
       <c r="K23" t="n">
-        <v>-53.1</v>
+        <v>-39.83</v>
       </c>
       <c r="L23" t="n">
-        <v>134.69</v>
+        <v>101.02</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>13.91</v>
+        <v>10.43</v>
       </c>
       <c r="K24" t="n">
-        <v>-162.5</v>
+        <v>-121.87</v>
       </c>
       <c r="L24" t="n">
-        <v>163.09</v>
+        <v>122.32</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>111.89</v>
+        <v>83.92</v>
       </c>
       <c r="K25" t="n">
-        <v>30.79</v>
+        <v>23.09</v>
       </c>
       <c r="L25" t="n">
-        <v>116.05</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>130.16</v>
+        <v>80.38</v>
       </c>
       <c r="K26" t="n">
-        <v>346.73</v>
+        <v>214.12</v>
       </c>
       <c r="L26" t="n">
-        <v>370.36</v>
+        <v>228.71</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-130.93</v>
+        <v>-98.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.720000000000001</v>
+        <v>-6.54</v>
       </c>
       <c r="L27" t="n">
-        <v>131.22</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>165.03</v>
+        <v>123.78</v>
       </c>
       <c r="K28" t="n">
-        <v>195.16</v>
+        <v>146.37</v>
       </c>
       <c r="L28" t="n">
-        <v>255.58</v>
+        <v>191.69</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>65.66</v>
+        <v>49.24</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.51</v>
+        <v>-19.13</v>
       </c>
       <c r="L29" t="n">
-        <v>70.44</v>
+        <v>52.83</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-19.9</v>
+        <v>-14.93</v>
       </c>
       <c r="K30" t="n">
-        <v>54.17</v>
+        <v>40.63</v>
       </c>
       <c r="L30" t="n">
-        <v>57.71</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>43.5</v>
+        <v>32.63</v>
       </c>
       <c r="K31" t="n">
-        <v>-58.61</v>
+        <v>-43.96</v>
       </c>
       <c r="L31" t="n">
-        <v>72.98999999999999</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.25</v>
+        <v>-6.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-48.9</v>
+        <v>-36.67</v>
       </c>
       <c r="L32" t="n">
-        <v>49.76</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>31.84</v>
+        <v>23.88</v>
       </c>
       <c r="K33" t="n">
-        <v>-31.65</v>
+        <v>-23.74</v>
       </c>
       <c r="L33" t="n">
-        <v>44.89</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-42.74</v>
+        <v>-32.06</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.65</v>
+        <v>-4.99</v>
       </c>
       <c r="L34" t="n">
-        <v>43.25</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>37.64</v>
+        <v>22.12</v>
       </c>
       <c r="K35" t="n">
-        <v>-49.7</v>
+        <v>-29.2</v>
       </c>
       <c r="L35" t="n">
-        <v>62.35</v>
+        <v>36.64</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>37.36</v>
+        <v>28.02</v>
       </c>
       <c r="K36" t="n">
-        <v>70.88</v>
+        <v>53.16</v>
       </c>
       <c r="L36" t="n">
-        <v>80.12</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>97.90000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-46.3</v>
+        <v>-34.73</v>
       </c>
       <c r="L37" t="n">
-        <v>108.3</v>
+        <v>81.22</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-146.58</v>
+        <v>-109.93</v>
       </c>
       <c r="K38" t="n">
-        <v>-50.97</v>
+        <v>-38.23</v>
       </c>
       <c r="L38" t="n">
-        <v>155.18</v>
+        <v>116.39</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>7.14</v>
+        <v>5.36</v>
       </c>
       <c r="K39" t="n">
-        <v>-129.91</v>
+        <v>-97.43000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>130.1</v>
+        <v>97.58</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-60.15</v>
+        <v>-5.42</v>
       </c>
       <c r="K40" t="n">
-        <v>-25.19</v>
+        <v>-2.27</v>
       </c>
       <c r="L40" t="n">
-        <v>65.20999999999999</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>136.51</v>
+        <v>102.38</v>
       </c>
       <c r="K41" t="n">
-        <v>207.67</v>
+        <v>155.75</v>
       </c>
       <c r="L41" t="n">
-        <v>248.52</v>
+        <v>186.39</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-89.47</v>
+        <v>-67.09999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>98.47</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>133.04</v>
+        <v>99.78</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-261.49</v>
+        <v>-165.5</v>
       </c>
       <c r="K43" t="n">
-        <v>60.77</v>
+        <v>38.46</v>
       </c>
       <c r="L43" t="n">
-        <v>268.46</v>
+        <v>169.91</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>55.11</v>
+        <v>41.33</v>
       </c>
       <c r="K44" t="n">
-        <v>68.7</v>
+        <v>51.52</v>
       </c>
       <c r="L44" t="n">
-        <v>88.06999999999999</v>
+        <v>66.05</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>16.1</v>
+        <v>12.08</v>
       </c>
       <c r="K45" t="n">
-        <v>-31.28</v>
+        <v>-23.46</v>
       </c>
       <c r="L45" t="n">
-        <v>35.18</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>36.57</v>
+        <v>27.42</v>
       </c>
       <c r="K46" t="n">
-        <v>31.55</v>
+        <v>23.66</v>
       </c>
       <c r="L46" t="n">
-        <v>48.29</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-6.64</v>
+        <v>-4.98</v>
       </c>
       <c r="K47" t="n">
-        <v>61.34</v>
+        <v>46.01</v>
       </c>
       <c r="L47" t="n">
-        <v>61.7</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>61.57</v>
+        <v>46.17</v>
       </c>
       <c r="K48" t="n">
-        <v>46.72</v>
+        <v>35.04</v>
       </c>
       <c r="L48" t="n">
-        <v>77.29000000000001</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-62.28</v>
+        <v>-46.71</v>
       </c>
       <c r="K49" t="n">
-        <v>11.14</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>63.27</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-49.59</v>
+        <v>-37.19</v>
       </c>
       <c r="K50" t="n">
-        <v>-186.47</v>
+        <v>-139.85</v>
       </c>
       <c r="L50" t="n">
-        <v>192.95</v>
+        <v>144.72</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>60.46</v>
+        <v>45.35</v>
       </c>
       <c r="K51" t="n">
-        <v>-35.82</v>
+        <v>-26.86</v>
       </c>
       <c r="L51" t="n">
-        <v>70.27</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>35.08</v>
+        <v>26.31</v>
       </c>
       <c r="K52" t="n">
-        <v>-108.24</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>113.78</v>
+        <v>85.34</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>135.75</v>
+        <v>101.81</v>
       </c>
       <c r="K53" t="n">
-        <v>-38.35</v>
+        <v>-28.76</v>
       </c>
       <c r="L53" t="n">
-        <v>141.07</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-103.74</v>
+        <v>-77.8</v>
       </c>
       <c r="K54" t="n">
-        <v>185.79</v>
+        <v>139.34</v>
       </c>
       <c r="L54" t="n">
-        <v>212.79</v>
+        <v>159.59</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>3.41</v>
+        <v>2.56</v>
       </c>
       <c r="K55" t="n">
-        <v>140.01</v>
+        <v>105</v>
       </c>
       <c r="L55" t="n">
-        <v>140.05</v>
+        <v>105.04</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>183.55</v>
+        <v>137.66</v>
       </c>
       <c r="K56" t="n">
-        <v>-186.64</v>
+        <v>-139.98</v>
       </c>
       <c r="L56" t="n">
-        <v>261.77</v>
+        <v>196.33</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-137.73</v>
+        <v>-103.3</v>
       </c>
       <c r="K57" t="n">
-        <v>98.62</v>
+        <v>73.97</v>
       </c>
       <c r="L57" t="n">
-        <v>169.4</v>
+        <v>127.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>259.4</v>
+        <v>194.55</v>
       </c>
       <c r="K58" t="n">
-        <v>-113.54</v>
+        <v>-85.16</v>
       </c>
       <c r="L58" t="n">
-        <v>283.16</v>
+        <v>212.37</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>49.08</v>
+        <v>36.81</v>
       </c>
       <c r="K59" t="n">
-        <v>70.09</v>
+        <v>52.57</v>
       </c>
       <c r="L59" t="n">
-        <v>85.56999999999999</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-45.69</v>
+        <v>-34.27</v>
       </c>
       <c r="K60" t="n">
-        <v>33.68</v>
+        <v>25.26</v>
       </c>
       <c r="L60" t="n">
-        <v>56.76</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-25.63</v>
+        <v>-19.22</v>
       </c>
       <c r="K61" t="n">
-        <v>30.34</v>
+        <v>22.75</v>
       </c>
       <c r="L61" t="n">
-        <v>39.72</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>3.35</v>
+        <v>2.51</v>
       </c>
       <c r="K62" t="n">
-        <v>-65.75</v>
+        <v>-49.32</v>
       </c>
       <c r="L62" t="n">
-        <v>65.84</v>
+        <v>49.38</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>79.38</v>
+        <v>59.54</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.68</v>
+        <v>-8.76</v>
       </c>
       <c r="L63" t="n">
-        <v>80.23999999999999</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-71.53</v>
+        <v>-53.65</v>
       </c>
       <c r="K64" t="n">
-        <v>-19.74</v>
+        <v>-14.8</v>
       </c>
       <c r="L64" t="n">
-        <v>74.2</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>63.51</v>
+        <v>47.63</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.72</v>
+        <v>-2.79</v>
       </c>
       <c r="L65" t="n">
-        <v>63.62</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>133.23</v>
+        <v>99.92</v>
       </c>
       <c r="K66" t="n">
-        <v>-76.73</v>
+        <v>-57.55</v>
       </c>
       <c r="L66" t="n">
-        <v>153.75</v>
+        <v>115.31</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>24.43</v>
+        <v>18.32</v>
       </c>
       <c r="K67" t="n">
-        <v>68.88</v>
+        <v>51.66</v>
       </c>
       <c r="L67" t="n">
-        <v>73.08</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-42.08</v>
+        <v>-31.56</v>
       </c>
       <c r="K68" t="n">
-        <v>108.97</v>
+        <v>81.73</v>
       </c>
       <c r="L68" t="n">
-        <v>116.81</v>
+        <v>87.61</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>15.06</v>
+        <v>11.3</v>
       </c>
       <c r="K69" t="n">
-        <v>-91.98999999999999</v>
+        <v>-68.98999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>93.22</v>
+        <v>69.91</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-154.96</v>
+        <v>-116.22</v>
       </c>
       <c r="K70" t="n">
-        <v>-168.06</v>
+        <v>-126.05</v>
       </c>
       <c r="L70" t="n">
-        <v>228.6</v>
+        <v>171.45</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>83.31999999999999</v>
+        <v>62.49</v>
       </c>
       <c r="K71" t="n">
-        <v>-128.3</v>
+        <v>-96.23</v>
       </c>
       <c r="L71" t="n">
-        <v>152.98</v>
+        <v>114.74</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>173.73</v>
+        <v>130.3</v>
       </c>
       <c r="K72" t="n">
-        <v>-217.14</v>
+        <v>-162.86</v>
       </c>
       <c r="L72" t="n">
-        <v>278.09</v>
+        <v>208.56</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>30.89</v>
+        <v>23.17</v>
       </c>
       <c r="K73" t="n">
-        <v>127.6</v>
+        <v>95.7</v>
       </c>
       <c r="L73" t="n">
-        <v>131.29</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>26.34</v>
+        <v>19.76</v>
       </c>
       <c r="K74" t="n">
-        <v>57.06</v>
+        <v>42.8</v>
       </c>
       <c r="L74" t="n">
-        <v>62.85</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>25.62</v>
+        <v>19.22</v>
       </c>
       <c r="K75" t="n">
-        <v>-46.2</v>
+        <v>-34.65</v>
       </c>
       <c r="L75" t="n">
-        <v>52.83</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>49.66</v>
+        <v>37.24</v>
       </c>
       <c r="K76" t="n">
-        <v>40.32</v>
+        <v>30.24</v>
       </c>
       <c r="L76" t="n">
-        <v>63.96</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-33.17</v>
+        <v>-24.88</v>
       </c>
       <c r="K77" t="n">
-        <v>-78.78</v>
+        <v>-59.09</v>
       </c>
       <c r="L77" t="n">
-        <v>85.48</v>
+        <v>64.11</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>4.66</v>
+        <v>3.49</v>
       </c>
       <c r="K78" t="n">
-        <v>68.79000000000001</v>
+        <v>51.59</v>
       </c>
       <c r="L78" t="n">
-        <v>68.94</v>
+        <v>51.71</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>57.23</v>
+        <v>42.92</v>
       </c>
       <c r="K79" t="n">
-        <v>57.93</v>
+        <v>43.44</v>
       </c>
       <c r="L79" t="n">
-        <v>81.43000000000001</v>
+        <v>61.07</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>76.92</v>
+        <v>57.69</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.65</v>
+        <v>-1.24</v>
       </c>
       <c r="L80" t="n">
-        <v>76.93000000000001</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.52</v>
+        <v>-16.89</v>
       </c>
       <c r="K81" t="n">
-        <v>-72.98</v>
+        <v>-54.74</v>
       </c>
       <c r="L81" t="n">
-        <v>76.38</v>
+        <v>57.28</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>76.36</v>
+        <v>57.27</v>
       </c>
       <c r="K82" t="n">
-        <v>-53.89</v>
+        <v>-40.42</v>
       </c>
       <c r="L82" t="n">
-        <v>93.45999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>38.83</v>
+        <v>29.13</v>
       </c>
       <c r="K83" t="n">
-        <v>-111.79</v>
+        <v>-83.84</v>
       </c>
       <c r="L83" t="n">
-        <v>118.34</v>
+        <v>88.76000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>71.81999999999999</v>
+        <v>53.87</v>
       </c>
       <c r="K84" t="n">
-        <v>-75.42</v>
+        <v>-56.57</v>
       </c>
       <c r="L84" t="n">
-        <v>104.15</v>
+        <v>78.11</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-96.77</v>
+        <v>-72.58</v>
       </c>
       <c r="K85" t="n">
-        <v>-122.1</v>
+        <v>-91.56999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>155.8</v>
+        <v>116.85</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-130.74</v>
+        <v>-98.05</v>
       </c>
       <c r="K86" t="n">
-        <v>-13.83</v>
+        <v>-10.37</v>
       </c>
       <c r="L86" t="n">
-        <v>131.47</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-45.72</v>
+        <v>-34.29</v>
       </c>
       <c r="K87" t="n">
-        <v>-173.22</v>
+        <v>-129.92</v>
       </c>
       <c r="L87" t="n">
-        <v>179.15</v>
+        <v>134.37</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-106.66</v>
+        <v>-80</v>
       </c>
       <c r="K88" t="n">
-        <v>202.2</v>
+        <v>151.65</v>
       </c>
       <c r="L88" t="n">
-        <v>228.6</v>
+        <v>171.45</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-56.57</v>
+        <v>-54.71</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="L14" t="n">
-        <v>56.61</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-44.25</v>
+        <v>-43.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.66</v>
+        <v>-14.46</v>
       </c>
       <c r="L15" t="n">
-        <v>46.62</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>17.75</v>
+        <v>18.46</v>
       </c>
       <c r="K16" t="n">
-        <v>23.04</v>
+        <v>23.95</v>
       </c>
       <c r="L16" t="n">
-        <v>29.08</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>23.83</v>
+        <v>25.99</v>
       </c>
       <c r="K17" t="n">
-        <v>-18.66</v>
+        <v>-20.36</v>
       </c>
       <c r="L17" t="n">
-        <v>30.27</v>
+        <v>33.02</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>9.25</v>
+        <v>9.31</v>
       </c>
       <c r="K18" t="n">
-        <v>50.19</v>
+        <v>50.55</v>
       </c>
       <c r="L18" t="n">
-        <v>51.03</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-34.31</v>
+        <v>-34.72</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.52</v>
+        <v>-34.92</v>
       </c>
       <c r="L19" t="n">
-        <v>48.67</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>30.12</v>
+        <v>28.99</v>
       </c>
       <c r="K20" t="n">
-        <v>-112.05</v>
+        <v>-107.86</v>
       </c>
       <c r="L20" t="n">
-        <v>116.03</v>
+        <v>111.69</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-80.31999999999999</v>
+        <v>-78.19</v>
       </c>
       <c r="K21" t="n">
-        <v>-66.17</v>
+        <v>-64.41</v>
       </c>
       <c r="L21" t="n">
-        <v>104.07</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-61.54</v>
+        <v>-60.01</v>
       </c>
       <c r="K22" t="n">
-        <v>80.22</v>
+        <v>78.23</v>
       </c>
       <c r="L22" t="n">
-        <v>101.11</v>
+        <v>98.59</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>92.84</v>
+        <v>93.44</v>
       </c>
       <c r="K23" t="n">
-        <v>-39.83</v>
+        <v>-40.08</v>
       </c>
       <c r="L23" t="n">
-        <v>101.02</v>
+        <v>101.67</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>10.43</v>
+        <v>10.28</v>
       </c>
       <c r="K24" t="n">
-        <v>-121.87</v>
+        <v>-120.13</v>
       </c>
       <c r="L24" t="n">
-        <v>122.32</v>
+        <v>120.57</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>83.92</v>
+        <v>86.2</v>
       </c>
       <c r="K25" t="n">
-        <v>23.09</v>
+        <v>23.72</v>
       </c>
       <c r="L25" t="n">
-        <v>87.03</v>
+        <v>89.41</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>80.38</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>214.12</v>
+        <v>209.98</v>
       </c>
       <c r="L26" t="n">
-        <v>228.71</v>
+        <v>224.28</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-98.2</v>
+        <v>-106.89</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.54</v>
+        <v>-7.12</v>
       </c>
       <c r="L27" t="n">
-        <v>98.42</v>
+        <v>107.12</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>123.78</v>
+        <v>120.98</v>
       </c>
       <c r="K28" t="n">
-        <v>146.37</v>
+        <v>143.06</v>
       </c>
       <c r="L28" t="n">
-        <v>191.69</v>
+        <v>187.36</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>49.24</v>
+        <v>47.71</v>
       </c>
       <c r="K29" t="n">
-        <v>-19.13</v>
+        <v>-18.54</v>
       </c>
       <c r="L29" t="n">
-        <v>52.83</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.93</v>
+        <v>-14.87</v>
       </c>
       <c r="K30" t="n">
-        <v>40.63</v>
+        <v>40.49</v>
       </c>
       <c r="L30" t="n">
-        <v>43.28</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>32.63</v>
+        <v>31.52</v>
       </c>
       <c r="K31" t="n">
-        <v>-43.96</v>
+        <v>-42.47</v>
       </c>
       <c r="L31" t="n">
-        <v>54.74</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-6.94</v>
+        <v>-7.25</v>
       </c>
       <c r="K32" t="n">
-        <v>-36.67</v>
+        <v>-38.32</v>
       </c>
       <c r="L32" t="n">
-        <v>37.32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>23.88</v>
+        <v>25.94</v>
       </c>
       <c r="K33" t="n">
-        <v>-23.74</v>
+        <v>-25.79</v>
       </c>
       <c r="L33" t="n">
-        <v>33.67</v>
+        <v>36.58</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-32.06</v>
+        <v>-32.26</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.99</v>
+        <v>-5.02</v>
       </c>
       <c r="L34" t="n">
-        <v>32.44</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>22.12</v>
+        <v>21.6</v>
       </c>
       <c r="K35" t="n">
-        <v>-29.2</v>
+        <v>-28.52</v>
       </c>
       <c r="L35" t="n">
-        <v>36.64</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>28.02</v>
+        <v>29.16</v>
       </c>
       <c r="K36" t="n">
-        <v>53.16</v>
+        <v>55.32</v>
       </c>
       <c r="L36" t="n">
-        <v>60.09</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>73.43000000000001</v>
+        <v>74.09</v>
       </c>
       <c r="K37" t="n">
-        <v>-34.73</v>
+        <v>-35.04</v>
       </c>
       <c r="L37" t="n">
-        <v>81.22</v>
+        <v>81.95999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-109.93</v>
+        <v>-109.88</v>
       </c>
       <c r="K38" t="n">
-        <v>-38.23</v>
+        <v>-38.21</v>
       </c>
       <c r="L38" t="n">
-        <v>116.39</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>5.36</v>
+        <v>5.49</v>
       </c>
       <c r="K39" t="n">
-        <v>-97.43000000000001</v>
+        <v>-99.92</v>
       </c>
       <c r="L39" t="n">
-        <v>97.58</v>
+        <v>100.07</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.42</v>
+        <v>-5.36</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.27</v>
+        <v>-2.25</v>
       </c>
       <c r="L40" t="n">
-        <v>5.88</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>102.38</v>
+        <v>100.9</v>
       </c>
       <c r="K41" t="n">
-        <v>155.75</v>
+        <v>153.49</v>
       </c>
       <c r="L41" t="n">
-        <v>186.39</v>
+        <v>183.68</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-67.09999999999999</v>
+        <v>-71.75</v>
       </c>
       <c r="K42" t="n">
-        <v>73.84999999999999</v>
+        <v>78.97</v>
       </c>
       <c r="L42" t="n">
-        <v>99.78</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-165.5</v>
+        <v>-166.96</v>
       </c>
       <c r="K43" t="n">
-        <v>38.46</v>
+        <v>38.8</v>
       </c>
       <c r="L43" t="n">
-        <v>169.91</v>
+        <v>171.4</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>41.33</v>
+        <v>39.51</v>
       </c>
       <c r="K44" t="n">
-        <v>51.52</v>
+        <v>49.25</v>
       </c>
       <c r="L44" t="n">
-        <v>66.05</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>12.08</v>
+        <v>12.61</v>
       </c>
       <c r="K45" t="n">
-        <v>-23.46</v>
+        <v>-24.5</v>
       </c>
       <c r="L45" t="n">
-        <v>26.39</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>27.42</v>
+        <v>27.74</v>
       </c>
       <c r="K46" t="n">
-        <v>23.66</v>
+        <v>23.94</v>
       </c>
       <c r="L46" t="n">
-        <v>36.22</v>
+        <v>36.64</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.98</v>
+        <v>-5.06</v>
       </c>
       <c r="K47" t="n">
-        <v>46.01</v>
+        <v>46.74</v>
       </c>
       <c r="L47" t="n">
-        <v>46.28</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>46.17</v>
+        <v>46.15</v>
       </c>
       <c r="K48" t="n">
-        <v>35.04</v>
+        <v>35.03</v>
       </c>
       <c r="L48" t="n">
-        <v>57.96</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-46.71</v>
+        <v>-47.68</v>
       </c>
       <c r="K49" t="n">
-        <v>8.359999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>47.45</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-37.19</v>
+        <v>-35.37</v>
       </c>
       <c r="K50" t="n">
-        <v>-139.85</v>
+        <v>-133.01</v>
       </c>
       <c r="L50" t="n">
-        <v>144.72</v>
+        <v>137.63</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>45.35</v>
+        <v>48.73</v>
       </c>
       <c r="K51" t="n">
-        <v>-26.86</v>
+        <v>-28.86</v>
       </c>
       <c r="L51" t="n">
-        <v>52.7</v>
+        <v>56.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>26.31</v>
+        <v>26.29</v>
       </c>
       <c r="K52" t="n">
-        <v>-81.18000000000001</v>
+        <v>-81.09999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>85.34</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>101.81</v>
+        <v>101.65</v>
       </c>
       <c r="K53" t="n">
-        <v>-28.76</v>
+        <v>-28.72</v>
       </c>
       <c r="L53" t="n">
-        <v>105.8</v>
+        <v>105.63</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-77.8</v>
+        <v>-75.16</v>
       </c>
       <c r="K54" t="n">
-        <v>139.34</v>
+        <v>134.62</v>
       </c>
       <c r="L54" t="n">
-        <v>159.59</v>
+        <v>154.18</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="K55" t="n">
-        <v>105</v>
+        <v>105.65</v>
       </c>
       <c r="L55" t="n">
-        <v>105.04</v>
+        <v>105.68</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>137.66</v>
+        <v>135.7</v>
       </c>
       <c r="K56" t="n">
-        <v>-139.98</v>
+        <v>-137.99</v>
       </c>
       <c r="L56" t="n">
-        <v>196.33</v>
+        <v>193.54</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-103.3</v>
+        <v>-106.61</v>
       </c>
       <c r="K57" t="n">
-        <v>73.97</v>
+        <v>76.34</v>
       </c>
       <c r="L57" t="n">
-        <v>127.05</v>
+        <v>131.12</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>194.55</v>
+        <v>188.38</v>
       </c>
       <c r="K58" t="n">
-        <v>-85.16</v>
+        <v>-82.45999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>212.37</v>
+        <v>205.64</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>36.81</v>
+        <v>35.05</v>
       </c>
       <c r="K59" t="n">
-        <v>52.57</v>
+        <v>50.05</v>
       </c>
       <c r="L59" t="n">
-        <v>64.18000000000001</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-34.27</v>
+        <v>-33.98</v>
       </c>
       <c r="K60" t="n">
-        <v>25.26</v>
+        <v>25.05</v>
       </c>
       <c r="L60" t="n">
-        <v>42.57</v>
+        <v>42.21</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-19.22</v>
+        <v>-20.39</v>
       </c>
       <c r="K61" t="n">
-        <v>22.75</v>
+        <v>24.14</v>
       </c>
       <c r="L61" t="n">
-        <v>29.79</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="K62" t="n">
-        <v>-49.32</v>
+        <v>-50.32</v>
       </c>
       <c r="L62" t="n">
-        <v>49.38</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>59.54</v>
+        <v>59.07</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.76</v>
+        <v>-8.69</v>
       </c>
       <c r="L63" t="n">
-        <v>60.18</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-53.65</v>
+        <v>-53.17</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.8</v>
+        <v>-14.67</v>
       </c>
       <c r="L64" t="n">
-        <v>55.65</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>47.63</v>
+        <v>51.97</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.79</v>
+        <v>-3.05</v>
       </c>
       <c r="L65" t="n">
-        <v>47.71</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>99.92</v>
+        <v>96.89</v>
       </c>
       <c r="K66" t="n">
-        <v>-57.55</v>
+        <v>-55.8</v>
       </c>
       <c r="L66" t="n">
-        <v>115.31</v>
+        <v>111.81</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>18.32</v>
+        <v>19.73</v>
       </c>
       <c r="K67" t="n">
-        <v>51.66</v>
+        <v>55.64</v>
       </c>
       <c r="L67" t="n">
-        <v>54.81</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-31.56</v>
+        <v>-32.67</v>
       </c>
       <c r="K68" t="n">
-        <v>81.73</v>
+        <v>84.61</v>
       </c>
       <c r="L68" t="n">
-        <v>87.61</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>11.3</v>
+        <v>12.08</v>
       </c>
       <c r="K69" t="n">
-        <v>-68.98999999999999</v>
+        <v>-73.77</v>
       </c>
       <c r="L69" t="n">
-        <v>69.91</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-116.22</v>
+        <v>-111.03</v>
       </c>
       <c r="K70" t="n">
-        <v>-126.05</v>
+        <v>-120.42</v>
       </c>
       <c r="L70" t="n">
-        <v>171.45</v>
+        <v>163.8</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>62.49</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-96.23</v>
+        <v>-103.19</v>
       </c>
       <c r="L71" t="n">
-        <v>114.74</v>
+        <v>123.04</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>130.3</v>
+        <v>126.57</v>
       </c>
       <c r="K72" t="n">
-        <v>-162.86</v>
+        <v>-158.19</v>
       </c>
       <c r="L72" t="n">
-        <v>208.56</v>
+        <v>202.59</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>23.17</v>
+        <v>24.7</v>
       </c>
       <c r="K73" t="n">
-        <v>95.7</v>
+        <v>102.01</v>
       </c>
       <c r="L73" t="n">
-        <v>98.47</v>
+        <v>104.95</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>19.76</v>
+        <v>19.49</v>
       </c>
       <c r="K74" t="n">
-        <v>42.8</v>
+        <v>42.23</v>
       </c>
       <c r="L74" t="n">
-        <v>47.14</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>19.22</v>
+        <v>19.42</v>
       </c>
       <c r="K75" t="n">
-        <v>-34.65</v>
+        <v>-35.01</v>
       </c>
       <c r="L75" t="n">
-        <v>39.62</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>37.24</v>
+        <v>36.74</v>
       </c>
       <c r="K76" t="n">
-        <v>30.24</v>
+        <v>29.82</v>
       </c>
       <c r="L76" t="n">
-        <v>47.97</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-24.88</v>
+        <v>-24.4</v>
       </c>
       <c r="K77" t="n">
-        <v>-59.09</v>
+        <v>-57.96</v>
       </c>
       <c r="L77" t="n">
-        <v>64.11</v>
+        <v>62.88</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="K78" t="n">
-        <v>51.59</v>
+        <v>52.46</v>
       </c>
       <c r="L78" t="n">
-        <v>51.71</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>42.92</v>
+        <v>42.7</v>
       </c>
       <c r="K79" t="n">
-        <v>43.44</v>
+        <v>43.22</v>
       </c>
       <c r="L79" t="n">
-        <v>61.07</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>57.69</v>
+        <v>60.68</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.24</v>
+        <v>-1.3</v>
       </c>
       <c r="L80" t="n">
-        <v>57.7</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.89</v>
+        <v>-17.7</v>
       </c>
       <c r="K81" t="n">
-        <v>-54.74</v>
+        <v>-57.36</v>
       </c>
       <c r="L81" t="n">
-        <v>57.28</v>
+        <v>60.03</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>57.27</v>
+        <v>58.76</v>
       </c>
       <c r="K82" t="n">
-        <v>-40.42</v>
+        <v>-41.47</v>
       </c>
       <c r="L82" t="n">
-        <v>70.09999999999999</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>29.13</v>
+        <v>30.05</v>
       </c>
       <c r="K83" t="n">
-        <v>-83.84</v>
+        <v>-86.5</v>
       </c>
       <c r="L83" t="n">
-        <v>88.76000000000001</v>
+        <v>91.56999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>53.87</v>
+        <v>56.38</v>
       </c>
       <c r="K84" t="n">
-        <v>-56.57</v>
+        <v>-59.2</v>
       </c>
       <c r="L84" t="n">
-        <v>78.11</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-72.58</v>
+        <v>-71.88</v>
       </c>
       <c r="K85" t="n">
-        <v>-91.56999999999999</v>
+        <v>-90.7</v>
       </c>
       <c r="L85" t="n">
-        <v>116.85</v>
+        <v>115.73</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-98.05</v>
+        <v>-106.98</v>
       </c>
       <c r="K86" t="n">
-        <v>-10.37</v>
+        <v>-11.31</v>
       </c>
       <c r="L86" t="n">
-        <v>98.59999999999999</v>
+        <v>107.57</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-34.29</v>
+        <v>-35.57</v>
       </c>
       <c r="K87" t="n">
-        <v>-129.92</v>
+        <v>-134.77</v>
       </c>
       <c r="L87" t="n">
-        <v>134.37</v>
+        <v>139.39</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-80</v>
+        <v>-80.65000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>151.65</v>
+        <v>152.89</v>
       </c>
       <c r="L88" t="n">
-        <v>171.45</v>
+        <v>172.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-54.71</v>
+        <v>-52.57</v>
       </c>
       <c r="K14" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="L14" t="n">
-        <v>54.74</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-43.66</v>
+        <v>-42.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.46</v>
+        <v>-14.24</v>
       </c>
       <c r="L15" t="n">
-        <v>45.99</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>18.46</v>
+        <v>19.27</v>
       </c>
       <c r="K16" t="n">
-        <v>23.95</v>
+        <v>25</v>
       </c>
       <c r="L16" t="n">
-        <v>30.24</v>
+        <v>31.56</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>25.99</v>
+        <v>28.47</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.36</v>
+        <v>-22.29</v>
       </c>
       <c r="L17" t="n">
-        <v>33.02</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>9.31</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>50.55</v>
+        <v>50.95</v>
       </c>
       <c r="L18" t="n">
-        <v>51.4</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-34.72</v>
+        <v>-35.18</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.92</v>
+        <v>-35.39</v>
       </c>
       <c r="L19" t="n">
-        <v>49.24</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>28.99</v>
+        <v>27.7</v>
       </c>
       <c r="K20" t="n">
-        <v>-107.86</v>
+        <v>-103.08</v>
       </c>
       <c r="L20" t="n">
-        <v>111.69</v>
+        <v>106.73</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-78.19</v>
+        <v>-75.75</v>
       </c>
       <c r="K21" t="n">
-        <v>-64.41</v>
+        <v>-62.4</v>
       </c>
       <c r="L21" t="n">
-        <v>101.3</v>
+        <v>98.15000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-60.01</v>
+        <v>-58.26</v>
       </c>
       <c r="K22" t="n">
-        <v>78.23</v>
+        <v>75.95</v>
       </c>
       <c r="L22" t="n">
-        <v>98.59</v>
+        <v>95.72</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>93.44</v>
+        <v>94.12</v>
       </c>
       <c r="K23" t="n">
-        <v>-40.08</v>
+        <v>-40.38</v>
       </c>
       <c r="L23" t="n">
-        <v>101.67</v>
+        <v>102.42</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>10.28</v>
+        <v>10.11</v>
       </c>
       <c r="K24" t="n">
-        <v>-120.13</v>
+        <v>-118.13</v>
       </c>
       <c r="L24" t="n">
-        <v>120.57</v>
+        <v>118.57</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>86.2</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>23.72</v>
+        <v>24.44</v>
       </c>
       <c r="L25" t="n">
-        <v>89.41</v>
+        <v>92.12</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>78.81999999999999</v>
+        <v>77.05</v>
       </c>
       <c r="K26" t="n">
-        <v>209.98</v>
+        <v>205.24</v>
       </c>
       <c r="L26" t="n">
-        <v>224.28</v>
+        <v>219.23</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-106.89</v>
+        <v>-116.82</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.12</v>
+        <v>-7.78</v>
       </c>
       <c r="L27" t="n">
-        <v>107.12</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>120.98</v>
+        <v>117.79</v>
       </c>
       <c r="K28" t="n">
-        <v>143.06</v>
+        <v>139.29</v>
       </c>
       <c r="L28" t="n">
-        <v>187.36</v>
+        <v>182.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>47.71</v>
+        <v>45.95</v>
       </c>
       <c r="K29" t="n">
-        <v>-18.54</v>
+        <v>-17.86</v>
       </c>
       <c r="L29" t="n">
-        <v>51.18</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.87</v>
+        <v>-14.82</v>
       </c>
       <c r="K30" t="n">
-        <v>40.49</v>
+        <v>40.32</v>
       </c>
       <c r="L30" t="n">
-        <v>43.13</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>31.52</v>
+        <v>30.26</v>
       </c>
       <c r="K31" t="n">
-        <v>-42.47</v>
+        <v>-40.77</v>
       </c>
       <c r="L31" t="n">
-        <v>52.89</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.25</v>
+        <v>-7.6</v>
       </c>
       <c r="K32" t="n">
-        <v>-38.32</v>
+        <v>-40.19</v>
       </c>
       <c r="L32" t="n">
-        <v>39</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>25.94</v>
+        <v>28.3</v>
       </c>
       <c r="K33" t="n">
-        <v>-25.79</v>
+        <v>-28.13</v>
       </c>
       <c r="L33" t="n">
-        <v>36.58</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-32.26</v>
+        <v>-35.5</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.02</v>
+        <v>-5.52</v>
       </c>
       <c r="L34" t="n">
-        <v>32.65</v>
+        <v>35.92</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>21.6</v>
+        <v>23.64</v>
       </c>
       <c r="K35" t="n">
-        <v>-28.52</v>
+        <v>-31.21</v>
       </c>
       <c r="L35" t="n">
-        <v>35.78</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>29.16</v>
+        <v>30.46</v>
       </c>
       <c r="K36" t="n">
-        <v>55.32</v>
+        <v>57.79</v>
       </c>
       <c r="L36" t="n">
-        <v>62.53</v>
+        <v>65.33</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>74.09</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-35.04</v>
+        <v>-35.4</v>
       </c>
       <c r="L37" t="n">
-        <v>81.95999999999999</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-109.88</v>
+        <v>-109.82</v>
       </c>
       <c r="K38" t="n">
-        <v>-38.21</v>
+        <v>-38.19</v>
       </c>
       <c r="L38" t="n">
-        <v>116.33</v>
+        <v>116.27</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
       <c r="K39" t="n">
-        <v>-99.92</v>
+        <v>-102.77</v>
       </c>
       <c r="L39" t="n">
-        <v>100.07</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.36</v>
+        <v>-5.6</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.25</v>
+        <v>-2.34</v>
       </c>
       <c r="L40" t="n">
-        <v>5.81</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>100.9</v>
+        <v>99.2</v>
       </c>
       <c r="K41" t="n">
-        <v>153.49</v>
+        <v>150.91</v>
       </c>
       <c r="L41" t="n">
-        <v>183.68</v>
+        <v>180.59</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-71.75</v>
+        <v>-77.06999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>78.97</v>
+        <v>84.81</v>
       </c>
       <c r="L42" t="n">
-        <v>106.7</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-166.96</v>
+        <v>-168.62</v>
       </c>
       <c r="K43" t="n">
-        <v>38.8</v>
+        <v>39.18</v>
       </c>
       <c r="L43" t="n">
-        <v>171.4</v>
+        <v>173.11</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>39.51</v>
+        <v>37.42</v>
       </c>
       <c r="K44" t="n">
-        <v>49.25</v>
+        <v>46.65</v>
       </c>
       <c r="L44" t="n">
-        <v>63.14</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>12.61</v>
+        <v>13.22</v>
       </c>
       <c r="K45" t="n">
-        <v>-24.5</v>
+        <v>-25.68</v>
       </c>
       <c r="L45" t="n">
-        <v>27.55</v>
+        <v>28.89</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>27.74</v>
+        <v>28.11</v>
       </c>
       <c r="K46" t="n">
-        <v>23.94</v>
+        <v>24.25</v>
       </c>
       <c r="L46" t="n">
-        <v>36.64</v>
+        <v>37.12</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-5.06</v>
+        <v>-5.15</v>
       </c>
       <c r="K47" t="n">
-        <v>46.74</v>
+        <v>47.58</v>
       </c>
       <c r="L47" t="n">
-        <v>47.01</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>46.15</v>
+        <v>46.13</v>
       </c>
       <c r="K48" t="n">
-        <v>35.03</v>
+        <v>35.01</v>
       </c>
       <c r="L48" t="n">
-        <v>57.94</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-47.68</v>
+        <v>-48.8</v>
       </c>
       <c r="K49" t="n">
-        <v>8.529999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="L49" t="n">
-        <v>48.44</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-35.37</v>
+        <v>-33.29</v>
       </c>
       <c r="K50" t="n">
-        <v>-133.01</v>
+        <v>-125.19</v>
       </c>
       <c r="L50" t="n">
-        <v>137.63</v>
+        <v>129.54</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>48.73</v>
+        <v>52.59</v>
       </c>
       <c r="K51" t="n">
-        <v>-28.86</v>
+        <v>-31.15</v>
       </c>
       <c r="L51" t="n">
-        <v>56.63</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>26.29</v>
+        <v>26.26</v>
       </c>
       <c r="K52" t="n">
-        <v>-81.09999999999999</v>
+        <v>-81.01000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>85.26000000000001</v>
+        <v>85.16</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>101.65</v>
+        <v>101.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-28.72</v>
+        <v>-28.67</v>
       </c>
       <c r="L53" t="n">
-        <v>105.63</v>
+        <v>105.44</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-75.16</v>
+        <v>-72.15000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>134.62</v>
+        <v>129.22</v>
       </c>
       <c r="L54" t="n">
-        <v>154.18</v>
+        <v>147.99</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="K55" t="n">
-        <v>105.65</v>
+        <v>106.38</v>
       </c>
       <c r="L55" t="n">
-        <v>105.68</v>
+        <v>106.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>135.7</v>
+        <v>133.46</v>
       </c>
       <c r="K56" t="n">
-        <v>-137.99</v>
+        <v>-135.71</v>
       </c>
       <c r="L56" t="n">
-        <v>193.54</v>
+        <v>190.34</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-106.61</v>
+        <v>-110.39</v>
       </c>
       <c r="K57" t="n">
-        <v>76.34</v>
+        <v>79.05</v>
       </c>
       <c r="L57" t="n">
-        <v>131.12</v>
+        <v>135.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>188.38</v>
+        <v>181.34</v>
       </c>
       <c r="K58" t="n">
-        <v>-82.45999999999999</v>
+        <v>-79.37</v>
       </c>
       <c r="L58" t="n">
-        <v>205.64</v>
+        <v>197.95</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>35.05</v>
+        <v>33.03</v>
       </c>
       <c r="K59" t="n">
-        <v>50.05</v>
+        <v>47.16</v>
       </c>
       <c r="L59" t="n">
-        <v>61.1</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-33.98</v>
+        <v>-33.65</v>
       </c>
       <c r="K60" t="n">
-        <v>25.05</v>
+        <v>24.81</v>
       </c>
       <c r="L60" t="n">
-        <v>42.21</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.39</v>
+        <v>-21.73</v>
       </c>
       <c r="K61" t="n">
-        <v>24.14</v>
+        <v>25.72</v>
       </c>
       <c r="L61" t="n">
-        <v>31.6</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="K62" t="n">
-        <v>-50.32</v>
+        <v>-51.46</v>
       </c>
       <c r="L62" t="n">
-        <v>50.38</v>
+        <v>51.53</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>59.07</v>
+        <v>58.54</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.69</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>59.7</v>
+        <v>59.17</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-53.17</v>
+        <v>-52.63</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.67</v>
+        <v>-14.52</v>
       </c>
       <c r="L64" t="n">
-        <v>55.16</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>51.97</v>
+        <v>56.92</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.05</v>
+        <v>-3.34</v>
       </c>
       <c r="L65" t="n">
-        <v>52.06</v>
+        <v>57.02</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>96.89</v>
+        <v>93.41</v>
       </c>
       <c r="K66" t="n">
-        <v>-55.8</v>
+        <v>-53.8</v>
       </c>
       <c r="L66" t="n">
-        <v>111.81</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>19.73</v>
+        <v>21.34</v>
       </c>
       <c r="K67" t="n">
-        <v>55.64</v>
+        <v>60.18</v>
       </c>
       <c r="L67" t="n">
-        <v>59.03</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-32.67</v>
+        <v>-33.95</v>
       </c>
       <c r="K68" t="n">
-        <v>84.61</v>
+        <v>87.91</v>
       </c>
       <c r="L68" t="n">
-        <v>90.7</v>
+        <v>94.23999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>12.08</v>
+        <v>12.97</v>
       </c>
       <c r="K69" t="n">
-        <v>-73.77</v>
+        <v>-79.22</v>
       </c>
       <c r="L69" t="n">
-        <v>74.75</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-111.03</v>
+        <v>-105.1</v>
       </c>
       <c r="K70" t="n">
-        <v>-120.42</v>
+        <v>-113.99</v>
       </c>
       <c r="L70" t="n">
-        <v>163.8</v>
+        <v>155.05</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>67.01000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="K71" t="n">
-        <v>-103.19</v>
+        <v>-111.14</v>
       </c>
       <c r="L71" t="n">
-        <v>123.04</v>
+        <v>132.52</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>126.57</v>
+        <v>122.3</v>
       </c>
       <c r="K72" t="n">
-        <v>-158.19</v>
+        <v>-152.87</v>
       </c>
       <c r="L72" t="n">
-        <v>202.59</v>
+        <v>195.77</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>24.7</v>
+        <v>26.44</v>
       </c>
       <c r="K73" t="n">
-        <v>102.01</v>
+        <v>109.21</v>
       </c>
       <c r="L73" t="n">
-        <v>104.95</v>
+        <v>112.37</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>19.49</v>
+        <v>19.19</v>
       </c>
       <c r="K74" t="n">
-        <v>42.23</v>
+        <v>41.57</v>
       </c>
       <c r="L74" t="n">
-        <v>46.51</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>19.42</v>
+        <v>19.65</v>
       </c>
       <c r="K75" t="n">
-        <v>-35.01</v>
+        <v>-35.43</v>
       </c>
       <c r="L75" t="n">
-        <v>40.04</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>36.74</v>
+        <v>36.15</v>
       </c>
       <c r="K76" t="n">
-        <v>29.82</v>
+        <v>29.35</v>
       </c>
       <c r="L76" t="n">
-        <v>47.32</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-24.4</v>
+        <v>-23.85</v>
       </c>
       <c r="K77" t="n">
-        <v>-57.96</v>
+        <v>-56.66</v>
       </c>
       <c r="L77" t="n">
-        <v>62.88</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="K78" t="n">
-        <v>52.46</v>
+        <v>53.46</v>
       </c>
       <c r="L78" t="n">
-        <v>52.58</v>
+        <v>53.58</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>42.7</v>
+        <v>42.44</v>
       </c>
       <c r="K79" t="n">
-        <v>43.22</v>
+        <v>42.96</v>
       </c>
       <c r="L79" t="n">
-        <v>60.75</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>60.68</v>
+        <v>64.11</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.3</v>
+        <v>-1.37</v>
       </c>
       <c r="L80" t="n">
-        <v>60.7</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.7</v>
+        <v>-18.63</v>
       </c>
       <c r="K81" t="n">
-        <v>-57.36</v>
+        <v>-60.35</v>
       </c>
       <c r="L81" t="n">
-        <v>60.03</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>58.76</v>
+        <v>60.47</v>
       </c>
       <c r="K82" t="n">
-        <v>-41.47</v>
+        <v>-42.67</v>
       </c>
       <c r="L82" t="n">
-        <v>71.92</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>30.05</v>
+        <v>31.1</v>
       </c>
       <c r="K83" t="n">
-        <v>-86.5</v>
+        <v>-89.53</v>
       </c>
       <c r="L83" t="n">
-        <v>91.56999999999999</v>
+        <v>94.78</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>56.38</v>
+        <v>59.25</v>
       </c>
       <c r="K84" t="n">
-        <v>-59.2</v>
+        <v>-62.22</v>
       </c>
       <c r="L84" t="n">
-        <v>81.75</v>
+        <v>85.92</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-71.88</v>
+        <v>-71.09</v>
       </c>
       <c r="K85" t="n">
-        <v>-90.7</v>
+        <v>-89.69</v>
       </c>
       <c r="L85" t="n">
-        <v>115.73</v>
+        <v>114.45</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-106.98</v>
+        <v>-117.17</v>
       </c>
       <c r="K86" t="n">
-        <v>-11.31</v>
+        <v>-12.39</v>
       </c>
       <c r="L86" t="n">
-        <v>107.57</v>
+        <v>117.83</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-35.57</v>
+        <v>-37.03</v>
       </c>
       <c r="K87" t="n">
-        <v>-134.77</v>
+        <v>-140.32</v>
       </c>
       <c r="L87" t="n">
-        <v>139.39</v>
+        <v>145.13</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-80.65000000000001</v>
+        <v>-81.40000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>152.89</v>
+        <v>154.31</v>
       </c>
       <c r="L88" t="n">
-        <v>172.86</v>
+        <v>174.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="F14" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="G14" t="n">
-        <v>165.7</v>
+        <v>160.4</v>
       </c>
       <c r="H14" t="n">
-        <v>87.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-52.57</v>
+        <v>-63.27</v>
       </c>
       <c r="K14" t="n">
-        <v>1.86</v>
+        <v>16.61</v>
       </c>
       <c r="L14" t="n">
-        <v>52.6</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:34:33</t>
+          <t>04:34:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="F15" t="n">
-        <v>5.81</v>
+        <v>1.46</v>
       </c>
       <c r="G15" t="n">
-        <v>164.5</v>
+        <v>169.1</v>
       </c>
       <c r="H15" t="n">
-        <v>79.8</v>
+        <v>81.2</v>
       </c>
       <c r="I15" t="n">
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.98</v>
+        <v>53.53</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.24</v>
+        <v>14.09</v>
       </c>
       <c r="L15" t="n">
-        <v>45.27</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:36:09</t>
+          <t>04:36:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.91</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="n">
-        <v>6.01</v>
+        <v>6.67</v>
       </c>
       <c r="G16" t="n">
-        <v>176.3</v>
+        <v>165.9</v>
       </c>
       <c r="H16" t="n">
-        <v>91.5</v>
+        <v>86.7</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>19.27</v>
+        <v>30.91</v>
       </c>
       <c r="K16" t="n">
-        <v>25</v>
+        <v>1.08</v>
       </c>
       <c r="L16" t="n">
-        <v>31.56</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:41:05</t>
+          <t>04:41:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="F17" t="n">
-        <v>5.88</v>
+        <v>5.64</v>
       </c>
       <c r="G17" t="n">
-        <v>161.1</v>
+        <v>169.3</v>
       </c>
       <c r="H17" t="n">
-        <v>87.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>28.47</v>
+        <v>-3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>-22.29</v>
+        <v>50.51</v>
       </c>
       <c r="L17" t="n">
-        <v>36.15</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:43:43</t>
+          <t>04:43:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="F18" t="n">
-        <v>5.92</v>
+        <v>6.67</v>
       </c>
       <c r="G18" t="n">
-        <v>160.7</v>
+        <v>164.6</v>
       </c>
       <c r="H18" t="n">
-        <v>95.2</v>
+        <v>80</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>9.390000000000001</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>50.95</v>
+        <v>66.2</v>
       </c>
       <c r="L18" t="n">
-        <v>51.81</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:45:19</t>
+          <t>04:45:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.87</v>
+        <v>1.32</v>
       </c>
       <c r="F19" t="n">
-        <v>6.14</v>
+        <v>3.48</v>
       </c>
       <c r="G19" t="n">
-        <v>170.9</v>
+        <v>168.5</v>
       </c>
       <c r="H19" t="n">
-        <v>92</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-35.18</v>
+        <v>31.81</v>
       </c>
       <c r="K19" t="n">
-        <v>-35.39</v>
+        <v>55.71</v>
       </c>
       <c r="L19" t="n">
-        <v>49.9</v>
+        <v>64.15000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:49:15</t>
+          <t>04:50:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.96</v>
+        <v>1.23</v>
       </c>
       <c r="F20" t="n">
-        <v>6.12</v>
+        <v>1.53</v>
       </c>
       <c r="G20" t="n">
-        <v>164.4</v>
+        <v>157.5</v>
       </c>
       <c r="H20" t="n">
-        <v>92.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="I20" t="n">
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>27.7</v>
+        <v>24.88</v>
       </c>
       <c r="K20" t="n">
-        <v>-103.08</v>
+        <v>-76.73</v>
       </c>
       <c r="L20" t="n">
-        <v>106.73</v>
+        <v>80.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:50:44</t>
+          <t>04:51:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.23</v>
+        <v>0.97</v>
       </c>
       <c r="F21" t="n">
-        <v>5.37</v>
+        <v>1.27</v>
       </c>
       <c r="G21" t="n">
-        <v>155.2</v>
+        <v>149.4</v>
       </c>
       <c r="H21" t="n">
-        <v>87.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-75.75</v>
+        <v>-44.84</v>
       </c>
       <c r="K21" t="n">
-        <v>-62.4</v>
+        <v>-98.67</v>
       </c>
       <c r="L21" t="n">
-        <v>98.15000000000001</v>
+        <v>108.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:52:39</t>
+          <t>04:53:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.99</v>
+        <v>1.1</v>
       </c>
       <c r="F22" t="n">
-        <v>5.05</v>
+        <v>6.67</v>
       </c>
       <c r="G22" t="n">
-        <v>153.7</v>
+        <v>149.1</v>
       </c>
       <c r="H22" t="n">
-        <v>88.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-58.26</v>
+        <v>36.49</v>
       </c>
       <c r="K22" t="n">
-        <v>75.95</v>
+        <v>-90.41</v>
       </c>
       <c r="L22" t="n">
-        <v>95.72</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:56:32</t>
+          <t>04:59:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="F23" t="n">
-        <v>6.43</v>
+        <v>6.67</v>
       </c>
       <c r="G23" t="n">
-        <v>159</v>
+        <v>154.9</v>
       </c>
       <c r="H23" t="n">
-        <v>86.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>94.12</v>
+        <v>-35.91</v>
       </c>
       <c r="K23" t="n">
-        <v>-40.38</v>
+        <v>-197.71</v>
       </c>
       <c r="L23" t="n">
-        <v>102.42</v>
+        <v>200.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:58:21</t>
+          <t>05:00:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="F24" t="n">
-        <v>5.04</v>
+        <v>1.55</v>
       </c>
       <c r="G24" t="n">
-        <v>157.4</v>
+        <v>172.6</v>
       </c>
       <c r="H24" t="n">
-        <v>83.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>10.11</v>
+        <v>-69.69</v>
       </c>
       <c r="K24" t="n">
-        <v>-118.13</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>118.57</v>
+        <v>113.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:00:19</t>
+          <t>05:02:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="F25" t="n">
-        <v>5.96</v>
+        <v>6.67</v>
       </c>
       <c r="G25" t="n">
-        <v>169.8</v>
+        <v>160.8</v>
       </c>
       <c r="H25" t="n">
-        <v>83.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>88.81999999999999</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>24.44</v>
+        <v>-214.55</v>
       </c>
       <c r="L25" t="n">
-        <v>92.12</v>
+        <v>234.73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:05:29</t>
+          <t>05:07:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.76</v>
+        <v>1.4</v>
       </c>
       <c r="F26" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="G26" t="n">
-        <v>141.3</v>
+        <v>158.5</v>
       </c>
       <c r="H26" t="n">
-        <v>90.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>77.05</v>
+        <v>3.86</v>
       </c>
       <c r="K26" t="n">
-        <v>205.24</v>
+        <v>-276.92</v>
       </c>
       <c r="L26" t="n">
-        <v>219.23</v>
+        <v>276.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:07:24</t>
+          <t>05:09:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="F27" t="n">
-        <v>5.78</v>
+        <v>6.67</v>
       </c>
       <c r="G27" t="n">
-        <v>178.5</v>
+        <v>168.5</v>
       </c>
       <c r="H27" t="n">
-        <v>80.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-116.82</v>
+        <v>-14.95</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.78</v>
+        <v>184.58</v>
       </c>
       <c r="L27" t="n">
-        <v>117.08</v>
+        <v>185.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:08:33</t>
+          <t>05:11:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="F28" t="n">
-        <v>5.71</v>
+        <v>6.67</v>
       </c>
       <c r="G28" t="n">
-        <v>168.2</v>
+        <v>173.4</v>
       </c>
       <c r="H28" t="n">
-        <v>86.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>117.79</v>
+        <v>-144.7</v>
       </c>
       <c r="K28" t="n">
-        <v>139.29</v>
+        <v>-167.23</v>
       </c>
       <c r="L28" t="n">
-        <v>182.41</v>
+        <v>221.14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:18:25</t>
+          <t>05:23:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="F29" t="n">
-        <v>5.32</v>
+        <v>2.65</v>
       </c>
       <c r="G29" t="n">
-        <v>166.6</v>
+        <v>168</v>
       </c>
       <c r="H29" t="n">
-        <v>84.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>45.95</v>
+        <v>-33.06</v>
       </c>
       <c r="K29" t="n">
-        <v>-17.86</v>
+        <v>-14.57</v>
       </c>
       <c r="L29" t="n">
-        <v>49.3</v>
+        <v>36.13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:20:14</t>
+          <t>05:24:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.03</v>
+        <v>0.74</v>
       </c>
       <c r="F30" t="n">
-        <v>5.72</v>
+        <v>6.48</v>
       </c>
       <c r="G30" t="n">
-        <v>157</v>
+        <v>152.2</v>
       </c>
       <c r="H30" t="n">
-        <v>89.8</v>
+        <v>84.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.82</v>
+        <v>-44.67</v>
       </c>
       <c r="K30" t="n">
-        <v>40.32</v>
+        <v>61.88</v>
       </c>
       <c r="L30" t="n">
-        <v>42.96</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:22:36</t>
+          <t>05:26:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="F31" t="n">
-        <v>6.96</v>
+        <v>6.67</v>
       </c>
       <c r="G31" t="n">
-        <v>173.3</v>
+        <v>154.5</v>
       </c>
       <c r="H31" t="n">
-        <v>82</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>30.26</v>
+        <v>1.42</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.77</v>
+        <v>-25.75</v>
       </c>
       <c r="L31" t="n">
-        <v>50.78</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:26:44</t>
+          <t>05:31:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="F32" t="n">
-        <v>5.73</v>
+        <v>2.47</v>
       </c>
       <c r="G32" t="n">
-        <v>160.9</v>
+        <v>152.8</v>
       </c>
       <c r="H32" t="n">
-        <v>89.8</v>
+        <v>82.8</v>
       </c>
       <c r="I32" t="n">
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.6</v>
+        <v>-49.74</v>
       </c>
       <c r="K32" t="n">
-        <v>-40.19</v>
+        <v>-1.99</v>
       </c>
       <c r="L32" t="n">
-        <v>40.91</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:28:48</t>
+          <t>05:32:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.04</v>
+        <v>0.89</v>
       </c>
       <c r="F33" t="n">
-        <v>5.09</v>
+        <v>4.45</v>
       </c>
       <c r="G33" t="n">
-        <v>160.8</v>
+        <v>168.4</v>
       </c>
       <c r="H33" t="n">
-        <v>83.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>28.3</v>
+        <v>4.02</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.13</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>39.9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:30:46</t>
+          <t>05:34:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="F34" t="n">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="G34" t="n">
-        <v>161.4</v>
+        <v>167.4</v>
       </c>
       <c r="H34" t="n">
-        <v>80.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-35.5</v>
+        <v>-31.88</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.52</v>
+        <v>55.06</v>
       </c>
       <c r="L34" t="n">
-        <v>35.92</v>
+        <v>63.62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:34:40</t>
+          <t>05:38:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>5.98</v>
       </c>
       <c r="G35" t="n">
-        <v>166.5</v>
+        <v>167.4</v>
       </c>
       <c r="H35" t="n">
-        <v>84.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>23.64</v>
+        <v>-44.24</v>
       </c>
       <c r="K35" t="n">
-        <v>-31.21</v>
+        <v>100.21</v>
       </c>
       <c r="L35" t="n">
-        <v>39.15</v>
+        <v>109.54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:36:23</t>
+          <t>05:40:49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1552,31 +1552,31 @@
         <v>1.48</v>
       </c>
       <c r="F36" t="n">
-        <v>6.18</v>
+        <v>6.67</v>
       </c>
       <c r="G36" t="n">
-        <v>157.7</v>
+        <v>159.5</v>
       </c>
       <c r="H36" t="n">
-        <v>85.2</v>
+        <v>91.7</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>30.46</v>
+        <v>70.5</v>
       </c>
       <c r="K36" t="n">
-        <v>57.79</v>
+        <v>-69.92</v>
       </c>
       <c r="L36" t="n">
-        <v>65.33</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:37:53</t>
+          <t>05:41:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="F37" t="n">
-        <v>6.48</v>
+        <v>6.67</v>
       </c>
       <c r="G37" t="n">
-        <v>157.5</v>
+        <v>176.2</v>
       </c>
       <c r="H37" t="n">
-        <v>88.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>74.84999999999999</v>
+        <v>27.05</v>
       </c>
       <c r="K37" t="n">
-        <v>-35.4</v>
+        <v>-91.98</v>
       </c>
       <c r="L37" t="n">
-        <v>82.8</v>
+        <v>95.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:42:03</t>
+          <t>05:46:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1636,31 +1636,31 @@
         <v>1.24</v>
       </c>
       <c r="F38" t="n">
-        <v>5.54</v>
+        <v>4.36</v>
       </c>
       <c r="G38" t="n">
-        <v>162.6</v>
+        <v>162.8</v>
       </c>
       <c r="H38" t="n">
-        <v>79.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-109.82</v>
+        <v>-169.66</v>
       </c>
       <c r="K38" t="n">
-        <v>-38.19</v>
+        <v>-18.51</v>
       </c>
       <c r="L38" t="n">
-        <v>116.27</v>
+        <v>170.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:43:12</t>
+          <t>05:48:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="F39" t="n">
-        <v>5.73</v>
+        <v>5.31</v>
       </c>
       <c r="G39" t="n">
-        <v>159.9</v>
+        <v>162.6</v>
       </c>
       <c r="H39" t="n">
-        <v>77.2</v>
+        <v>80.3</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>5.65</v>
+        <v>52.71</v>
       </c>
       <c r="K39" t="n">
-        <v>-102.77</v>
+        <v>-126.55</v>
       </c>
       <c r="L39" t="n">
-        <v>102.92</v>
+        <v>137.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:44:35</t>
+          <t>05:50:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>0.95</v>
+        <v>1.37</v>
       </c>
       <c r="F40" t="n">
-        <v>5.43</v>
+        <v>5.96</v>
       </c>
       <c r="G40" t="n">
-        <v>164.1</v>
+        <v>157.6</v>
       </c>
       <c r="H40" t="n">
-        <v>82.5</v>
+        <v>85.5</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.6</v>
+        <v>112.89</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.34</v>
+        <v>-152.2</v>
       </c>
       <c r="L40" t="n">
-        <v>6.07</v>
+        <v>189.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:49:57</t>
+          <t>05:54:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="F41" t="n">
-        <v>5.54</v>
+        <v>6.67</v>
       </c>
       <c r="G41" t="n">
-        <v>148.6</v>
+        <v>150.4</v>
       </c>
       <c r="H41" t="n">
-        <v>91.2</v>
+        <v>86.3</v>
       </c>
       <c r="I41" t="n">
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>99.2</v>
+        <v>-67.05</v>
       </c>
       <c r="K41" t="n">
-        <v>150.91</v>
+        <v>191.32</v>
       </c>
       <c r="L41" t="n">
-        <v>180.59</v>
+        <v>202.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:51:20</t>
+          <t>05:55:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="F42" t="n">
-        <v>6.1</v>
+        <v>6.27</v>
       </c>
       <c r="G42" t="n">
-        <v>158.5</v>
+        <v>157.4</v>
       </c>
       <c r="H42" t="n">
-        <v>82.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-77.06999999999999</v>
+        <v>190.67</v>
       </c>
       <c r="K42" t="n">
-        <v>84.81</v>
+        <v>165</v>
       </c>
       <c r="L42" t="n">
-        <v>114.6</v>
+        <v>252.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:53:00</t>
+          <t>05:57:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.63</v>
+        <v>1.05</v>
       </c>
       <c r="F43" t="n">
-        <v>5.64</v>
+        <v>6.34</v>
       </c>
       <c r="G43" t="n">
-        <v>152.4</v>
+        <v>158.3</v>
       </c>
       <c r="H43" t="n">
-        <v>90.7</v>
+        <v>88</v>
       </c>
       <c r="I43" t="n">
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-168.62</v>
+        <v>284.68</v>
       </c>
       <c r="K43" t="n">
-        <v>39.18</v>
+        <v>-75.86</v>
       </c>
       <c r="L43" t="n">
-        <v>173.11</v>
+        <v>294.62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:03:00</t>
+          <t>06:08:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="F44" t="n">
-        <v>6.01</v>
+        <v>6.67</v>
       </c>
       <c r="G44" t="n">
-        <v>158.2</v>
+        <v>148.9</v>
       </c>
       <c r="H44" t="n">
-        <v>93.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>37.42</v>
+        <v>57.81</v>
       </c>
       <c r="K44" t="n">
-        <v>46.65</v>
+        <v>-20.9</v>
       </c>
       <c r="L44" t="n">
-        <v>59.81</v>
+        <v>61.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:05:06</t>
+          <t>06:10:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0.98</v>
+        <v>1.34</v>
       </c>
       <c r="F45" t="n">
-        <v>5.13</v>
+        <v>3.75</v>
       </c>
       <c r="G45" t="n">
-        <v>164.2</v>
+        <v>158</v>
       </c>
       <c r="H45" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>13.22</v>
+        <v>24.3</v>
       </c>
       <c r="K45" t="n">
-        <v>-25.68</v>
+        <v>-49.87</v>
       </c>
       <c r="L45" t="n">
-        <v>28.89</v>
+        <v>55.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:07:35</t>
+          <t>06:11:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="F46" t="n">
-        <v>6.42</v>
+        <v>6.67</v>
       </c>
       <c r="G46" t="n">
-        <v>150.2</v>
+        <v>153</v>
       </c>
       <c r="H46" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>28.11</v>
+        <v>-34.14</v>
       </c>
       <c r="K46" t="n">
-        <v>24.25</v>
+        <v>-31.02</v>
       </c>
       <c r="L46" t="n">
-        <v>37.12</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:13:00</t>
+          <t>06:17:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="F47" t="n">
-        <v>6.01</v>
+        <v>2.68</v>
       </c>
       <c r="G47" t="n">
-        <v>150.5</v>
+        <v>165.5</v>
       </c>
       <c r="H47" t="n">
-        <v>84.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-5.15</v>
+        <v>54.63</v>
       </c>
       <c r="K47" t="n">
-        <v>47.58</v>
+        <v>33.42</v>
       </c>
       <c r="L47" t="n">
-        <v>47.86</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:14:32</t>
+          <t>06:19:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="F48" t="n">
-        <v>5.52</v>
+        <v>6.67</v>
       </c>
       <c r="G48" t="n">
-        <v>166.2</v>
+        <v>148.9</v>
       </c>
       <c r="H48" t="n">
-        <v>90.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>46.13</v>
+        <v>44.18</v>
       </c>
       <c r="K48" t="n">
-        <v>35.01</v>
+        <v>-74.59</v>
       </c>
       <c r="L48" t="n">
-        <v>57.91</v>
+        <v>86.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:16:28</t>
+          <t>06:21:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.99</v>
+        <v>1.42</v>
       </c>
       <c r="F49" t="n">
-        <v>6.57</v>
+        <v>6.67</v>
       </c>
       <c r="G49" t="n">
-        <v>167.3</v>
+        <v>169.2</v>
       </c>
       <c r="H49" t="n">
-        <v>81.8</v>
+        <v>87.2</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-48.8</v>
+        <v>37.19</v>
       </c>
       <c r="K49" t="n">
-        <v>8.73</v>
+        <v>-63.26</v>
       </c>
       <c r="L49" t="n">
-        <v>49.57</v>
+        <v>73.38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:21:41</t>
+          <t>06:24:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="F50" t="n">
-        <v>5.51</v>
+        <v>3.12</v>
       </c>
       <c r="G50" t="n">
-        <v>154.5</v>
+        <v>158.4</v>
       </c>
       <c r="H50" t="n">
-        <v>88.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-33.29</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-125.19</v>
+        <v>97.08</v>
       </c>
       <c r="L50" t="n">
-        <v>129.54</v>
+        <v>117.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:23:04</t>
+          <t>06:26:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="F51" t="n">
-        <v>6.06</v>
+        <v>6.02</v>
       </c>
       <c r="G51" t="n">
-        <v>161.6</v>
+        <v>164</v>
       </c>
       <c r="H51" t="n">
-        <v>93.09999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>52.59</v>
+        <v>113.11</v>
       </c>
       <c r="K51" t="n">
-        <v>-31.15</v>
+        <v>-139.41</v>
       </c>
       <c r="L51" t="n">
-        <v>61.13</v>
+        <v>179.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:24:07</t>
+          <t>06:27:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="F52" t="n">
-        <v>6.03</v>
+        <v>6.67</v>
       </c>
       <c r="G52" t="n">
-        <v>141.8</v>
+        <v>147.5</v>
       </c>
       <c r="H52" t="n">
-        <v>94.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>26.26</v>
+        <v>113.21</v>
       </c>
       <c r="K52" t="n">
-        <v>-81.01000000000001</v>
+        <v>12.09</v>
       </c>
       <c r="L52" t="n">
-        <v>85.16</v>
+        <v>113.85</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:29:57</t>
+          <t>06:33:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.97</v>
+        <v>1.44</v>
       </c>
       <c r="F53" t="n">
-        <v>5.62</v>
+        <v>6.67</v>
       </c>
       <c r="G53" t="n">
-        <v>167.3</v>
+        <v>170.4</v>
       </c>
       <c r="H53" t="n">
-        <v>87.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>101.47</v>
+        <v>-103.68</v>
       </c>
       <c r="K53" t="n">
-        <v>-28.67</v>
+        <v>70.16</v>
       </c>
       <c r="L53" t="n">
-        <v>105.44</v>
+        <v>125.19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:31:09</t>
+          <t>06:34:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="F54" t="n">
-        <v>6.56</v>
+        <v>4.5</v>
       </c>
       <c r="G54" t="n">
-        <v>165.3</v>
+        <v>159.9</v>
       </c>
       <c r="H54" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-72.15000000000001</v>
+        <v>-96.54000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>129.22</v>
+        <v>-6.4</v>
       </c>
       <c r="L54" t="n">
-        <v>147.99</v>
+        <v>96.76000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:33:14</t>
+          <t>06:36:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="F55" t="n">
-        <v>6.7</v>
+        <v>6.67</v>
       </c>
       <c r="G55" t="n">
-        <v>156.4</v>
+        <v>146.3</v>
       </c>
       <c r="H55" t="n">
-        <v>87.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I55" t="n">
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>2.59</v>
+        <v>233.7</v>
       </c>
       <c r="K55" t="n">
-        <v>106.38</v>
+        <v>-38.36</v>
       </c>
       <c r="L55" t="n">
-        <v>106.41</v>
+        <v>236.83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:37:21</t>
+          <t>06:40:04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="F56" t="n">
-        <v>6.81</v>
+        <v>4.4</v>
       </c>
       <c r="G56" t="n">
-        <v>158.6</v>
+        <v>177.8</v>
       </c>
       <c r="H56" t="n">
-        <v>79.2</v>
+        <v>86.2</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>133.46</v>
+        <v>-259.22</v>
       </c>
       <c r="K56" t="n">
-        <v>-135.71</v>
+        <v>55.93</v>
       </c>
       <c r="L56" t="n">
-        <v>190.34</v>
+        <v>265.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:38:39</t>
+          <t>06:41:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="F57" t="n">
-        <v>6.07</v>
+        <v>6.17</v>
       </c>
       <c r="G57" t="n">
-        <v>144.5</v>
+        <v>163.6</v>
       </c>
       <c r="H57" t="n">
-        <v>90.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-110.39</v>
+        <v>211.98</v>
       </c>
       <c r="K57" t="n">
-        <v>79.05</v>
+        <v>-263.76</v>
       </c>
       <c r="L57" t="n">
-        <v>135.77</v>
+        <v>338.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:29</t>
+          <t>06:42:48</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="F58" t="n">
-        <v>6.34</v>
+        <v>6.67</v>
       </c>
       <c r="G58" t="n">
-        <v>163.7</v>
+        <v>151.7</v>
       </c>
       <c r="H58" t="n">
-        <v>87.8</v>
+        <v>84.5</v>
       </c>
       <c r="I58" t="n">
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>181.34</v>
+        <v>123.46</v>
       </c>
       <c r="K58" t="n">
-        <v>-79.37</v>
+        <v>-112.72</v>
       </c>
       <c r="L58" t="n">
-        <v>197.95</v>
+        <v>167.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:51:34</t>
+          <t>06:54:50</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="F59" t="n">
-        <v>5.76</v>
+        <v>6.67</v>
       </c>
       <c r="G59" t="n">
-        <v>162.8</v>
+        <v>147.8</v>
       </c>
       <c r="H59" t="n">
-        <v>88.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>33.03</v>
+        <v>36.69</v>
       </c>
       <c r="K59" t="n">
-        <v>47.16</v>
+        <v>40.86</v>
       </c>
       <c r="L59" t="n">
-        <v>57.57</v>
+        <v>54.92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:53:23</t>
+          <t>06:56:13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.54</v>
+        <v>1.1</v>
       </c>
       <c r="F60" t="n">
-        <v>6.07</v>
+        <v>6.67</v>
       </c>
       <c r="G60" t="n">
-        <v>165.9</v>
+        <v>166.4</v>
       </c>
       <c r="H60" t="n">
-        <v>80</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-33.65</v>
+        <v>-5.68</v>
       </c>
       <c r="K60" t="n">
-        <v>24.81</v>
+        <v>-54.13</v>
       </c>
       <c r="L60" t="n">
-        <v>41.81</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:55:39</t>
+          <t>06:57:38</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="F61" t="n">
-        <v>5.42</v>
+        <v>6.67</v>
       </c>
       <c r="G61" t="n">
-        <v>160.1</v>
+        <v>155.7</v>
       </c>
       <c r="H61" t="n">
-        <v>83.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.73</v>
+        <v>-54.16</v>
       </c>
       <c r="K61" t="n">
-        <v>25.72</v>
+        <v>-6.22</v>
       </c>
       <c r="L61" t="n">
-        <v>33.67</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:59:17</t>
+          <t>07:01:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="F62" t="n">
-        <v>5.36</v>
+        <v>6.67</v>
       </c>
       <c r="G62" t="n">
-        <v>163.8</v>
+        <v>162.1</v>
       </c>
       <c r="H62" t="n">
-        <v>83.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>2.62</v>
+        <v>-31.86</v>
       </c>
       <c r="K62" t="n">
-        <v>-51.46</v>
+        <v>62.47</v>
       </c>
       <c r="L62" t="n">
-        <v>51.53</v>
+        <v>70.12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:00:43</t>
+          <t>07:04:05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="F63" t="n">
-        <v>6.14</v>
+        <v>6.61</v>
       </c>
       <c r="G63" t="n">
-        <v>157.5</v>
+        <v>148.2</v>
       </c>
       <c r="H63" t="n">
-        <v>91.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>58.54</v>
+        <v>67.55</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.609999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="L63" t="n">
-        <v>59.17</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:02:20</t>
+          <t>07:05:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="F64" t="n">
-        <v>6.1</v>
+        <v>6.67</v>
       </c>
       <c r="G64" t="n">
-        <v>166.4</v>
+        <v>167.2</v>
       </c>
       <c r="H64" t="n">
-        <v>80.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-52.63</v>
+        <v>16.81</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.52</v>
+        <v>-109.93</v>
       </c>
       <c r="L64" t="n">
-        <v>54.59</v>
+        <v>111.21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:07:23</t>
+          <t>07:11:42</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="F65" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="G65" t="n">
-        <v>163.5</v>
+        <v>154.6</v>
       </c>
       <c r="H65" t="n">
-        <v>99.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>56.92</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.34</v>
+        <v>108.5</v>
       </c>
       <c r="L65" t="n">
-        <v>57.02</v>
+        <v>142.58</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:08:48</t>
+          <t>07:13:52</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="F66" t="n">
-        <v>6.36</v>
+        <v>6.67</v>
       </c>
       <c r="G66" t="n">
-        <v>163.9</v>
+        <v>165.6</v>
       </c>
       <c r="H66" t="n">
-        <v>83.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>93.41</v>
+        <v>-18.12</v>
       </c>
       <c r="K66" t="n">
-        <v>-53.8</v>
+        <v>122.57</v>
       </c>
       <c r="L66" t="n">
-        <v>107.8</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:11:18</t>
+          <t>07:16:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="F67" t="n">
-        <v>6.38</v>
+        <v>6.67</v>
       </c>
       <c r="G67" t="n">
-        <v>159.1</v>
+        <v>173.3</v>
       </c>
       <c r="H67" t="n">
-        <v>86.2</v>
+        <v>89.2</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>21.34</v>
+        <v>72.48</v>
       </c>
       <c r="K67" t="n">
-        <v>60.18</v>
+        <v>-40.11</v>
       </c>
       <c r="L67" t="n">
-        <v>63.85</v>
+        <v>82.84</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:16:58</t>
+          <t>07:19:06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="F68" t="n">
-        <v>5.93</v>
+        <v>6.67</v>
       </c>
       <c r="G68" t="n">
-        <v>150.6</v>
+        <v>174.4</v>
       </c>
       <c r="H68" t="n">
-        <v>92.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-33.95</v>
+        <v>85.67</v>
       </c>
       <c r="K68" t="n">
-        <v>87.91</v>
+        <v>-145.33</v>
       </c>
       <c r="L68" t="n">
-        <v>94.23999999999999</v>
+        <v>168.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:19:20</t>
+          <t>07:21:35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="F69" t="n">
-        <v>5.44</v>
+        <v>4.42</v>
       </c>
       <c r="G69" t="n">
-        <v>165.6</v>
+        <v>165.8</v>
       </c>
       <c r="H69" t="n">
-        <v>80.8</v>
+        <v>93.2</v>
       </c>
       <c r="I69" t="n">
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>12.97</v>
+        <v>-35.66</v>
       </c>
       <c r="K69" t="n">
-        <v>-79.22</v>
+        <v>-99.2</v>
       </c>
       <c r="L69" t="n">
-        <v>80.28</v>
+        <v>105.41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:20:04</t>
+          <t>07:22:37</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8</v>
+        <v>1.27</v>
       </c>
       <c r="F70" t="n">
-        <v>5.7</v>
+        <v>1.57</v>
       </c>
       <c r="G70" t="n">
-        <v>159.6</v>
+        <v>169.4</v>
       </c>
       <c r="H70" t="n">
-        <v>89.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-105.1</v>
+        <v>55.8</v>
       </c>
       <c r="K70" t="n">
-        <v>-113.99</v>
+        <v>90.23</v>
       </c>
       <c r="L70" t="n">
-        <v>155.05</v>
+        <v>106.09</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:25:12</t>
+          <t>07:26:45</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="F71" t="n">
-        <v>6.09</v>
+        <v>6.67</v>
       </c>
       <c r="G71" t="n">
-        <v>167.2</v>
+        <v>170</v>
       </c>
       <c r="H71" t="n">
-        <v>88</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>72.17</v>
+        <v>-289.83</v>
       </c>
       <c r="K71" t="n">
-        <v>-111.14</v>
+        <v>-59.59</v>
       </c>
       <c r="L71" t="n">
-        <v>132.52</v>
+        <v>295.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:26:13</t>
+          <t>07:27:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="F72" t="n">
-        <v>5.7</v>
+        <v>1.94</v>
       </c>
       <c r="G72" t="n">
-        <v>142.1</v>
+        <v>167.5</v>
       </c>
       <c r="H72" t="n">
-        <v>92.8</v>
+        <v>74.5</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>122.3</v>
+        <v>-184.95</v>
       </c>
       <c r="K72" t="n">
-        <v>-152.87</v>
+        <v>-33.31</v>
       </c>
       <c r="L72" t="n">
-        <v>195.77</v>
+        <v>187.92</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:27:55</t>
+          <t>07:29:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>0.78</v>
+        <v>1.62</v>
       </c>
       <c r="F73" t="n">
-        <v>6.41</v>
+        <v>6.67</v>
       </c>
       <c r="G73" t="n">
-        <v>159.9</v>
+        <v>165</v>
       </c>
       <c r="H73" t="n">
-        <v>79.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>26.44</v>
+        <v>-72.7</v>
       </c>
       <c r="K73" t="n">
-        <v>109.21</v>
+        <v>-280.14</v>
       </c>
       <c r="L73" t="n">
-        <v>112.37</v>
+        <v>289.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:36:51</t>
+          <t>07:39:06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="F74" t="n">
-        <v>5.48</v>
+        <v>6.6</v>
       </c>
       <c r="G74" t="n">
-        <v>159.6</v>
+        <v>172</v>
       </c>
       <c r="H74" t="n">
-        <v>79.7</v>
+        <v>89</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>19.19</v>
+        <v>22.06</v>
       </c>
       <c r="K74" t="n">
-        <v>41.57</v>
+        <v>-35.01</v>
       </c>
       <c r="L74" t="n">
-        <v>45.79</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:38:59</t>
+          <t>07:41:20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="F75" t="n">
-        <v>5.98</v>
+        <v>6.67</v>
       </c>
       <c r="G75" t="n">
-        <v>153.2</v>
+        <v>153.4</v>
       </c>
       <c r="H75" t="n">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>19.65</v>
+        <v>45.31</v>
       </c>
       <c r="K75" t="n">
-        <v>-35.43</v>
+        <v>-14.39</v>
       </c>
       <c r="L75" t="n">
-        <v>40.51</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:40:38</t>
+          <t>07:43:38</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>5.79</v>
+        <v>2.44</v>
       </c>
       <c r="G76" t="n">
-        <v>145.5</v>
+        <v>168.7</v>
       </c>
       <c r="H76" t="n">
-        <v>86</v>
+        <v>91.2</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>36.15</v>
+        <v>37.04</v>
       </c>
       <c r="K76" t="n">
-        <v>29.35</v>
+        <v>17.36</v>
       </c>
       <c r="L76" t="n">
-        <v>46.57</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:46:28</t>
+          <t>07:47:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="F77" t="n">
-        <v>5.29</v>
+        <v>1.53</v>
       </c>
       <c r="G77" t="n">
-        <v>167.9</v>
+        <v>148.8</v>
       </c>
       <c r="H77" t="n">
-        <v>80.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-23.85</v>
+        <v>-56.94</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.66</v>
+        <v>-30.81</v>
       </c>
       <c r="L77" t="n">
-        <v>61.48</v>
+        <v>64.73999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:48:47</t>
+          <t>07:49:48</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="F78" t="n">
-        <v>5.62</v>
+        <v>6.67</v>
       </c>
       <c r="G78" t="n">
-        <v>156</v>
+        <v>168.9</v>
       </c>
       <c r="H78" t="n">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>3.62</v>
+        <v>-83.03</v>
       </c>
       <c r="K78" t="n">
-        <v>53.46</v>
+        <v>25.86</v>
       </c>
       <c r="L78" t="n">
-        <v>53.58</v>
+        <v>86.97</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:49:56</t>
+          <t>07:51:25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="F79" t="n">
-        <v>6.63</v>
+        <v>6.67</v>
       </c>
       <c r="G79" t="n">
-        <v>155.9</v>
+        <v>168.7</v>
       </c>
       <c r="H79" t="n">
-        <v>87.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>42.44</v>
+        <v>57.47</v>
       </c>
       <c r="K79" t="n">
-        <v>42.96</v>
+        <v>25.29</v>
       </c>
       <c r="L79" t="n">
-        <v>60.39</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:54:33</t>
+          <t>07:56:34</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="F80" t="n">
-        <v>5.31</v>
+        <v>5.87</v>
       </c>
       <c r="G80" t="n">
-        <v>156.4</v>
+        <v>161</v>
       </c>
       <c r="H80" t="n">
-        <v>87.8</v>
+        <v>88.8</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>64.11</v>
+        <v>11.35</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.37</v>
+        <v>-77.75</v>
       </c>
       <c r="L80" t="n">
-        <v>64.12</v>
+        <v>78.56999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:56:09</t>
+          <t>07:58:42</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="F81" t="n">
-        <v>5.61</v>
+        <v>6.31</v>
       </c>
       <c r="G81" t="n">
-        <v>163.1</v>
+        <v>156.3</v>
       </c>
       <c r="H81" t="n">
-        <v>92.7</v>
+        <v>85.7</v>
       </c>
       <c r="I81" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.63</v>
+        <v>106.98</v>
       </c>
       <c r="K81" t="n">
-        <v>-60.35</v>
+        <v>-1.44</v>
       </c>
       <c r="L81" t="n">
-        <v>63.16</v>
+        <v>106.99</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:58:15</t>
+          <t>08:00:38</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="F82" t="n">
-        <v>6.05</v>
+        <v>1.36</v>
       </c>
       <c r="G82" t="n">
-        <v>147.4</v>
+        <v>157.1</v>
       </c>
       <c r="H82" t="n">
-        <v>86.8</v>
+        <v>89.3</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>60.47</v>
+        <v>0.09</v>
       </c>
       <c r="K82" t="n">
-        <v>-42.67</v>
+        <v>-37.53</v>
       </c>
       <c r="L82" t="n">
-        <v>74.01000000000001</v>
+        <v>37.53</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:04:09</t>
+          <t>08:05:16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="F83" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="G83" t="n">
-        <v>161.6</v>
+        <v>155.2</v>
       </c>
       <c r="H83" t="n">
-        <v>87.3</v>
+        <v>87.5</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>31.1</v>
+        <v>-114.16</v>
       </c>
       <c r="K83" t="n">
-        <v>-89.53</v>
+        <v>120.66</v>
       </c>
       <c r="L83" t="n">
-        <v>94.78</v>
+        <v>166.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:06:04</t>
+          <t>08:06:16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="F84" t="n">
-        <v>5.46</v>
+        <v>1.4</v>
       </c>
       <c r="G84" t="n">
-        <v>149</v>
+        <v>157.5</v>
       </c>
       <c r="H84" t="n">
-        <v>91.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>59.25</v>
+        <v>-100.76</v>
       </c>
       <c r="K84" t="n">
-        <v>-62.22</v>
+        <v>46.02</v>
       </c>
       <c r="L84" t="n">
-        <v>85.92</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:08:10</t>
+          <t>08:08:16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="F85" t="n">
-        <v>5.81</v>
+        <v>6.67</v>
       </c>
       <c r="G85" t="n">
-        <v>162.6</v>
+        <v>165.3</v>
       </c>
       <c r="H85" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-71.09</v>
+        <v>52.95</v>
       </c>
       <c r="K85" t="n">
-        <v>-89.69</v>
+        <v>135.13</v>
       </c>
       <c r="L85" t="n">
-        <v>114.45</v>
+        <v>145.14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:12:53</t>
+          <t>08:13:18</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="F86" t="n">
-        <v>5.62</v>
+        <v>5.12</v>
       </c>
       <c r="G86" t="n">
-        <v>173.3</v>
+        <v>165.8</v>
       </c>
       <c r="H86" t="n">
-        <v>88.3</v>
+        <v>86.7</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>-117.17</v>
+        <v>255.88</v>
       </c>
       <c r="K86" t="n">
-        <v>-12.39</v>
+        <v>27.84</v>
       </c>
       <c r="L86" t="n">
-        <v>117.83</v>
+        <v>257.39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:14:53</t>
+          <t>08:15:10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="F87" t="n">
-        <v>5.79</v>
+        <v>6.67</v>
       </c>
       <c r="G87" t="n">
-        <v>167.1</v>
+        <v>168.1</v>
       </c>
       <c r="H87" t="n">
-        <v>88.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-37.03</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-140.32</v>
+        <v>172.86</v>
       </c>
       <c r="L87" t="n">
-        <v>145.13</v>
+        <v>185.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:17:21</t>
+          <t>08:17:12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="F88" t="n">
-        <v>5.86</v>
+        <v>5.12</v>
       </c>
       <c r="G88" t="n">
-        <v>168.8</v>
+        <v>158.2</v>
       </c>
       <c r="H88" t="n">
-        <v>87.5</v>
+        <v>90.7</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-81.40000000000001</v>
+        <v>151.82</v>
       </c>
       <c r="K88" t="n">
-        <v>154.31</v>
+        <v>34.99</v>
       </c>
       <c r="L88" t="n">
-        <v>174.47</v>
+        <v>155.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>53.53</v>
+        <v>54.58</v>
       </c>
       <c r="K15" t="n">
-        <v>14.09</v>
+        <v>14.36</v>
       </c>
       <c r="L15" t="n">
-        <v>55.35</v>
+        <v>56.44</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>30.91</v>
+        <v>29.63</v>
       </c>
       <c r="K16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="L16" t="n">
-        <v>30.93</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.5</v>
+        <v>-3.28</v>
       </c>
       <c r="K17" t="n">
-        <v>50.51</v>
+        <v>47.29</v>
       </c>
       <c r="L17" t="n">
-        <v>50.63</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>74.43000000000001</v>
+        <v>72.91</v>
       </c>
       <c r="K18" t="n">
-        <v>66.2</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>99.61</v>
+        <v>97.56999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>31.81</v>
+        <v>32.43</v>
       </c>
       <c r="K19" t="n">
-        <v>55.71</v>
+        <v>56.8</v>
       </c>
       <c r="L19" t="n">
-        <v>64.15000000000001</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="20">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-44.84</v>
+        <v>-43.93</v>
       </c>
       <c r="K21" t="n">
-        <v>-98.67</v>
+        <v>-96.66</v>
       </c>
       <c r="L21" t="n">
-        <v>108.38</v>
+        <v>106.17</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>36.49</v>
+        <v>37.2</v>
       </c>
       <c r="K22" t="n">
-        <v>-90.41</v>
+        <v>-92.18000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>97.48999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-35.91</v>
+        <v>-35.18</v>
       </c>
       <c r="K23" t="n">
-        <v>-197.71</v>
+        <v>-193.68</v>
       </c>
       <c r="L23" t="n">
-        <v>200.95</v>
+        <v>196.84</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-69.69</v>
+        <v>-61.95</v>
       </c>
       <c r="K24" t="n">
-        <v>89.31999999999999</v>
+        <v>79.39</v>
       </c>
       <c r="L24" t="n">
-        <v>113.29</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>95.20999999999999</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-214.55</v>
+        <v>-195.9</v>
       </c>
       <c r="L25" t="n">
-        <v>234.73</v>
+        <v>214.32</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="K26" t="n">
-        <v>-276.92</v>
+        <v>-271.27</v>
       </c>
       <c r="L26" t="n">
-        <v>276.95</v>
+        <v>271.3</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-14.95</v>
+        <v>-13.65</v>
       </c>
       <c r="K27" t="n">
-        <v>184.58</v>
+        <v>168.53</v>
       </c>
       <c r="L27" t="n">
-        <v>185.19</v>
+        <v>169.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-144.7</v>
+        <v>-135.46</v>
       </c>
       <c r="K28" t="n">
-        <v>-167.23</v>
+        <v>-156.56</v>
       </c>
       <c r="L28" t="n">
-        <v>221.14</v>
+        <v>207.03</v>
       </c>
     </row>
     <row r="29">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>-44.67</v>
+        <v>-40.78</v>
       </c>
       <c r="K30" t="n">
-        <v>61.88</v>
+        <v>56.49</v>
       </c>
       <c r="L30" t="n">
-        <v>76.31</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="K31" t="n">
-        <v>-25.75</v>
+        <v>-25.22</v>
       </c>
       <c r="L31" t="n">
-        <v>25.78</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-49.74</v>
+        <v>-46.56</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.99</v>
+        <v>-1.86</v>
       </c>
       <c r="L32" t="n">
-        <v>49.78</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>4.02</v>
+        <v>3.85</v>
       </c>
       <c r="K33" t="n">
-        <v>-74.90000000000001</v>
+        <v>-71.78</v>
       </c>
       <c r="L33" t="n">
-        <v>75</v>
+        <v>71.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-31.88</v>
+        <v>-30.55</v>
       </c>
       <c r="K34" t="n">
-        <v>55.06</v>
+        <v>52.76</v>
       </c>
       <c r="L34" t="n">
-        <v>63.62</v>
+        <v>60.97</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-44.24</v>
+        <v>-45.1</v>
       </c>
       <c r="K35" t="n">
-        <v>100.21</v>
+        <v>102.18</v>
       </c>
       <c r="L35" t="n">
-        <v>109.54</v>
+        <v>111.69</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>70.5</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-69.92</v>
+        <v>-68.48999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>99.29000000000001</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>27.05</v>
+        <v>25.33</v>
       </c>
       <c r="K37" t="n">
-        <v>-91.98</v>
+        <v>-86.09999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>95.87</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-169.66</v>
+        <v>-150.81</v>
       </c>
       <c r="K38" t="n">
-        <v>-18.51</v>
+        <v>-16.45</v>
       </c>
       <c r="L38" t="n">
-        <v>170.66</v>
+        <v>151.7</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>52.71</v>
+        <v>48.12</v>
       </c>
       <c r="K39" t="n">
-        <v>-126.55</v>
+        <v>-115.55</v>
       </c>
       <c r="L39" t="n">
-        <v>137.09</v>
+        <v>125.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>112.89</v>
+        <v>110.59</v>
       </c>
       <c r="K40" t="n">
-        <v>-152.2</v>
+        <v>-149.09</v>
       </c>
       <c r="L40" t="n">
-        <v>189.5</v>
+        <v>185.63</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-67.05</v>
+        <v>-64.26000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>191.32</v>
+        <v>183.35</v>
       </c>
       <c r="L41" t="n">
-        <v>202.73</v>
+        <v>194.28</v>
       </c>
     </row>
     <row r="42">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>284.68</v>
+        <v>272.82</v>
       </c>
       <c r="K43" t="n">
-        <v>-75.86</v>
+        <v>-72.7</v>
       </c>
       <c r="L43" t="n">
-        <v>294.62</v>
+        <v>282.34</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>57.81</v>
+        <v>55.4</v>
       </c>
       <c r="K44" t="n">
-        <v>-20.9</v>
+        <v>-20.03</v>
       </c>
       <c r="L44" t="n">
-        <v>61.47</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>24.3</v>
+        <v>24.78</v>
       </c>
       <c r="K45" t="n">
-        <v>-49.87</v>
+        <v>-50.85</v>
       </c>
       <c r="L45" t="n">
-        <v>55.48</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-34.14</v>
+        <v>-32.72</v>
       </c>
       <c r="K46" t="n">
-        <v>-31.02</v>
+        <v>-29.73</v>
       </c>
       <c r="L46" t="n">
-        <v>46.13</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>54.63</v>
+        <v>53.52</v>
       </c>
       <c r="K47" t="n">
-        <v>33.42</v>
+        <v>32.73</v>
       </c>
       <c r="L47" t="n">
-        <v>64.04000000000001</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>44.18</v>
+        <v>42.34</v>
       </c>
       <c r="K48" t="n">
-        <v>-74.59</v>
+        <v>-71.48</v>
       </c>
       <c r="L48" t="n">
-        <v>86.69</v>
+        <v>83.08</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>37.19</v>
+        <v>35.64</v>
       </c>
       <c r="K49" t="n">
-        <v>-63.26</v>
+        <v>-60.63</v>
       </c>
       <c r="L49" t="n">
-        <v>73.38</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="50">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>113.11</v>
+        <v>108.39</v>
       </c>
       <c r="K51" t="n">
-        <v>-139.41</v>
+        <v>-133.6</v>
       </c>
       <c r="L51" t="n">
-        <v>179.52</v>
+        <v>172.04</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>113.21</v>
+        <v>100.63</v>
       </c>
       <c r="K52" t="n">
-        <v>12.09</v>
+        <v>10.74</v>
       </c>
       <c r="L52" t="n">
-        <v>113.85</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-103.68</v>
+        <v>-94.66</v>
       </c>
       <c r="K53" t="n">
-        <v>70.16</v>
+        <v>64.06</v>
       </c>
       <c r="L53" t="n">
-        <v>125.19</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-96.54000000000001</v>
+        <v>-92.52</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.4</v>
+        <v>-6.13</v>
       </c>
       <c r="L54" t="n">
-        <v>96.76000000000001</v>
+        <v>92.73</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>233.7</v>
+        <v>228.94</v>
       </c>
       <c r="K55" t="n">
-        <v>-38.36</v>
+        <v>-37.57</v>
       </c>
       <c r="L55" t="n">
-        <v>236.83</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>211.98</v>
+        <v>216.13</v>
       </c>
       <c r="K57" t="n">
-        <v>-263.76</v>
+        <v>-268.93</v>
       </c>
       <c r="L57" t="n">
-        <v>338.38</v>
+        <v>345.02</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>123.46</v>
+        <v>112.73</v>
       </c>
       <c r="K58" t="n">
-        <v>-112.72</v>
+        <v>-102.92</v>
       </c>
       <c r="L58" t="n">
-        <v>167.18</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>36.69</v>
+        <v>35.17</v>
       </c>
       <c r="K59" t="n">
-        <v>40.86</v>
+        <v>39.16</v>
       </c>
       <c r="L59" t="n">
-        <v>54.92</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.68</v>
+        <v>-5.31</v>
       </c>
       <c r="K60" t="n">
-        <v>-54.13</v>
+        <v>-50.67</v>
       </c>
       <c r="L60" t="n">
-        <v>54.43</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-54.16</v>
+        <v>-49.45</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.22</v>
+        <v>-5.68</v>
       </c>
       <c r="L61" t="n">
-        <v>54.51</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>-31.86</v>
+        <v>-29.09</v>
       </c>
       <c r="K62" t="n">
-        <v>62.47</v>
+        <v>57.04</v>
       </c>
       <c r="L62" t="n">
-        <v>70.12</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>67.55</v>
+        <v>64.73</v>
       </c>
       <c r="K63" t="n">
-        <v>7.37</v>
+        <v>7.06</v>
       </c>
       <c r="L63" t="n">
-        <v>67.95</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>16.81</v>
+        <v>16.46</v>
       </c>
       <c r="K64" t="n">
-        <v>-109.93</v>
+        <v>-107.69</v>
       </c>
       <c r="L64" t="n">
-        <v>111.21</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>92.51000000000001</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>108.5</v>
+        <v>103.98</v>
       </c>
       <c r="L65" t="n">
-        <v>142.58</v>
+        <v>136.64</v>
       </c>
     </row>
     <row r="66">
@@ -2866,13 +2866,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>72.48</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-40.11</v>
+        <v>-35.65</v>
       </c>
       <c r="L67" t="n">
-        <v>82.84</v>
+        <v>73.63</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>85.67</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-145.33</v>
+        <v>-148.18</v>
       </c>
       <c r="L68" t="n">
-        <v>168.7</v>
+        <v>172.01</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-35.66</v>
+        <v>-33.39</v>
       </c>
       <c r="K69" t="n">
-        <v>-99.2</v>
+        <v>-92.86</v>
       </c>
       <c r="L69" t="n">
-        <v>105.41</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-289.83</v>
+        <v>-264.63</v>
       </c>
       <c r="K71" t="n">
-        <v>-59.59</v>
+        <v>-54.41</v>
       </c>
       <c r="L71" t="n">
-        <v>295.9</v>
+        <v>270.17</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-184.95</v>
+        <v>-164.4</v>
       </c>
       <c r="K72" t="n">
-        <v>-33.31</v>
+        <v>-29.61</v>
       </c>
       <c r="L72" t="n">
-        <v>187.92</v>
+        <v>167.04</v>
       </c>
     </row>
     <row r="73">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>22.06</v>
+        <v>20.14</v>
       </c>
       <c r="K74" t="n">
-        <v>-35.01</v>
+        <v>-31.96</v>
       </c>
       <c r="L74" t="n">
-        <v>41.38</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>45.31</v>
+        <v>46.2</v>
       </c>
       <c r="K75" t="n">
-        <v>-14.39</v>
+        <v>-14.67</v>
       </c>
       <c r="L75" t="n">
-        <v>47.54</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>37.04</v>
+        <v>36.29</v>
       </c>
       <c r="K76" t="n">
-        <v>17.36</v>
+        <v>17</v>
       </c>
       <c r="L76" t="n">
-        <v>40.91</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-56.94</v>
+        <v>-54.57</v>
       </c>
       <c r="K77" t="n">
-        <v>-30.81</v>
+        <v>-29.53</v>
       </c>
       <c r="L77" t="n">
-        <v>64.73999999999999</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-83.03</v>
+        <v>-73.81</v>
       </c>
       <c r="K78" t="n">
-        <v>25.86</v>
+        <v>22.99</v>
       </c>
       <c r="L78" t="n">
-        <v>86.97</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>57.47</v>
+        <v>51.08</v>
       </c>
       <c r="K79" t="n">
-        <v>25.29</v>
+        <v>22.48</v>
       </c>
       <c r="L79" t="n">
-        <v>62.79</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>11.35</v>
+        <v>10.09</v>
       </c>
       <c r="K80" t="n">
-        <v>-77.75</v>
+        <v>-69.11</v>
       </c>
       <c r="L80" t="n">
-        <v>78.56999999999999</v>
+        <v>69.84</v>
       </c>
     </row>
     <row r="81">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="K82" t="n">
-        <v>-37.53</v>
+        <v>-34.26</v>
       </c>
       <c r="L82" t="n">
-        <v>37.53</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-114.16</v>
+        <v>-111.83</v>
       </c>
       <c r="K83" t="n">
-        <v>120.66</v>
+        <v>118.19</v>
       </c>
       <c r="L83" t="n">
-        <v>166.1</v>
+        <v>162.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-100.76</v>
+        <v>-98.7</v>
       </c>
       <c r="K84" t="n">
-        <v>46.02</v>
+        <v>45.08</v>
       </c>
       <c r="L84" t="n">
-        <v>110.77</v>
+        <v>108.51</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>52.95</v>
+        <v>47.07</v>
       </c>
       <c r="K85" t="n">
-        <v>135.13</v>
+        <v>120.12</v>
       </c>
       <c r="L85" t="n">
-        <v>145.14</v>
+        <v>129.01</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>255.88</v>
+        <v>227.45</v>
       </c>
       <c r="K86" t="n">
-        <v>27.84</v>
+        <v>24.75</v>
       </c>
       <c r="L86" t="n">
-        <v>257.39</v>
+        <v>228.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>67.09999999999999</v>
+        <v>59.64</v>
       </c>
       <c r="K87" t="n">
-        <v>172.86</v>
+        <v>153.65</v>
       </c>
       <c r="L87" t="n">
-        <v>185.42</v>
+        <v>164.82</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>151.82</v>
+        <v>142.13</v>
       </c>
       <c r="K88" t="n">
-        <v>34.99</v>
+        <v>32.76</v>
       </c>
       <c r="L88" t="n">
-        <v>155.8</v>
+        <v>145.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -628,31 +628,31 @@
         <v>1.11</v>
       </c>
       <c r="F14" t="n">
-        <v>4.8</v>
+        <v>5.97</v>
       </c>
       <c r="G14" t="n">
-        <v>160.4</v>
+        <v>168.3</v>
       </c>
       <c r="H14" t="n">
-        <v>88.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-63.27</v>
+        <v>33.09</v>
       </c>
       <c r="K14" t="n">
-        <v>16.61</v>
+        <v>-16.71</v>
       </c>
       <c r="L14" t="n">
-        <v>65.41</v>
+        <v>37.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:34:19</t>
+          <t>04:33:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.16</v>
+        <v>0.83</v>
       </c>
       <c r="F15" t="n">
-        <v>1.46</v>
+        <v>5.08</v>
       </c>
       <c r="G15" t="n">
-        <v>169.1</v>
+        <v>171.1</v>
       </c>
       <c r="H15" t="n">
-        <v>81.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>54.58</v>
+        <v>-37.57</v>
       </c>
       <c r="K15" t="n">
-        <v>14.36</v>
+        <v>-8.98</v>
       </c>
       <c r="L15" t="n">
-        <v>56.44</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:36:56</t>
+          <t>04:34:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="F16" t="n">
-        <v>6.67</v>
+        <v>2.17</v>
       </c>
       <c r="G16" t="n">
-        <v>165.9</v>
+        <v>141.7</v>
       </c>
       <c r="H16" t="n">
-        <v>86.7</v>
+        <v>26.7</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>29.63</v>
+        <v>12.7</v>
       </c>
       <c r="K16" t="n">
-        <v>1.04</v>
+        <v>20.24</v>
       </c>
       <c r="L16" t="n">
-        <v>29.64</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:41:54</t>
+          <t>04:39:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2</v>
+        <v>0.63</v>
       </c>
       <c r="F17" t="n">
-        <v>5.64</v>
+        <v>0.93</v>
       </c>
       <c r="G17" t="n">
-        <v>169.3</v>
+        <v>161.6</v>
       </c>
       <c r="H17" t="n">
-        <v>91.09999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.28</v>
+        <v>-1.49</v>
       </c>
       <c r="K17" t="n">
-        <v>47.29</v>
+        <v>-41.26</v>
       </c>
       <c r="L17" t="n">
-        <v>47.4</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:43:54</t>
+          <t>04:40:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.21</v>
+        <v>0.96</v>
       </c>
       <c r="F18" t="n">
-        <v>6.67</v>
+        <v>2.92</v>
       </c>
       <c r="G18" t="n">
-        <v>164.6</v>
+        <v>163</v>
       </c>
       <c r="H18" t="n">
-        <v>80</v>
+        <v>13.8</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>72.91</v>
+        <v>-45.46</v>
       </c>
       <c r="K18" t="n">
-        <v>64.84999999999999</v>
+        <v>-5.19</v>
       </c>
       <c r="L18" t="n">
-        <v>97.56999999999999</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:45:24</t>
+          <t>04:42:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="F19" t="n">
-        <v>3.48</v>
+        <v>5.9</v>
       </c>
       <c r="G19" t="n">
-        <v>168.5</v>
+        <v>151.3</v>
       </c>
       <c r="H19" t="n">
-        <v>81.90000000000001</v>
+        <v>35</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>32.43</v>
+        <v>-40.67</v>
       </c>
       <c r="K19" t="n">
-        <v>56.8</v>
+        <v>10.16</v>
       </c>
       <c r="L19" t="n">
-        <v>65.41</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:50:22</t>
+          <t>04:47:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="F20" t="n">
-        <v>1.53</v>
+        <v>4.35</v>
       </c>
       <c r="G20" t="n">
-        <v>157.5</v>
+        <v>156.5</v>
       </c>
       <c r="H20" t="n">
-        <v>87.8</v>
+        <v>93.8</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>24.88</v>
+        <v>0.76</v>
       </c>
       <c r="K20" t="n">
-        <v>-76.73</v>
+        <v>83.84</v>
       </c>
       <c r="L20" t="n">
-        <v>80.67</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:51:49</t>
+          <t>04:48:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0.97</v>
+        <v>1.42</v>
       </c>
       <c r="F21" t="n">
-        <v>1.27</v>
+        <v>6.67</v>
       </c>
       <c r="G21" t="n">
-        <v>149.4</v>
+        <v>160.9</v>
       </c>
       <c r="H21" t="n">
-        <v>82.40000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-43.93</v>
+        <v>73.78</v>
       </c>
       <c r="K21" t="n">
-        <v>-96.66</v>
+        <v>-26.6</v>
       </c>
       <c r="L21" t="n">
-        <v>106.17</v>
+        <v>78.43000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:53:38</t>
+          <t>04:49:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="F22" t="n">
-        <v>6.67</v>
+        <v>1.27</v>
       </c>
       <c r="G22" t="n">
-        <v>149.1</v>
+        <v>164.8</v>
       </c>
       <c r="H22" t="n">
-        <v>87</v>
+        <v>61.9</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>37.2</v>
+        <v>-12.11</v>
       </c>
       <c r="K22" t="n">
-        <v>-92.18000000000001</v>
+        <v>77.38</v>
       </c>
       <c r="L22" t="n">
-        <v>99.40000000000001</v>
+        <v>78.31999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:59:35</t>
+          <t>04:55:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>6.67</v>
+        <v>1.82</v>
       </c>
       <c r="G23" t="n">
-        <v>154.9</v>
+        <v>175.3</v>
       </c>
       <c r="H23" t="n">
-        <v>86.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-35.18</v>
+        <v>75.09</v>
       </c>
       <c r="K23" t="n">
-        <v>-193.68</v>
+        <v>-82.12</v>
       </c>
       <c r="L23" t="n">
-        <v>196.84</v>
+        <v>111.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:00:54</t>
+          <t>04:57:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="F24" t="n">
-        <v>1.55</v>
+        <v>4.21</v>
       </c>
       <c r="G24" t="n">
-        <v>172.6</v>
+        <v>155.4</v>
       </c>
       <c r="H24" t="n">
-        <v>89.09999999999999</v>
+        <v>48.6</v>
       </c>
       <c r="I24" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-61.95</v>
+        <v>154.61</v>
       </c>
       <c r="K24" t="n">
-        <v>79.39</v>
+        <v>-71.69</v>
       </c>
       <c r="L24" t="n">
-        <v>100.7</v>
+        <v>170.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:02:50</t>
+          <t>04:59:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="F25" t="n">
         <v>6.67</v>
       </c>
       <c r="G25" t="n">
-        <v>160.8</v>
+        <v>163.6</v>
       </c>
       <c r="H25" t="n">
-        <v>92.2</v>
+        <v>72.5</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>86.93000000000001</v>
+        <v>28.18</v>
       </c>
       <c r="K25" t="n">
-        <v>-195.9</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>214.32</v>
+        <v>94.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:07:38</t>
+          <t>05:04:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="F26" t="n">
-        <v>6.67</v>
+        <v>4.78</v>
       </c>
       <c r="G26" t="n">
-        <v>158.5</v>
+        <v>165.4</v>
       </c>
       <c r="H26" t="n">
-        <v>93.2</v>
+        <v>28.8</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>3.78</v>
+        <v>-143.16</v>
       </c>
       <c r="K26" t="n">
-        <v>-271.27</v>
+        <v>57.01</v>
       </c>
       <c r="L26" t="n">
-        <v>271.3</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:09:13</t>
+          <t>05:05:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="F27" t="n">
-        <v>6.67</v>
+        <v>5.47</v>
       </c>
       <c r="G27" t="n">
-        <v>168.5</v>
+        <v>162.4</v>
       </c>
       <c r="H27" t="n">
-        <v>86.59999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-13.65</v>
+        <v>-156.32</v>
       </c>
       <c r="K27" t="n">
-        <v>168.53</v>
+        <v>94.34</v>
       </c>
       <c r="L27" t="n">
-        <v>169.08</v>
+        <v>182.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:11:40</t>
+          <t>05:07:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>6.67</v>
+        <v>1.42</v>
       </c>
       <c r="G28" t="n">
-        <v>173.4</v>
+        <v>156</v>
       </c>
       <c r="H28" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-135.46</v>
+        <v>93.44</v>
       </c>
       <c r="K28" t="n">
-        <v>-156.56</v>
+        <v>10.3</v>
       </c>
       <c r="L28" t="n">
-        <v>207.03</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:23:39</t>
+          <t>05:18:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="F29" t="n">
-        <v>2.65</v>
+        <v>5.71</v>
       </c>
       <c r="G29" t="n">
-        <v>168</v>
+        <v>172.5</v>
       </c>
       <c r="H29" t="n">
-        <v>82.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-33.06</v>
+        <v>9.44</v>
       </c>
       <c r="K29" t="n">
-        <v>-14.57</v>
+        <v>-30.29</v>
       </c>
       <c r="L29" t="n">
-        <v>36.13</v>
+        <v>31.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:24:38</t>
+          <t>05:19:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="F30" t="n">
-        <v>6.48</v>
+        <v>5.33</v>
       </c>
       <c r="G30" t="n">
-        <v>152.2</v>
+        <v>156.8</v>
       </c>
       <c r="H30" t="n">
-        <v>84.5</v>
+        <v>63</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-40.78</v>
+        <v>37</v>
       </c>
       <c r="K30" t="n">
-        <v>56.49</v>
+        <v>-22.98</v>
       </c>
       <c r="L30" t="n">
-        <v>69.68000000000001</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:26:41</t>
+          <t>05:21:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="F31" t="n">
-        <v>6.67</v>
+        <v>6.15</v>
       </c>
       <c r="G31" t="n">
-        <v>154.5</v>
+        <v>164.2</v>
       </c>
       <c r="H31" t="n">
-        <v>79.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>1.4</v>
+        <v>30.03</v>
       </c>
       <c r="K31" t="n">
-        <v>-25.22</v>
+        <v>-5.48</v>
       </c>
       <c r="L31" t="n">
-        <v>25.26</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:31:59</t>
+          <t>05:27:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.98</v>
+        <v>1.19</v>
       </c>
       <c r="F32" t="n">
-        <v>2.47</v>
+        <v>3.39</v>
       </c>
       <c r="G32" t="n">
-        <v>152.8</v>
+        <v>158.6</v>
       </c>
       <c r="H32" t="n">
-        <v>82.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-46.56</v>
+        <v>-45.9</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.86</v>
+        <v>-25.13</v>
       </c>
       <c r="L32" t="n">
-        <v>46.6</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:32:48</t>
+          <t>05:29:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.89</v>
+        <v>1.26</v>
       </c>
       <c r="F33" t="n">
-        <v>4.45</v>
+        <v>3.19</v>
       </c>
       <c r="G33" t="n">
-        <v>168.4</v>
+        <v>166.6</v>
       </c>
       <c r="H33" t="n">
-        <v>87.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>3.85</v>
+        <v>32.19</v>
       </c>
       <c r="K33" t="n">
-        <v>-71.78</v>
+        <v>-8.25</v>
       </c>
       <c r="L33" t="n">
-        <v>71.88</v>
+        <v>33.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:34:32</t>
+          <t>05:31:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="F34" t="n">
-        <v>5.25</v>
+        <v>6.67</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4</v>
+        <v>165.6</v>
       </c>
       <c r="H34" t="n">
-        <v>89.90000000000001</v>
+        <v>52.1</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-30.55</v>
+        <v>-30.06</v>
       </c>
       <c r="K34" t="n">
-        <v>52.76</v>
+        <v>42.26</v>
       </c>
       <c r="L34" t="n">
-        <v>60.97</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:38:39</t>
+          <t>05:34:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="F35" t="n">
-        <v>5.98</v>
+        <v>3.87</v>
       </c>
       <c r="G35" t="n">
-        <v>167.4</v>
+        <v>165.2</v>
       </c>
       <c r="H35" t="n">
-        <v>92.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-45.1</v>
+        <v>-53.38</v>
       </c>
       <c r="K35" t="n">
-        <v>102.18</v>
+        <v>-42.33</v>
       </c>
       <c r="L35" t="n">
-        <v>111.69</v>
+        <v>68.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:40:49</t>
+          <t>05:36:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="F36" t="n">
-        <v>6.67</v>
+        <v>5.59</v>
       </c>
       <c r="G36" t="n">
-        <v>159.5</v>
+        <v>152.5</v>
       </c>
       <c r="H36" t="n">
-        <v>91.7</v>
+        <v>60.8</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>69.06999999999999</v>
+        <v>-81.09</v>
       </c>
       <c r="K36" t="n">
-        <v>-68.48999999999999</v>
+        <v>25.2</v>
       </c>
       <c r="L36" t="n">
-        <v>97.27</v>
+        <v>84.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:41:59</t>
+          <t>05:38:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="F37" t="n">
         <v>6.67</v>
       </c>
       <c r="G37" t="n">
-        <v>176.2</v>
+        <v>146.2</v>
       </c>
       <c r="H37" t="n">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>25.33</v>
+        <v>-55.1</v>
       </c>
       <c r="K37" t="n">
-        <v>-86.09999999999999</v>
+        <v>53.65</v>
       </c>
       <c r="L37" t="n">
-        <v>89.75</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:46:21</t>
+          <t>05:43:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="F38" t="n">
-        <v>4.36</v>
+        <v>1.66</v>
       </c>
       <c r="G38" t="n">
-        <v>162.8</v>
+        <v>172.9</v>
       </c>
       <c r="H38" t="n">
-        <v>86.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-150.81</v>
+        <v>174.25</v>
       </c>
       <c r="K38" t="n">
-        <v>-16.45</v>
+        <v>136.99</v>
       </c>
       <c r="L38" t="n">
-        <v>151.7</v>
+        <v>221.65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:48:43</t>
+          <t>05:45:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="F39" t="n">
-        <v>5.31</v>
+        <v>4.25</v>
       </c>
       <c r="G39" t="n">
-        <v>162.6</v>
+        <v>160.2</v>
       </c>
       <c r="H39" t="n">
-        <v>80.3</v>
+        <v>55.8</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>48.12</v>
+        <v>28.12</v>
       </c>
       <c r="K39" t="n">
-        <v>-115.55</v>
+        <v>-140.9</v>
       </c>
       <c r="L39" t="n">
-        <v>125.17</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:50:05</t>
+          <t>05:47:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="F40" t="n">
-        <v>5.96</v>
+        <v>6.67</v>
       </c>
       <c r="G40" t="n">
-        <v>157.6</v>
+        <v>163.2</v>
       </c>
       <c r="H40" t="n">
-        <v>85.5</v>
+        <v>52.8</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>110.59</v>
+        <v>-70.73</v>
       </c>
       <c r="K40" t="n">
-        <v>-149.09</v>
+        <v>106.96</v>
       </c>
       <c r="L40" t="n">
-        <v>185.63</v>
+        <v>128.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:54:21</t>
+          <t>05:52:35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="F41" t="n">
         <v>6.67</v>
       </c>
       <c r="G41" t="n">
-        <v>150.4</v>
+        <v>160.2</v>
       </c>
       <c r="H41" t="n">
-        <v>86.3</v>
+        <v>32.7</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-64.26000000000001</v>
+        <v>-68.73</v>
       </c>
       <c r="K41" t="n">
-        <v>183.35</v>
+        <v>-65.03</v>
       </c>
       <c r="L41" t="n">
-        <v>194.28</v>
+        <v>94.62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:55:43</t>
+          <t>05:54:49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="F42" t="n">
-        <v>6.27</v>
+        <v>2.61</v>
       </c>
       <c r="G42" t="n">
-        <v>157.4</v>
+        <v>164</v>
       </c>
       <c r="H42" t="n">
-        <v>86.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="I42" t="n">
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>190.67</v>
+        <v>-132.12</v>
       </c>
       <c r="K42" t="n">
-        <v>165</v>
+        <v>106.04</v>
       </c>
       <c r="L42" t="n">
-        <v>252.15</v>
+        <v>169.41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:57:37</t>
+          <t>05:56:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="F43" t="n">
-        <v>6.34</v>
+        <v>3.33</v>
       </c>
       <c r="G43" t="n">
-        <v>158.3</v>
+        <v>163.3</v>
       </c>
       <c r="H43" t="n">
-        <v>88</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>272.82</v>
+        <v>-150.97</v>
       </c>
       <c r="K43" t="n">
-        <v>-72.7</v>
+        <v>-84</v>
       </c>
       <c r="L43" t="n">
-        <v>282.34</v>
+        <v>172.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:08:27</t>
+          <t>06:07:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="F44" t="n">
-        <v>6.67</v>
+        <v>2.22</v>
       </c>
       <c r="G44" t="n">
-        <v>148.9</v>
+        <v>165.7</v>
       </c>
       <c r="H44" t="n">
-        <v>94.3</v>
+        <v>47.8</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>55.4</v>
+        <v>-27.11</v>
       </c>
       <c r="K44" t="n">
-        <v>-20.03</v>
+        <v>25.18</v>
       </c>
       <c r="L44" t="n">
-        <v>58.91</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:10:21</t>
+          <t>06:07:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="F45" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="G45" t="n">
-        <v>158</v>
+        <v>162.4</v>
       </c>
       <c r="H45" t="n">
-        <v>84.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>24.78</v>
+        <v>-20.8</v>
       </c>
       <c r="K45" t="n">
-        <v>-50.85</v>
+        <v>-32.05</v>
       </c>
       <c r="L45" t="n">
-        <v>56.56</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:11:53</t>
+          <t>06:09:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.55</v>
+        <v>0.98</v>
       </c>
       <c r="F46" t="n">
         <v>6.67</v>
       </c>
       <c r="G46" t="n">
-        <v>153</v>
+        <v>167.1</v>
       </c>
       <c r="H46" t="n">
-        <v>89.3</v>
+        <v>42.2</v>
       </c>
       <c r="I46" t="n">
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-32.72</v>
+        <v>-11.8</v>
       </c>
       <c r="K46" t="n">
-        <v>-29.73</v>
+        <v>-23.02</v>
       </c>
       <c r="L46" t="n">
-        <v>44.21</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:17:28</t>
+          <t>06:14:51</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="F47" t="n">
-        <v>2.68</v>
+        <v>5.34</v>
       </c>
       <c r="G47" t="n">
-        <v>165.5</v>
+        <v>157.2</v>
       </c>
       <c r="H47" t="n">
-        <v>90.5</v>
+        <v>45.4</v>
       </c>
       <c r="I47" t="n">
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>53.52</v>
+        <v>33.85</v>
       </c>
       <c r="K47" t="n">
-        <v>32.73</v>
+        <v>-51.53</v>
       </c>
       <c r="L47" t="n">
-        <v>62.74</v>
+        <v>61.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:19:53</t>
+          <t>06:16:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="F48" t="n">
-        <v>6.67</v>
+        <v>2.6</v>
       </c>
       <c r="G48" t="n">
-        <v>148.9</v>
+        <v>149.9</v>
       </c>
       <c r="H48" t="n">
-        <v>89.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>42.34</v>
+        <v>-15.96</v>
       </c>
       <c r="K48" t="n">
-        <v>-71.48</v>
+        <v>-38.48</v>
       </c>
       <c r="L48" t="n">
-        <v>83.08</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:21:16</t>
+          <t>06:18:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="F49" t="n">
-        <v>6.67</v>
+        <v>4.03</v>
       </c>
       <c r="G49" t="n">
-        <v>169.2</v>
+        <v>164.4</v>
       </c>
       <c r="H49" t="n">
-        <v>87.2</v>
+        <v>82.5</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>35.64</v>
+        <v>43.73</v>
       </c>
       <c r="K49" t="n">
-        <v>-60.63</v>
+        <v>24.89</v>
       </c>
       <c r="L49" t="n">
-        <v>70.33</v>
+        <v>50.32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:24:42</t>
+          <t>06:22:02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="F50" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="G50" t="n">
-        <v>158.4</v>
+        <v>164.6</v>
       </c>
       <c r="H50" t="n">
-        <v>76.2</v>
+        <v>60.4</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>66.59999999999999</v>
+        <v>-68.73</v>
       </c>
       <c r="K50" t="n">
-        <v>97.08</v>
+        <v>29.17</v>
       </c>
       <c r="L50" t="n">
-        <v>117.73</v>
+        <v>74.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:26:47</t>
+          <t>06:23:16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="F51" t="n">
-        <v>6.02</v>
+        <v>1.38</v>
       </c>
       <c r="G51" t="n">
-        <v>164</v>
+        <v>167.7</v>
       </c>
       <c r="H51" t="n">
-        <v>85.8</v>
+        <v>33.2</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>108.39</v>
+        <v>49.19</v>
       </c>
       <c r="K51" t="n">
-        <v>-133.6</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>172.04</v>
+        <v>81.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:27:59</t>
+          <t>06:25:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="F52" t="n">
-        <v>6.67</v>
+        <v>4.89</v>
       </c>
       <c r="G52" t="n">
-        <v>147.5</v>
+        <v>159.9</v>
       </c>
       <c r="H52" t="n">
-        <v>81.8</v>
+        <v>73.8</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>100.63</v>
+        <v>-37.1</v>
       </c>
       <c r="K52" t="n">
-        <v>10.74</v>
+        <v>-91.2</v>
       </c>
       <c r="L52" t="n">
-        <v>101.2</v>
+        <v>98.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:33:14</t>
+          <t>06:29:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="F53" t="n">
         <v>6.67</v>
       </c>
       <c r="G53" t="n">
-        <v>170.4</v>
+        <v>167.1</v>
       </c>
       <c r="H53" t="n">
-        <v>85.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-94.66</v>
+        <v>-89.08</v>
       </c>
       <c r="K53" t="n">
-        <v>64.06</v>
+        <v>-106.37</v>
       </c>
       <c r="L53" t="n">
-        <v>114.3</v>
+        <v>138.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:34:46</t>
+          <t>06:30:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="F54" t="n">
-        <v>4.5</v>
+        <v>5.79</v>
       </c>
       <c r="G54" t="n">
-        <v>159.9</v>
+        <v>159.4</v>
       </c>
       <c r="H54" t="n">
-        <v>94</v>
+        <v>52.8</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-92.52</v>
+        <v>114.67</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.13</v>
+        <v>-78.63</v>
       </c>
       <c r="L54" t="n">
-        <v>92.73</v>
+        <v>139.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:36:05</t>
+          <t>06:32:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="F55" t="n">
-        <v>6.67</v>
+        <v>6.27</v>
       </c>
       <c r="G55" t="n">
-        <v>146.3</v>
+        <v>154.7</v>
       </c>
       <c r="H55" t="n">
-        <v>83.3</v>
+        <v>64.7</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>228.94</v>
+        <v>107.3</v>
       </c>
       <c r="K55" t="n">
-        <v>-37.57</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>232</v>
+        <v>127.82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:40:04</t>
+          <t>06:37:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="F56" t="n">
-        <v>4.4</v>
+        <v>6.67</v>
       </c>
       <c r="G56" t="n">
-        <v>177.8</v>
+        <v>181.9</v>
       </c>
       <c r="H56" t="n">
-        <v>86.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-259.22</v>
+        <v>21.87</v>
       </c>
       <c r="K56" t="n">
-        <v>55.93</v>
+        <v>-172.01</v>
       </c>
       <c r="L56" t="n">
-        <v>265.19</v>
+        <v>173.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:41:44</t>
+          <t>06:38:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="F57" t="n">
-        <v>6.17</v>
+        <v>5.01</v>
       </c>
       <c r="G57" t="n">
-        <v>163.6</v>
+        <v>159.9</v>
       </c>
       <c r="H57" t="n">
-        <v>91.90000000000001</v>
+        <v>48.8</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>216.13</v>
+        <v>140.03</v>
       </c>
       <c r="K57" t="n">
-        <v>-268.93</v>
+        <v>19.95</v>
       </c>
       <c r="L57" t="n">
-        <v>345.02</v>
+        <v>141.45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:42:48</t>
+          <t>06:40:49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.63</v>
+        <v>1.12</v>
       </c>
       <c r="F58" t="n">
         <v>6.67</v>
       </c>
       <c r="G58" t="n">
-        <v>151.7</v>
+        <v>157.2</v>
       </c>
       <c r="H58" t="n">
-        <v>84.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>112.73</v>
+        <v>106.03</v>
       </c>
       <c r="K58" t="n">
-        <v>-102.92</v>
+        <v>-123.64</v>
       </c>
       <c r="L58" t="n">
-        <v>152.64</v>
+        <v>162.88</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:54:50</t>
+          <t>06:49:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="F59" t="n">
         <v>6.67</v>
       </c>
       <c r="G59" t="n">
-        <v>147.8</v>
+        <v>168.6</v>
       </c>
       <c r="H59" t="n">
-        <v>87.59999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>35.17</v>
+        <v>16.24</v>
       </c>
       <c r="K59" t="n">
-        <v>39.16</v>
+        <v>-27.1</v>
       </c>
       <c r="L59" t="n">
-        <v>52.63</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:56:13</t>
+          <t>06:51:20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="F60" t="n">
-        <v>6.67</v>
+        <v>4.85</v>
       </c>
       <c r="G60" t="n">
-        <v>166.4</v>
+        <v>167.2</v>
       </c>
       <c r="H60" t="n">
-        <v>82.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.31</v>
+        <v>-18.14</v>
       </c>
       <c r="K60" t="n">
-        <v>-50.67</v>
+        <v>-20.38</v>
       </c>
       <c r="L60" t="n">
-        <v>50.95</v>
+        <v>27.28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:57:38</t>
+          <t>06:53:25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.25</v>
+        <v>0.89</v>
       </c>
       <c r="F61" t="n">
-        <v>6.67</v>
+        <v>4.1</v>
       </c>
       <c r="G61" t="n">
-        <v>155.7</v>
+        <v>151.2</v>
       </c>
       <c r="H61" t="n">
-        <v>91.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="I61" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-49.45</v>
+        <v>-30.9</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.68</v>
+        <v>-27.56</v>
       </c>
       <c r="L61" t="n">
-        <v>49.77</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:01:30</t>
+          <t>06:57:49</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="F62" t="n">
-        <v>6.67</v>
+        <v>6.3</v>
       </c>
       <c r="G62" t="n">
-        <v>162.1</v>
+        <v>162.7</v>
       </c>
       <c r="H62" t="n">
-        <v>85.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-29.09</v>
+        <v>-35.78</v>
       </c>
       <c r="K62" t="n">
-        <v>57.04</v>
+        <v>34.82</v>
       </c>
       <c r="L62" t="n">
-        <v>64.03</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:04:05</t>
+          <t>06:58:49</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="F63" t="n">
-        <v>6.61</v>
+        <v>5.5</v>
       </c>
       <c r="G63" t="n">
-        <v>148.2</v>
+        <v>170.1</v>
       </c>
       <c r="H63" t="n">
-        <v>83.7</v>
+        <v>60.7</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>64.73</v>
+        <v>7.33</v>
       </c>
       <c r="K63" t="n">
-        <v>7.06</v>
+        <v>46.09</v>
       </c>
       <c r="L63" t="n">
-        <v>65.12</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:05:30</t>
+          <t>06:59:24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="F64" t="n">
         <v>6.67</v>
       </c>
       <c r="G64" t="n">
-        <v>167.2</v>
+        <v>172.2</v>
       </c>
       <c r="H64" t="n">
-        <v>88.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>16.46</v>
+        <v>6.51</v>
       </c>
       <c r="K64" t="n">
-        <v>-107.69</v>
+        <v>-44.74</v>
       </c>
       <c r="L64" t="n">
-        <v>108.94</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:11:42</t>
+          <t>07:04:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="F65" t="n">
-        <v>5.11</v>
+        <v>6.67</v>
       </c>
       <c r="G65" t="n">
-        <v>154.6</v>
+        <v>152.2</v>
       </c>
       <c r="H65" t="n">
-        <v>85.90000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>88.65000000000001</v>
+        <v>72.91</v>
       </c>
       <c r="K65" t="n">
-        <v>103.98</v>
+        <v>-45.57</v>
       </c>
       <c r="L65" t="n">
-        <v>136.64</v>
+        <v>85.98</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:13:52</t>
+          <t>07:05:46</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="F66" t="n">
         <v>6.67</v>
       </c>
       <c r="G66" t="n">
-        <v>165.6</v>
+        <v>167.4</v>
       </c>
       <c r="H66" t="n">
-        <v>85.2</v>
+        <v>80.2</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.12</v>
+        <v>-16.34</v>
       </c>
       <c r="K66" t="n">
-        <v>122.57</v>
+        <v>-69.56</v>
       </c>
       <c r="L66" t="n">
-        <v>123.9</v>
+        <v>71.45999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:16:14</t>
+          <t>07:07:55</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="F67" t="n">
-        <v>6.67</v>
+        <v>6.48</v>
       </c>
       <c r="G67" t="n">
-        <v>173.3</v>
+        <v>164.8</v>
       </c>
       <c r="H67" t="n">
-        <v>89.2</v>
+        <v>25.7</v>
       </c>
       <c r="I67" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>64.43000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-35.65</v>
+        <v>2.59</v>
       </c>
       <c r="L67" t="n">
-        <v>73.63</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:19:06</t>
+          <t>07:12:16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="F68" t="n">
-        <v>6.67</v>
+        <v>3.53</v>
       </c>
       <c r="G68" t="n">
-        <v>174.4</v>
+        <v>171.4</v>
       </c>
       <c r="H68" t="n">
-        <v>84.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>87.34999999999999</v>
+        <v>101.28</v>
       </c>
       <c r="K68" t="n">
-        <v>-148.18</v>
+        <v>-68.13</v>
       </c>
       <c r="L68" t="n">
-        <v>172.01</v>
+        <v>122.06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:21:35</t>
+          <t>07:14:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="F69" t="n">
-        <v>4.42</v>
+        <v>2.3</v>
       </c>
       <c r="G69" t="n">
-        <v>165.8</v>
+        <v>178.5</v>
       </c>
       <c r="H69" t="n">
-        <v>93.2</v>
+        <v>91.8</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-33.39</v>
+        <v>107.56</v>
       </c>
       <c r="K69" t="n">
-        <v>-92.86</v>
+        <v>-41.32</v>
       </c>
       <c r="L69" t="n">
-        <v>98.68000000000001</v>
+        <v>115.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:22:37</t>
+          <t>07:17:06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="F70" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>169.4</v>
+        <v>151.9</v>
       </c>
       <c r="H70" t="n">
-        <v>89.7</v>
+        <v>62.5</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>55.8</v>
+        <v>131.65</v>
       </c>
       <c r="K70" t="n">
-        <v>90.23</v>
+        <v>-6.94</v>
       </c>
       <c r="L70" t="n">
-        <v>106.09</v>
+        <v>131.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:26:45</t>
+          <t>07:23:17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="F71" t="n">
         <v>6.67</v>
       </c>
       <c r="G71" t="n">
-        <v>170</v>
+        <v>154.2</v>
       </c>
       <c r="H71" t="n">
-        <v>85.40000000000001</v>
+        <v>43.4</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-264.63</v>
+        <v>98.92</v>
       </c>
       <c r="K71" t="n">
-        <v>-54.41</v>
+        <v>125.38</v>
       </c>
       <c r="L71" t="n">
-        <v>270.17</v>
+        <v>159.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:27:25</t>
+          <t>07:25:07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="F72" t="n">
-        <v>1.94</v>
+        <v>5.77</v>
       </c>
       <c r="G72" t="n">
-        <v>167.5</v>
+        <v>157.5</v>
       </c>
       <c r="H72" t="n">
-        <v>74.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-164.4</v>
+        <v>-65.28</v>
       </c>
       <c r="K72" t="n">
-        <v>-29.61</v>
+        <v>107.48</v>
       </c>
       <c r="L72" t="n">
-        <v>167.04</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:29:27</t>
+          <t>07:27:26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="F73" t="n">
-        <v>6.67</v>
+        <v>2.2</v>
       </c>
       <c r="G73" t="n">
-        <v>165</v>
+        <v>172.4</v>
       </c>
       <c r="H73" t="n">
-        <v>86.09999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-72.7</v>
+        <v>106.09</v>
       </c>
       <c r="K73" t="n">
-        <v>-280.14</v>
+        <v>-0.64</v>
       </c>
       <c r="L73" t="n">
-        <v>289.42</v>
+        <v>106.09</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:39:06</t>
+          <t>07:37:37</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="F74" t="n">
-        <v>6.6</v>
+        <v>6.67</v>
       </c>
       <c r="G74" t="n">
-        <v>172</v>
+        <v>155.7</v>
       </c>
       <c r="H74" t="n">
-        <v>89</v>
+        <v>20.9</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>20.14</v>
+        <v>-28.51</v>
       </c>
       <c r="K74" t="n">
-        <v>-31.96</v>
+        <v>1.43</v>
       </c>
       <c r="L74" t="n">
-        <v>37.78</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:41:20</t>
+          <t>07:39:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="F75" t="n">
         <v>6.67</v>
       </c>
       <c r="G75" t="n">
-        <v>153.4</v>
+        <v>173.7</v>
       </c>
       <c r="H75" t="n">
-        <v>88.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>46.2</v>
+        <v>-20.98</v>
       </c>
       <c r="K75" t="n">
-        <v>-14.67</v>
+        <v>26.08</v>
       </c>
       <c r="L75" t="n">
-        <v>48.47</v>
+        <v>33.47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:43:38</t>
+          <t>07:40:52</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="F76" t="n">
-        <v>2.44</v>
+        <v>5.01</v>
       </c>
       <c r="G76" t="n">
-        <v>168.7</v>
+        <v>161.1</v>
       </c>
       <c r="H76" t="n">
-        <v>91.2</v>
+        <v>73.7</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>36.29</v>
+        <v>4.63</v>
       </c>
       <c r="K76" t="n">
-        <v>17</v>
+        <v>26.14</v>
       </c>
       <c r="L76" t="n">
-        <v>40.07</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:47:49</t>
+          <t>07:44:59</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="F77" t="n">
-        <v>1.53</v>
+        <v>6.67</v>
       </c>
       <c r="G77" t="n">
-        <v>148.8</v>
+        <v>161.9</v>
       </c>
       <c r="H77" t="n">
-        <v>83.90000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-54.57</v>
+        <v>19.62</v>
       </c>
       <c r="K77" t="n">
-        <v>-29.53</v>
+        <v>-49.41</v>
       </c>
       <c r="L77" t="n">
-        <v>62.05</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:49:48</t>
+          <t>07:46:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="F78" t="n">
         <v>6.67</v>
       </c>
       <c r="G78" t="n">
-        <v>168.9</v>
+        <v>163.4</v>
       </c>
       <c r="H78" t="n">
-        <v>86.7</v>
+        <v>18.7</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-73.81</v>
+        <v>48.86</v>
       </c>
       <c r="K78" t="n">
-        <v>22.99</v>
+        <v>4.63</v>
       </c>
       <c r="L78" t="n">
-        <v>77.3</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:51:25</t>
+          <t>07:47:46</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="F79" t="n">
-        <v>6.67</v>
+        <v>5.86</v>
       </c>
       <c r="G79" t="n">
-        <v>168.7</v>
+        <v>160</v>
       </c>
       <c r="H79" t="n">
-        <v>90.3</v>
+        <v>51.7</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>51.08</v>
+        <v>38.4</v>
       </c>
       <c r="K79" t="n">
-        <v>22.48</v>
+        <v>-23.69</v>
       </c>
       <c r="L79" t="n">
-        <v>55.81</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:56:34</t>
+          <t>07:53:29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="F80" t="n">
-        <v>5.87</v>
+        <v>6.67</v>
       </c>
       <c r="G80" t="n">
-        <v>161</v>
+        <v>166.4</v>
       </c>
       <c r="H80" t="n">
-        <v>88.8</v>
+        <v>55.2</v>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>10.09</v>
+        <v>60.26</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.11</v>
+        <v>-32.38</v>
       </c>
       <c r="L80" t="n">
-        <v>69.84</v>
+        <v>68.41</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:58:42</t>
+          <t>07:55:59</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="F81" t="n">
-        <v>6.31</v>
+        <v>3.07</v>
       </c>
       <c r="G81" t="n">
-        <v>156.3</v>
+        <v>164.7</v>
       </c>
       <c r="H81" t="n">
-        <v>85.7</v>
+        <v>33.5</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>106.98</v>
+        <v>33.96</v>
       </c>
       <c r="K81" t="n">
-        <v>-1.44</v>
+        <v>44.04</v>
       </c>
       <c r="L81" t="n">
-        <v>106.99</v>
+        <v>55.62</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:00:38</t>
+          <t>07:56:45</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="F82" t="n">
-        <v>1.36</v>
+        <v>6.67</v>
       </c>
       <c r="G82" t="n">
-        <v>157.1</v>
+        <v>159.8</v>
       </c>
       <c r="H82" t="n">
-        <v>89.3</v>
+        <v>30.5</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>0.08</v>
+        <v>63.7</v>
       </c>
       <c r="K82" t="n">
-        <v>-34.26</v>
+        <v>47.34</v>
       </c>
       <c r="L82" t="n">
-        <v>34.26</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:05:16</t>
+          <t>08:00:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.41</v>
+        <v>2.17</v>
       </c>
       <c r="F83" t="n">
         <v>6.67</v>
       </c>
       <c r="G83" t="n">
-        <v>155.2</v>
+        <v>159.5</v>
       </c>
       <c r="H83" t="n">
-        <v>87.5</v>
+        <v>30.6</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-111.83</v>
+        <v>-105.31</v>
       </c>
       <c r="K83" t="n">
-        <v>118.19</v>
+        <v>19.11</v>
       </c>
       <c r="L83" t="n">
-        <v>162.71</v>
+        <v>107.03</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:06:16</t>
+          <t>08:02:43</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.1</v>
+        <v>1.49</v>
       </c>
       <c r="F84" t="n">
-        <v>1.4</v>
+        <v>5.32</v>
       </c>
       <c r="G84" t="n">
-        <v>157.5</v>
+        <v>144.4</v>
       </c>
       <c r="H84" t="n">
-        <v>88.2</v>
+        <v>55.7</v>
       </c>
       <c r="I84" t="n">
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-98.7</v>
+        <v>63.01</v>
       </c>
       <c r="K84" t="n">
-        <v>45.08</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>108.51</v>
+        <v>105.09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:08:16</t>
+          <t>08:05:16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.34</v>
+        <v>1.36</v>
       </c>
       <c r="F85" t="n">
         <v>6.67</v>
       </c>
       <c r="G85" t="n">
-        <v>165.3</v>
+        <v>159.6</v>
       </c>
       <c r="H85" t="n">
-        <v>82.2</v>
+        <v>57.1</v>
       </c>
       <c r="I85" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>47.07</v>
+        <v>115.85</v>
       </c>
       <c r="K85" t="n">
-        <v>120.12</v>
+        <v>-78.56999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>129.01</v>
+        <v>139.98</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:13:18</t>
+          <t>08:10:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="F86" t="n">
-        <v>5.12</v>
+        <v>2.44</v>
       </c>
       <c r="G86" t="n">
-        <v>165.8</v>
+        <v>169</v>
       </c>
       <c r="H86" t="n">
-        <v>86.7</v>
+        <v>73.2</v>
       </c>
       <c r="I86" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>227.45</v>
+        <v>-135.08</v>
       </c>
       <c r="K86" t="n">
-        <v>24.75</v>
+        <v>-104.78</v>
       </c>
       <c r="L86" t="n">
-        <v>228.79</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:15:10</t>
+          <t>08:12:28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="F87" t="n">
-        <v>6.67</v>
+        <v>4.21</v>
       </c>
       <c r="G87" t="n">
-        <v>168.1</v>
+        <v>151.6</v>
       </c>
       <c r="H87" t="n">
-        <v>83.90000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="I87" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>59.64</v>
+        <v>101.91</v>
       </c>
       <c r="K87" t="n">
-        <v>153.65</v>
+        <v>-138.17</v>
       </c>
       <c r="L87" t="n">
-        <v>164.82</v>
+        <v>171.69</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:17:12</t>
+          <t>08:14:03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="F88" t="n">
-        <v>5.12</v>
+        <v>4.55</v>
       </c>
       <c r="G88" t="n">
-        <v>158.2</v>
+        <v>167.9</v>
       </c>
       <c r="H88" t="n">
-        <v>90.7</v>
+        <v>48.6</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>142.13</v>
+        <v>-91.05</v>
       </c>
       <c r="K88" t="n">
-        <v>32.76</v>
+        <v>145.88</v>
       </c>
       <c r="L88" t="n">
-        <v>145.86</v>
+        <v>171.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="F14" t="n">
-        <v>5.97</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>168.3</v>
+        <v>173.7</v>
       </c>
       <c r="H14" t="n">
-        <v>69.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>33.09</v>
+        <v>29.47</v>
       </c>
       <c r="K14" t="n">
-        <v>-16.71</v>
+        <v>10.52</v>
       </c>
       <c r="L14" t="n">
-        <v>37.07</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:33:24</t>
+          <t>04:34:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.83</v>
+        <v>1.24</v>
       </c>
       <c r="F15" t="n">
-        <v>5.08</v>
+        <v>3.81</v>
       </c>
       <c r="G15" t="n">
-        <v>171.1</v>
+        <v>163.1</v>
       </c>
       <c r="H15" t="n">
-        <v>85.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-37.57</v>
+        <v>-2.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.98</v>
+        <v>-37.36</v>
       </c>
       <c r="L15" t="n">
-        <v>38.63</v>
+        <v>37.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:34:42</t>
+          <t>04:36:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="F16" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="G16" t="n">
-        <v>141.7</v>
+        <v>166.7</v>
       </c>
       <c r="H16" t="n">
-        <v>26.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>12.7</v>
+        <v>-38.77</v>
       </c>
       <c r="K16" t="n">
-        <v>20.24</v>
+        <v>-2.6</v>
       </c>
       <c r="L16" t="n">
-        <v>23.9</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:39:14</t>
+          <t>04:40:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.63</v>
+        <v>1.15</v>
       </c>
       <c r="F17" t="n">
-        <v>0.93</v>
+        <v>6.67</v>
       </c>
       <c r="G17" t="n">
-        <v>161.6</v>
+        <v>172.7</v>
       </c>
       <c r="H17" t="n">
-        <v>57.6</v>
+        <v>49.3</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.49</v>
+        <v>-34.19</v>
       </c>
       <c r="K17" t="n">
-        <v>-41.26</v>
+        <v>-41.11</v>
       </c>
       <c r="L17" t="n">
-        <v>41.28</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:40:39</t>
+          <t>04:43:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.96</v>
+        <v>1.38</v>
       </c>
       <c r="F18" t="n">
-        <v>2.92</v>
+        <v>6.67</v>
       </c>
       <c r="G18" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H18" t="n">
-        <v>13.8</v>
+        <v>51.9</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-45.46</v>
+        <v>-39.86</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.19</v>
+        <v>14.31</v>
       </c>
       <c r="L18" t="n">
-        <v>45.76</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:42:24</t>
+          <t>04:45:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="F19" t="n">
-        <v>5.9</v>
+        <v>6.67</v>
       </c>
       <c r="G19" t="n">
-        <v>151.3</v>
+        <v>149.3</v>
       </c>
       <c r="H19" t="n">
-        <v>35</v>
+        <v>83.5</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-40.67</v>
+        <v>-13.51</v>
       </c>
       <c r="K19" t="n">
-        <v>10.16</v>
+        <v>-50.33</v>
       </c>
       <c r="L19" t="n">
-        <v>41.92</v>
+        <v>52.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:47:19</t>
+          <t>04:49:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.43</v>
+        <v>0.98</v>
       </c>
       <c r="F20" t="n">
-        <v>4.35</v>
+        <v>4.91</v>
       </c>
       <c r="G20" t="n">
-        <v>156.5</v>
+        <v>162.9</v>
       </c>
       <c r="H20" t="n">
-        <v>93.8</v>
+        <v>54.3</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>0.76</v>
+        <v>66.98</v>
       </c>
       <c r="K20" t="n">
-        <v>83.84</v>
+        <v>55.85</v>
       </c>
       <c r="L20" t="n">
-        <v>83.84</v>
+        <v>87.20999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:48:19</t>
+          <t>04:52:48</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="F21" t="n">
-        <v>6.67</v>
+        <v>5.47</v>
       </c>
       <c r="G21" t="n">
-        <v>160.9</v>
+        <v>168.4</v>
       </c>
       <c r="H21" t="n">
-        <v>55.1</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>73.78</v>
+        <v>57.85</v>
       </c>
       <c r="K21" t="n">
-        <v>-26.6</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>78.43000000000001</v>
+        <v>96.56999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:49:57</t>
+          <t>04:53:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.97</v>
+        <v>1.12</v>
       </c>
       <c r="F22" t="n">
-        <v>1.27</v>
+        <v>3.45</v>
       </c>
       <c r="G22" t="n">
-        <v>164.8</v>
+        <v>156.2</v>
       </c>
       <c r="H22" t="n">
-        <v>61.9</v>
+        <v>49.6</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>-12.11</v>
+        <v>-10.28</v>
       </c>
       <c r="K22" t="n">
-        <v>77.38</v>
+        <v>-83.78</v>
       </c>
       <c r="L22" t="n">
-        <v>78.31999999999999</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:55:13</t>
+          <t>04:57:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.82</v>
+        <v>3.57</v>
       </c>
       <c r="G23" t="n">
-        <v>175.3</v>
+        <v>176.7</v>
       </c>
       <c r="H23" t="n">
-        <v>54.8</v>
+        <v>43.8</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>75.09</v>
+        <v>79.11</v>
       </c>
       <c r="K23" t="n">
-        <v>-82.12</v>
+        <v>-81.2</v>
       </c>
       <c r="L23" t="n">
-        <v>111.28</v>
+        <v>113.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:57:43</t>
+          <t>04:59:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="F24" t="n">
-        <v>4.21</v>
+        <v>2.13</v>
       </c>
       <c r="G24" t="n">
-        <v>155.4</v>
+        <v>152.1</v>
       </c>
       <c r="H24" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>154.61</v>
+        <v>-73.26000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-71.69</v>
+        <v>64.92</v>
       </c>
       <c r="L24" t="n">
-        <v>170.42</v>
+        <v>97.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:59:39</t>
+          <t>05:01:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="F25" t="n">
         <v>6.67</v>
       </c>
       <c r="G25" t="n">
-        <v>163.6</v>
+        <v>164.2</v>
       </c>
       <c r="H25" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>28.18</v>
+        <v>34.64</v>
       </c>
       <c r="K25" t="n">
-        <v>90.18000000000001</v>
+        <v>-102.9</v>
       </c>
       <c r="L25" t="n">
-        <v>94.48</v>
+        <v>108.57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:04:26</t>
+          <t>05:05:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.28</v>
+        <v>0.91</v>
       </c>
       <c r="F26" t="n">
-        <v>4.78</v>
+        <v>2.59</v>
       </c>
       <c r="G26" t="n">
-        <v>165.4</v>
+        <v>165.2</v>
       </c>
       <c r="H26" t="n">
-        <v>28.8</v>
+        <v>80.8</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-143.16</v>
+        <v>170.33</v>
       </c>
       <c r="K26" t="n">
-        <v>57.01</v>
+        <v>-51.78</v>
       </c>
       <c r="L26" t="n">
-        <v>154.1</v>
+        <v>178.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:05:53</t>
+          <t>05:06:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.29</v>
+        <v>0.98</v>
       </c>
       <c r="F27" t="n">
-        <v>5.47</v>
+        <v>6.08</v>
       </c>
       <c r="G27" t="n">
-        <v>162.4</v>
+        <v>158.8</v>
       </c>
       <c r="H27" t="n">
-        <v>63.9</v>
+        <v>58.8</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-156.32</v>
+        <v>143.48</v>
       </c>
       <c r="K27" t="n">
-        <v>94.34</v>
+        <v>-27.54</v>
       </c>
       <c r="L27" t="n">
-        <v>182.58</v>
+        <v>146.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:07:08</t>
+          <t>05:08:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1.42</v>
+        <v>3.75</v>
       </c>
       <c r="G28" t="n">
-        <v>156</v>
+        <v>172.5</v>
       </c>
       <c r="H28" t="n">
-        <v>95.5</v>
+        <v>52.6</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>93.44</v>
+        <v>-125.9</v>
       </c>
       <c r="K28" t="n">
-        <v>10.3</v>
+        <v>37.76</v>
       </c>
       <c r="L28" t="n">
-        <v>94</v>
+        <v>131.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:18:36</t>
+          <t>05:17:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="F29" t="n">
-        <v>5.71</v>
+        <v>1.35</v>
       </c>
       <c r="G29" t="n">
-        <v>172.5</v>
+        <v>166.6</v>
       </c>
       <c r="H29" t="n">
-        <v>70.09999999999999</v>
+        <v>48.2</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>9.44</v>
+        <v>-3.66</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.29</v>
+        <v>32.67</v>
       </c>
       <c r="L29" t="n">
-        <v>31.72</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:19:50</t>
+          <t>05:18:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.92</v>
+        <v>1.09</v>
       </c>
       <c r="F30" t="n">
-        <v>5.33</v>
+        <v>6.33</v>
       </c>
       <c r="G30" t="n">
-        <v>156.8</v>
+        <v>156.4</v>
       </c>
       <c r="H30" t="n">
-        <v>63</v>
+        <v>48.7</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>37</v>
+        <v>-31.14</v>
       </c>
       <c r="K30" t="n">
-        <v>-22.98</v>
+        <v>-5.74</v>
       </c>
       <c r="L30" t="n">
-        <v>43.55</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:21:30</t>
+          <t>05:20:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.36</v>
+        <v>0.76</v>
       </c>
       <c r="F31" t="n">
-        <v>6.15</v>
+        <v>4.07</v>
       </c>
       <c r="G31" t="n">
-        <v>164.2</v>
+        <v>147.5</v>
       </c>
       <c r="H31" t="n">
-        <v>99.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>30.03</v>
+        <v>18.75</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.48</v>
+        <v>6.5</v>
       </c>
       <c r="L31" t="n">
-        <v>30.53</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:27:26</t>
+          <t>05:23:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="F32" t="n">
-        <v>3.39</v>
+        <v>4.88</v>
       </c>
       <c r="G32" t="n">
-        <v>158.6</v>
+        <v>164.4</v>
       </c>
       <c r="H32" t="n">
-        <v>81.40000000000001</v>
+        <v>48.6</v>
       </c>
       <c r="I32" t="n">
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-45.9</v>
+        <v>14.57</v>
       </c>
       <c r="K32" t="n">
-        <v>-25.13</v>
+        <v>-43.83</v>
       </c>
       <c r="L32" t="n">
-        <v>52.33</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:29:14</t>
+          <t>05:24:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="F33" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="G33" t="n">
-        <v>166.6</v>
+        <v>164.6</v>
       </c>
       <c r="H33" t="n">
-        <v>64.7</v>
+        <v>78.2</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>32.19</v>
+        <v>35.87</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.25</v>
+        <v>-11.57</v>
       </c>
       <c r="L33" t="n">
-        <v>33.23</v>
+        <v>37.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:31:13</t>
+          <t>05:26:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="F34" t="n">
-        <v>6.67</v>
+        <v>4.37</v>
       </c>
       <c r="G34" t="n">
-        <v>165.6</v>
+        <v>153.6</v>
       </c>
       <c r="H34" t="n">
-        <v>52.1</v>
+        <v>53.9</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>-30.06</v>
+        <v>48.24</v>
       </c>
       <c r="K34" t="n">
-        <v>42.26</v>
+        <v>7.89</v>
       </c>
       <c r="L34" t="n">
-        <v>51.86</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:34:21</t>
+          <t>05:32:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>3.87</v>
+        <v>4.07</v>
       </c>
       <c r="G35" t="n">
-        <v>165.2</v>
+        <v>169</v>
       </c>
       <c r="H35" t="n">
-        <v>74.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-53.38</v>
+        <v>-5.05</v>
       </c>
       <c r="K35" t="n">
-        <v>-42.33</v>
+        <v>26.6</v>
       </c>
       <c r="L35" t="n">
-        <v>68.13</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:36:52</t>
+          <t>05:33:49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="F36" t="n">
-        <v>5.59</v>
+        <v>4.99</v>
       </c>
       <c r="G36" t="n">
-        <v>152.5</v>
+        <v>154.9</v>
       </c>
       <c r="H36" t="n">
-        <v>60.8</v>
+        <v>50.7</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-81.09</v>
+        <v>-75.23</v>
       </c>
       <c r="K36" t="n">
-        <v>25.2</v>
+        <v>28.22</v>
       </c>
       <c r="L36" t="n">
-        <v>84.92</v>
+        <v>80.34999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:38:10</t>
+          <t>05:36:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="F37" t="n">
         <v>6.67</v>
       </c>
       <c r="G37" t="n">
-        <v>146.2</v>
+        <v>154.7</v>
       </c>
       <c r="H37" t="n">
-        <v>87.5</v>
+        <v>63.7</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>-55.1</v>
+        <v>25.31</v>
       </c>
       <c r="K37" t="n">
-        <v>53.65</v>
+        <v>47.72</v>
       </c>
       <c r="L37" t="n">
-        <v>76.90000000000001</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:43:50</t>
+          <t>05:41:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="F38" t="n">
-        <v>1.66</v>
+        <v>4.88</v>
       </c>
       <c r="G38" t="n">
-        <v>172.9</v>
+        <v>142</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>22.4</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>174.25</v>
+        <v>60.51</v>
       </c>
       <c r="K38" t="n">
-        <v>136.99</v>
+        <v>-48.87</v>
       </c>
       <c r="L38" t="n">
-        <v>221.65</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:45:04</t>
+          <t>05:43:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="F39" t="n">
-        <v>4.25</v>
+        <v>6.67</v>
       </c>
       <c r="G39" t="n">
-        <v>160.2</v>
+        <v>172.1</v>
       </c>
       <c r="H39" t="n">
-        <v>55.8</v>
+        <v>72.5</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>28.12</v>
+        <v>75.31</v>
       </c>
       <c r="K39" t="n">
-        <v>-140.9</v>
+        <v>-36.58</v>
       </c>
       <c r="L39" t="n">
-        <v>143.68</v>
+        <v>83.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:47:24</t>
+          <t>05:45:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="F40" t="n">
-        <v>6.67</v>
+        <v>6.16</v>
       </c>
       <c r="G40" t="n">
-        <v>163.2</v>
+        <v>164.5</v>
       </c>
       <c r="H40" t="n">
-        <v>52.8</v>
+        <v>67</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-70.73</v>
+        <v>24.16</v>
       </c>
       <c r="K40" t="n">
-        <v>106.96</v>
+        <v>-41.7</v>
       </c>
       <c r="L40" t="n">
-        <v>128.23</v>
+        <v>48.19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:52:35</t>
+          <t>05:50:07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="F41" t="n">
-        <v>6.67</v>
+        <v>2.26</v>
       </c>
       <c r="G41" t="n">
-        <v>160.2</v>
+        <v>160.6</v>
       </c>
       <c r="H41" t="n">
-        <v>32.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-68.73</v>
+        <v>51.46</v>
       </c>
       <c r="K41" t="n">
-        <v>-65.03</v>
+        <v>-132.7</v>
       </c>
       <c r="L41" t="n">
-        <v>94.62</v>
+        <v>142.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:54:49</t>
+          <t>05:51:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="F42" t="n">
-        <v>2.61</v>
+        <v>6.67</v>
       </c>
       <c r="G42" t="n">
-        <v>164</v>
+        <v>151.3</v>
       </c>
       <c r="H42" t="n">
-        <v>68.3</v>
+        <v>59.1</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-132.12</v>
+        <v>71.05</v>
       </c>
       <c r="K42" t="n">
-        <v>106.04</v>
+        <v>-108.89</v>
       </c>
       <c r="L42" t="n">
-        <v>169.41</v>
+        <v>130.02</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:56:17</t>
+          <t>05:52:39</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="F43" t="n">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="G43" t="n">
-        <v>163.3</v>
+        <v>145.4</v>
       </c>
       <c r="H43" t="n">
-        <v>74.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-150.97</v>
+        <v>127.17</v>
       </c>
       <c r="K43" t="n">
-        <v>-84</v>
+        <v>132.87</v>
       </c>
       <c r="L43" t="n">
-        <v>172.77</v>
+        <v>183.93</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:07:03</t>
+          <t>06:03:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="F44" t="n">
-        <v>2.22</v>
+        <v>1.38</v>
       </c>
       <c r="G44" t="n">
-        <v>165.7</v>
+        <v>147.6</v>
       </c>
       <c r="H44" t="n">
-        <v>47.8</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-27.11</v>
+        <v>-2.91</v>
       </c>
       <c r="K44" t="n">
-        <v>25.18</v>
+        <v>-23.98</v>
       </c>
       <c r="L44" t="n">
-        <v>37.01</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:07:46</t>
+          <t>06:05:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="F45" t="n">
-        <v>1.6</v>
+        <v>4.42</v>
       </c>
       <c r="G45" t="n">
-        <v>162.4</v>
+        <v>158.7</v>
       </c>
       <c r="H45" t="n">
-        <v>75.09999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>-20.8</v>
+        <v>-8.34</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.05</v>
+        <v>28.26</v>
       </c>
       <c r="L45" t="n">
-        <v>38.2</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:09:34</t>
+          <t>06:07:06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.98</v>
+        <v>1.18</v>
       </c>
       <c r="F46" t="n">
-        <v>6.67</v>
+        <v>5.84</v>
       </c>
       <c r="G46" t="n">
-        <v>167.1</v>
+        <v>160.5</v>
       </c>
       <c r="H46" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.8</v>
+        <v>-13</v>
       </c>
       <c r="K46" t="n">
-        <v>-23.02</v>
+        <v>25.4</v>
       </c>
       <c r="L46" t="n">
-        <v>25.87</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:14:51</t>
+          <t>06:13:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F47" t="n">
-        <v>5.34</v>
+        <v>2.46</v>
       </c>
       <c r="G47" t="n">
-        <v>157.2</v>
+        <v>182</v>
       </c>
       <c r="H47" t="n">
-        <v>45.4</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>33.85</v>
+        <v>33.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-51.53</v>
+        <v>34.7</v>
       </c>
       <c r="L47" t="n">
-        <v>61.65</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:16:57</t>
+          <t>06:14:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="F48" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="G48" t="n">
-        <v>149.9</v>
+        <v>159.8</v>
       </c>
       <c r="H48" t="n">
-        <v>71.2</v>
+        <v>39.7</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-15.96</v>
+        <v>35.61</v>
       </c>
       <c r="K48" t="n">
-        <v>-38.48</v>
+        <v>-36.33</v>
       </c>
       <c r="L48" t="n">
-        <v>41.66</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:18:46</t>
+          <t>06:15:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="F49" t="n">
-        <v>4.03</v>
+        <v>6.25</v>
       </c>
       <c r="G49" t="n">
-        <v>164.4</v>
+        <v>152.8</v>
       </c>
       <c r="H49" t="n">
-        <v>82.5</v>
+        <v>42</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>43.73</v>
+        <v>-17.87</v>
       </c>
       <c r="K49" t="n">
-        <v>24.89</v>
+        <v>-43.64</v>
       </c>
       <c r="L49" t="n">
-        <v>50.32</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:22:02</t>
+          <t>06:21:02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="F50" t="n">
-        <v>2.1</v>
+        <v>5.93</v>
       </c>
       <c r="G50" t="n">
-        <v>164.6</v>
+        <v>151.5</v>
       </c>
       <c r="H50" t="n">
-        <v>60.4</v>
+        <v>86</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-68.73</v>
+        <v>40.5</v>
       </c>
       <c r="K50" t="n">
-        <v>29.17</v>
+        <v>-44.83</v>
       </c>
       <c r="L50" t="n">
-        <v>74.66</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:23:16</t>
+          <t>06:23:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="F51" t="n">
-        <v>1.38</v>
+        <v>4.44</v>
       </c>
       <c r="G51" t="n">
-        <v>167.7</v>
+        <v>154.5</v>
       </c>
       <c r="H51" t="n">
-        <v>33.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>49.19</v>
+        <v>37.84</v>
       </c>
       <c r="K51" t="n">
-        <v>64.51000000000001</v>
+        <v>-46.05</v>
       </c>
       <c r="L51" t="n">
-        <v>81.12</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:25:06</t>
+          <t>06:24:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="F52" t="n">
-        <v>4.89</v>
+        <v>3.63</v>
       </c>
       <c r="G52" t="n">
-        <v>159.9</v>
+        <v>158.5</v>
       </c>
       <c r="H52" t="n">
-        <v>73.8</v>
+        <v>93.8</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-37.1</v>
+        <v>-51.79</v>
       </c>
       <c r="K52" t="n">
-        <v>-91.2</v>
+        <v>-34.27</v>
       </c>
       <c r="L52" t="n">
-        <v>98.45</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:29:43</t>
+          <t>06:28:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="F53" t="n">
         <v>6.67</v>
       </c>
       <c r="G53" t="n">
-        <v>167.1</v>
+        <v>167.3</v>
       </c>
       <c r="H53" t="n">
-        <v>84.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J53" t="n">
-        <v>-89.08</v>
+        <v>106.54</v>
       </c>
       <c r="K53" t="n">
-        <v>-106.37</v>
+        <v>-30.86</v>
       </c>
       <c r="L53" t="n">
-        <v>138.74</v>
+        <v>110.92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:30:55</t>
+          <t>06:30:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="F54" t="n">
-        <v>5.79</v>
+        <v>6.67</v>
       </c>
       <c r="G54" t="n">
-        <v>159.4</v>
+        <v>156.4</v>
       </c>
       <c r="H54" t="n">
-        <v>52.8</v>
+        <v>78.7</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>114.67</v>
+        <v>-86.34999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-78.63</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>139.03</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:32:22</t>
+          <t>06:31:52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="F55" t="n">
-        <v>6.27</v>
+        <v>6.35</v>
       </c>
       <c r="G55" t="n">
-        <v>154.7</v>
+        <v>156.2</v>
       </c>
       <c r="H55" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>107.3</v>
+        <v>90.09</v>
       </c>
       <c r="K55" t="n">
-        <v>69.45999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="L55" t="n">
-        <v>127.82</v>
+        <v>118.46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:37:00</t>
+          <t>06:37:51</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.66</v>
+        <v>1.1</v>
       </c>
       <c r="F56" t="n">
-        <v>6.67</v>
+        <v>3.25</v>
       </c>
       <c r="G56" t="n">
-        <v>181.9</v>
+        <v>163.8</v>
       </c>
       <c r="H56" t="n">
-        <v>77.90000000000001</v>
+        <v>35.1</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>21.87</v>
+        <v>76.72</v>
       </c>
       <c r="K56" t="n">
-        <v>-172.01</v>
+        <v>-166.45</v>
       </c>
       <c r="L56" t="n">
-        <v>173.4</v>
+        <v>183.28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:38:27</t>
+          <t>06:39:09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="F57" t="n">
-        <v>5.01</v>
+        <v>6.67</v>
       </c>
       <c r="G57" t="n">
-        <v>159.9</v>
+        <v>157</v>
       </c>
       <c r="H57" t="n">
-        <v>48.8</v>
+        <v>37.9</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>140.03</v>
+        <v>18.55</v>
       </c>
       <c r="K57" t="n">
-        <v>19.95</v>
+        <v>-57.6</v>
       </c>
       <c r="L57" t="n">
-        <v>141.45</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:40:49</t>
+          <t>06:40:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="F58" t="n">
-        <v>6.67</v>
+        <v>5.91</v>
       </c>
       <c r="G58" t="n">
-        <v>157.2</v>
+        <v>156.8</v>
       </c>
       <c r="H58" t="n">
-        <v>67.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>106.03</v>
+        <v>179.08</v>
       </c>
       <c r="K58" t="n">
-        <v>-123.64</v>
+        <v>-100.13</v>
       </c>
       <c r="L58" t="n">
-        <v>162.88</v>
+        <v>205.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:49:31</t>
+          <t>06:53:20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="F59" t="n">
         <v>6.67</v>
       </c>
       <c r="G59" t="n">
-        <v>168.6</v>
+        <v>164.2</v>
       </c>
       <c r="H59" t="n">
-        <v>53.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>16.24</v>
+        <v>27.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-27.1</v>
+        <v>-2.04</v>
       </c>
       <c r="L59" t="n">
-        <v>31.6</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:51:20</t>
+          <t>06:53:50</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="F60" t="n">
-        <v>4.85</v>
+        <v>4.09</v>
       </c>
       <c r="G60" t="n">
-        <v>167.2</v>
+        <v>158.6</v>
       </c>
       <c r="H60" t="n">
-        <v>50</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-18.14</v>
+        <v>-28.24</v>
       </c>
       <c r="K60" t="n">
-        <v>-20.38</v>
+        <v>-11.98</v>
       </c>
       <c r="L60" t="n">
-        <v>27.28</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:53:25</t>
+          <t>06:55:35</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>0.89</v>
+        <v>1.35</v>
       </c>
       <c r="F61" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="G61" t="n">
-        <v>151.2</v>
+        <v>166.6</v>
       </c>
       <c r="H61" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-30.9</v>
+        <v>19.26</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.56</v>
+        <v>-3</v>
       </c>
       <c r="L61" t="n">
-        <v>41.4</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:57:49</t>
+          <t>06:59:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="F62" t="n">
-        <v>6.3</v>
+        <v>6.67</v>
       </c>
       <c r="G62" t="n">
-        <v>162.7</v>
+        <v>165.6</v>
       </c>
       <c r="H62" t="n">
-        <v>67.09999999999999</v>
+        <v>52.1</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-35.78</v>
+        <v>-25.03</v>
       </c>
       <c r="K62" t="n">
-        <v>34.82</v>
+        <v>38.04</v>
       </c>
       <c r="L62" t="n">
-        <v>49.93</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:58:49</t>
+          <t>07:01:16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="F63" t="n">
-        <v>5.5</v>
+        <v>4.57</v>
       </c>
       <c r="G63" t="n">
-        <v>170.1</v>
+        <v>165.2</v>
       </c>
       <c r="H63" t="n">
-        <v>60.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>7.33</v>
+        <v>-32.76</v>
       </c>
       <c r="K63" t="n">
-        <v>46.09</v>
+        <v>-20.47</v>
       </c>
       <c r="L63" t="n">
-        <v>46.67</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:59:24</t>
+          <t>07:03:06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="F64" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="G64" t="n">
-        <v>172.2</v>
+        <v>152.5</v>
       </c>
       <c r="H64" t="n">
-        <v>77.2</v>
+        <v>60.8</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>6.51</v>
+        <v>-44.58</v>
       </c>
       <c r="K64" t="n">
-        <v>-44.74</v>
+        <v>17.39</v>
       </c>
       <c r="L64" t="n">
-        <v>45.21</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:04:30</t>
+          <t>07:07:56</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="F65" t="n">
         <v>6.67</v>
       </c>
       <c r="G65" t="n">
-        <v>152.2</v>
+        <v>146.2</v>
       </c>
       <c r="H65" t="n">
-        <v>53.8</v>
+        <v>87.5</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>72.91</v>
+        <v>-47.54</v>
       </c>
       <c r="K65" t="n">
-        <v>-45.57</v>
+        <v>48.17</v>
       </c>
       <c r="L65" t="n">
-        <v>85.98</v>
+        <v>67.68000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:05:46</t>
+          <t>07:10:17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="F66" t="n">
-        <v>6.67</v>
+        <v>2.3</v>
       </c>
       <c r="G66" t="n">
-        <v>167.4</v>
+        <v>172.9</v>
       </c>
       <c r="H66" t="n">
-        <v>80.2</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.34</v>
+        <v>97.13</v>
       </c>
       <c r="K66" t="n">
-        <v>-69.56</v>
+        <v>82</v>
       </c>
       <c r="L66" t="n">
-        <v>71.45999999999999</v>
+        <v>127.12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:07:55</t>
+          <t>07:12:02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="F67" t="n">
-        <v>6.48</v>
+        <v>4.89</v>
       </c>
       <c r="G67" t="n">
-        <v>164.8</v>
+        <v>160.2</v>
       </c>
       <c r="H67" t="n">
-        <v>25.7</v>
+        <v>55.8</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>74.45999999999999</v>
+        <v>14.54</v>
       </c>
       <c r="K67" t="n">
-        <v>2.59</v>
+        <v>-78.76000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>74.5</v>
+        <v>80.09</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:12:16</t>
+          <t>07:16:03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="F68" t="n">
-        <v>3.53</v>
+        <v>6.67</v>
       </c>
       <c r="G68" t="n">
-        <v>171.4</v>
+        <v>163.2</v>
       </c>
       <c r="H68" t="n">
-        <v>87</v>
+        <v>52.8</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>101.28</v>
+        <v>-59.32</v>
       </c>
       <c r="K68" t="n">
-        <v>-68.13</v>
+        <v>95.72</v>
       </c>
       <c r="L68" t="n">
-        <v>122.06</v>
+        <v>112.61</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:14:42</t>
+          <t>07:18:10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.16</v>
+        <v>1.72</v>
       </c>
       <c r="F69" t="n">
-        <v>2.3</v>
+        <v>6.67</v>
       </c>
       <c r="G69" t="n">
-        <v>178.5</v>
+        <v>160.2</v>
       </c>
       <c r="H69" t="n">
-        <v>91.8</v>
+        <v>32.7</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>107.56</v>
+        <v>-51.41</v>
       </c>
       <c r="K69" t="n">
-        <v>-41.32</v>
+        <v>-37.47</v>
       </c>
       <c r="L69" t="n">
-        <v>115.22</v>
+        <v>63.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:17:06</t>
+          <t>07:20:11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="F70" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="G70" t="n">
-        <v>151.9</v>
+        <v>164</v>
       </c>
       <c r="H70" t="n">
-        <v>62.5</v>
+        <v>68.3</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J70" t="n">
-        <v>131.65</v>
+        <v>-82.83</v>
       </c>
       <c r="K70" t="n">
-        <v>-6.94</v>
+        <v>77.08</v>
       </c>
       <c r="L70" t="n">
-        <v>131.83</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:23:17</t>
+          <t>07:24:40</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="F71" t="n">
-        <v>6.67</v>
+        <v>3.94</v>
       </c>
       <c r="G71" t="n">
-        <v>154.2</v>
+        <v>163.3</v>
       </c>
       <c r="H71" t="n">
-        <v>43.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>98.92</v>
+        <v>-139.31</v>
       </c>
       <c r="K71" t="n">
-        <v>125.38</v>
+        <v>-60.19</v>
       </c>
       <c r="L71" t="n">
-        <v>159.7</v>
+        <v>151.76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:25:07</t>
+          <t>07:26:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="F72" t="n">
-        <v>5.77</v>
+        <v>2.83</v>
       </c>
       <c r="G72" t="n">
-        <v>157.5</v>
+        <v>165.7</v>
       </c>
       <c r="H72" t="n">
-        <v>83.09999999999999</v>
+        <v>47.8</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-65.28</v>
+        <v>-109.73</v>
       </c>
       <c r="K72" t="n">
-        <v>107.48</v>
+        <v>114.73</v>
       </c>
       <c r="L72" t="n">
-        <v>125.75</v>
+        <v>158.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:27:26</t>
+          <t>07:28:17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="F73" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="G73" t="n">
-        <v>172.4</v>
+        <v>162.4</v>
       </c>
       <c r="H73" t="n">
-        <v>4.4</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>106.09</v>
+        <v>-101.41</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.64</v>
+        <v>-129.6</v>
       </c>
       <c r="L73" t="n">
-        <v>106.09</v>
+        <v>164.56</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:37:37</t>
+          <t>07:38:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="F74" t="n">
         <v>6.67</v>
       </c>
       <c r="G74" t="n">
-        <v>155.7</v>
+        <v>167.1</v>
       </c>
       <c r="H74" t="n">
-        <v>20.9</v>
+        <v>42.2</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>-28.51</v>
+        <v>-11.89</v>
       </c>
       <c r="K74" t="n">
-        <v>1.43</v>
+        <v>-20.36</v>
       </c>
       <c r="L74" t="n">
-        <v>28.55</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:39:04</t>
+          <t>07:39:42</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="F75" t="n">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="G75" t="n">
-        <v>173.7</v>
+        <v>157.2</v>
       </c>
       <c r="H75" t="n">
-        <v>76.5</v>
+        <v>45.4</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>-20.98</v>
+        <v>21.24</v>
       </c>
       <c r="K75" t="n">
-        <v>26.08</v>
+        <v>-30.87</v>
       </c>
       <c r="L75" t="n">
-        <v>33.47</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:40:52</t>
+          <t>07:41:48</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="F76" t="n">
-        <v>5.01</v>
+        <v>3.21</v>
       </c>
       <c r="G76" t="n">
-        <v>161.1</v>
+        <v>149.9</v>
       </c>
       <c r="H76" t="n">
-        <v>73.7</v>
+        <v>71.2</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>4.63</v>
+        <v>-11.78</v>
       </c>
       <c r="K76" t="n">
-        <v>26.14</v>
+        <v>-22.53</v>
       </c>
       <c r="L76" t="n">
-        <v>26.55</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:44:59</t>
+          <t>07:46:21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="F77" t="n">
-        <v>6.67</v>
+        <v>4.71</v>
       </c>
       <c r="G77" t="n">
-        <v>161.9</v>
+        <v>164.4</v>
       </c>
       <c r="H77" t="n">
-        <v>60.8</v>
+        <v>82.5</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>19.62</v>
+        <v>37.43</v>
       </c>
       <c r="K77" t="n">
-        <v>-49.41</v>
+        <v>27.21</v>
       </c>
       <c r="L77" t="n">
-        <v>53.17</v>
+        <v>46.27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:46:04</t>
+          <t>07:48:38</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="F78" t="n">
-        <v>6.67</v>
+        <v>2.7</v>
       </c>
       <c r="G78" t="n">
-        <v>163.4</v>
+        <v>164.6</v>
       </c>
       <c r="H78" t="n">
-        <v>18.7</v>
+        <v>60.4</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>48.86</v>
+        <v>-39.44</v>
       </c>
       <c r="K78" t="n">
-        <v>4.63</v>
+        <v>19.77</v>
       </c>
       <c r="L78" t="n">
-        <v>49.08</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:47:46</t>
+          <t>07:49:25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="F79" t="n">
-        <v>5.86</v>
+        <v>1.47</v>
       </c>
       <c r="G79" t="n">
-        <v>160</v>
+        <v>167.7</v>
       </c>
       <c r="H79" t="n">
-        <v>51.7</v>
+        <v>33.2</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>38.4</v>
+        <v>26.16</v>
       </c>
       <c r="K79" t="n">
-        <v>-23.69</v>
+        <v>39.6</v>
       </c>
       <c r="L79" t="n">
-        <v>45.12</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:53:29</t>
+          <t>07:54:10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="F80" t="n">
-        <v>6.67</v>
+        <v>5.57</v>
       </c>
       <c r="G80" t="n">
-        <v>166.4</v>
+        <v>159.9</v>
       </c>
       <c r="H80" t="n">
-        <v>55.2</v>
+        <v>73.8</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>60.26</v>
+        <v>-40.38</v>
       </c>
       <c r="K80" t="n">
-        <v>-32.38</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>68.41</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:55:59</t>
+          <t>07:55:44</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="F81" t="n">
-        <v>3.07</v>
+        <v>6.67</v>
       </c>
       <c r="G81" t="n">
-        <v>164.7</v>
+        <v>167.1</v>
       </c>
       <c r="H81" t="n">
-        <v>33.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>33.96</v>
+        <v>-57.68</v>
       </c>
       <c r="K81" t="n">
-        <v>44.04</v>
+        <v>-57.18</v>
       </c>
       <c r="L81" t="n">
-        <v>55.62</v>
+        <v>81.20999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:56:45</t>
+          <t>07:56:40</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="F82" t="n">
-        <v>6.67</v>
+        <v>6.39</v>
       </c>
       <c r="G82" t="n">
-        <v>159.8</v>
+        <v>159.4</v>
       </c>
       <c r="H82" t="n">
-        <v>30.5</v>
+        <v>52.8</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>63.7</v>
+        <v>70.23</v>
       </c>
       <c r="K82" t="n">
-        <v>47.34</v>
+        <v>-41.8</v>
       </c>
       <c r="L82" t="n">
-        <v>79.36</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:00:26</t>
+          <t>08:02:13</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.17</v>
+        <v>1.28</v>
       </c>
       <c r="F83" t="n">
         <v>6.67</v>
       </c>
       <c r="G83" t="n">
-        <v>159.5</v>
+        <v>154.7</v>
       </c>
       <c r="H83" t="n">
-        <v>30.6</v>
+        <v>64.7</v>
       </c>
       <c r="I83" t="n">
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-105.31</v>
+        <v>91.63</v>
       </c>
       <c r="K83" t="n">
-        <v>19.11</v>
+        <v>73.12</v>
       </c>
       <c r="L83" t="n">
-        <v>107.03</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:02:43</t>
+          <t>08:04:37</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="F84" t="n">
-        <v>5.32</v>
+        <v>6.67</v>
       </c>
       <c r="G84" t="n">
-        <v>144.4</v>
+        <v>181.9</v>
       </c>
       <c r="H84" t="n">
-        <v>55.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>63.01</v>
+        <v>18.18</v>
       </c>
       <c r="K84" t="n">
-        <v>-84.09999999999999</v>
+        <v>-120.25</v>
       </c>
       <c r="L84" t="n">
-        <v>105.09</v>
+        <v>121.62</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:05:16</t>
+          <t>08:05:35</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="F85" t="n">
-        <v>6.67</v>
+        <v>5.65</v>
       </c>
       <c r="G85" t="n">
-        <v>159.6</v>
+        <v>159.9</v>
       </c>
       <c r="H85" t="n">
-        <v>57.1</v>
+        <v>48.8</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>115.85</v>
+        <v>-65.75</v>
       </c>
       <c r="K85" t="n">
-        <v>-78.56999999999999</v>
+        <v>-69.64</v>
       </c>
       <c r="L85" t="n">
-        <v>139.98</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:10:26</t>
+          <t>08:08:58</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="F86" t="n">
-        <v>2.44</v>
+        <v>4.64</v>
       </c>
       <c r="G86" t="n">
-        <v>169</v>
+        <v>168.2</v>
       </c>
       <c r="H86" t="n">
-        <v>73.2</v>
+        <v>74.8</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-135.08</v>
+        <v>118.12</v>
       </c>
       <c r="K86" t="n">
-        <v>-104.78</v>
+        <v>73.88</v>
       </c>
       <c r="L86" t="n">
-        <v>170.96</v>
+        <v>139.32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:12:28</t>
+          <t>08:10:48</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="F87" t="n">
-        <v>4.21</v>
+        <v>6.07</v>
       </c>
       <c r="G87" t="n">
-        <v>151.6</v>
+        <v>158.4</v>
       </c>
       <c r="H87" t="n">
-        <v>63.1</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>101.91</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-138.17</v>
+        <v>145.39</v>
       </c>
       <c r="L87" t="n">
-        <v>171.69</v>
+        <v>169.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:14:03</t>
+          <t>08:13:35</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="F88" t="n">
-        <v>4.55</v>
+        <v>4.34</v>
       </c>
       <c r="G88" t="n">
-        <v>167.9</v>
+        <v>159.6</v>
       </c>
       <c r="H88" t="n">
-        <v>48.6</v>
+        <v>57.6</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>-91.05</v>
+        <v>-11.87</v>
       </c>
       <c r="K88" t="n">
-        <v>145.88</v>
+        <v>117.76</v>
       </c>
       <c r="L88" t="n">
-        <v>171.96</v>
+        <v>118.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-28.xlsx
+++ b/output/2025-06-28.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-52.57</v>
+        <v>-53.4</v>
       </c>
       <c r="K14" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="L14" t="n">
-        <v>52.6</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.98</v>
+        <v>-44.63</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.24</v>
+        <v>-14.78</v>
       </c>
       <c r="L15" t="n">
-        <v>45.27</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>19.27</v>
+        <v>21.42</v>
       </c>
       <c r="K16" t="n">
-        <v>25</v>
+        <v>27.8</v>
       </c>
       <c r="L16" t="n">
-        <v>31.56</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>28.47</v>
+        <v>33.31</v>
       </c>
       <c r="K17" t="n">
-        <v>-22.29</v>
+        <v>-26.08</v>
       </c>
       <c r="L17" t="n">
-        <v>36.15</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>9.390000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="K18" t="n">
-        <v>50.95</v>
+        <v>55.1</v>
       </c>
       <c r="L18" t="n">
-        <v>51.81</v>
+        <v>56.03</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-35.18</v>
+        <v>-37.67</v>
       </c>
       <c r="K19" t="n">
-        <v>-35.39</v>
+        <v>-37.89</v>
       </c>
       <c r="L19" t="n">
-        <v>49.9</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>27.7</v>
+        <v>29.25</v>
       </c>
       <c r="K20" t="n">
-        <v>-103.08</v>
+        <v>-108.83</v>
       </c>
       <c r="L20" t="n">
-        <v>106.73</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-75.75</v>
+        <v>-81.56999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-62.4</v>
+        <v>-67.2</v>
       </c>
       <c r="L21" t="n">
-        <v>98.15000000000001</v>
+        <v>105.69</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-58.26</v>
+        <v>-62.67</v>
       </c>
       <c r="K22" t="n">
-        <v>75.95</v>
+        <v>81.7</v>
       </c>
       <c r="L22" t="n">
-        <v>95.72</v>
+        <v>102.96</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>94.12</v>
+        <v>112.19</v>
       </c>
       <c r="K23" t="n">
-        <v>-40.38</v>
+        <v>-48.13</v>
       </c>
       <c r="L23" t="n">
-        <v>102.42</v>
+        <v>122.08</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>10.11</v>
+        <v>11.68</v>
       </c>
       <c r="K24" t="n">
-        <v>-118.13</v>
+        <v>-136.44</v>
       </c>
       <c r="L24" t="n">
-        <v>118.57</v>
+        <v>136.94</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>88.81999999999999</v>
+        <v>108.55</v>
       </c>
       <c r="K25" t="n">
-        <v>24.44</v>
+        <v>29.87</v>
       </c>
       <c r="L25" t="n">
-        <v>92.12</v>
+        <v>112.59</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>77.05</v>
+        <v>94.05</v>
       </c>
       <c r="K26" t="n">
-        <v>205.24</v>
+        <v>250.53</v>
       </c>
       <c r="L26" t="n">
-        <v>219.23</v>
+        <v>267.6</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-116.82</v>
+        <v>-156.13</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.78</v>
+        <v>-10.4</v>
       </c>
       <c r="L27" t="n">
-        <v>117.08</v>
+        <v>156.47</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>117.79</v>
+        <v>137.39</v>
       </c>
       <c r="K28" t="n">
-        <v>139.29</v>
+        <v>162.47</v>
       </c>
       <c r="L28" t="n">
-        <v>182.41</v>
+        <v>212.78</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>45.95</v>
+        <v>46.41</v>
       </c>
       <c r="K29" t="n">
-        <v>-17.86</v>
+        <v>-18.03</v>
       </c>
       <c r="L29" t="n">
-        <v>49.3</v>
+        <v>49.79</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.82</v>
+        <v>-15.7</v>
       </c>
       <c r="K30" t="n">
-        <v>40.32</v>
+        <v>42.73</v>
       </c>
       <c r="L30" t="n">
-        <v>42.96</v>
+        <v>45.52</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>30.26</v>
+        <v>30.2</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.77</v>
+        <v>-40.69</v>
       </c>
       <c r="L31" t="n">
-        <v>50.78</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.6</v>
+        <v>-8.42</v>
       </c>
       <c r="K32" t="n">
-        <v>-40.19</v>
+        <v>-44.49</v>
       </c>
       <c r="L32" t="n">
-        <v>40.91</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>28.3</v>
+        <v>33.01</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.13</v>
+        <v>-32.81</v>
       </c>
       <c r="L33" t="n">
-        <v>39.9</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-35.5</v>
+        <v>-42.01</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.52</v>
+        <v>-6.53</v>
       </c>
       <c r="L34" t="n">
-        <v>35.92</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>23.64</v>
+        <v>29.59</v>
       </c>
       <c r="K35" t="n">
-        <v>-31.21</v>
+        <v>-39.07</v>
       </c>
       <c r="L35" t="n">
-        <v>39.15</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>30.46</v>
+        <v>35.93</v>
       </c>
       <c r="K36" t="n">
-        <v>57.79</v>
+        <v>68.17</v>
       </c>
       <c r="L36" t="n">
-        <v>65.33</v>
+        <v>77.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>74.84999999999999</v>
+        <v>85.88</v>
       </c>
       <c r="K37" t="n">
-        <v>-35.4</v>
+        <v>-40.62</v>
       </c>
       <c r="L37" t="n">
-        <v>82.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-109.82</v>
+        <v>-129.72</v>
       </c>
       <c r="K38" t="n">
-        <v>-38.19</v>
+        <v>-45.11</v>
       </c>
       <c r="L38" t="n">
-        <v>116.27</v>
+        <v>137.34</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>5.65</v>
+        <v>6.91</v>
       </c>
       <c r="K39" t="n">
-        <v>-102.77</v>
+        <v>-125.66</v>
       </c>
       <c r="L39" t="n">
-        <v>102.92</v>
+        <v>125.85</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.6</v>
+        <v>-6.93</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.34</v>
+        <v>-2.9</v>
       </c>
       <c r="L40" t="n">
-        <v>6.07</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>99.2</v>
+        <v>117.97</v>
       </c>
       <c r="K41" t="n">
-        <v>150.91</v>
+        <v>179.47</v>
       </c>
       <c r="L41" t="n">
-        <v>180.59</v>
+        <v>214.77</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-77.06999999999999</v>
+        <v>-100.38</v>
       </c>
       <c r="K42" t="n">
-        <v>84.81</v>
+        <v>110.47</v>
       </c>
       <c r="L42" t="n">
-        <v>114.6</v>
+        <v>149.26</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-168.62</v>
+        <v>-212.72</v>
       </c>
       <c r="K43" t="n">
-        <v>39.18</v>
+        <v>49.43</v>
       </c>
       <c r="L43" t="n">
-        <v>173.11</v>
+        <v>218.39</v>
       </c>
     </row>
     <row r="44">
@@ -1906,7 +1906,7 @@
         <v>46.65</v>
       </c>
       <c r="L44" t="n">
-        <v>59.81</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>13.22</v>
+        <v>14.6</v>
       </c>
       <c r="K45" t="n">
-        <v>-25.68</v>
+        <v>-28.37</v>
       </c>
       <c r="L45" t="n">
-        <v>28.89</v>
+        <v>31.91</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>28.11</v>
+        <v>30.37</v>
       </c>
       <c r="K46" t="n">
-        <v>24.25</v>
+        <v>26.2</v>
       </c>
       <c r="L46" t="n">
-        <v>37.12</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-5.15</v>
+        <v>-5.53</v>
       </c>
       <c r="K47" t="n">
-        <v>47.58</v>
+        <v>51.12</v>
       </c>
       <c r="L47" t="n">
-        <v>47.86</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>46.13</v>
+        <v>49.54</v>
       </c>
       <c r="K48" t="n">
-        <v>35.01</v>
+        <v>37.6</v>
       </c>
       <c r="L48" t="n">
-        <v>57.91</v>
+        <v>62.19</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-48.8</v>
+        <v>-52.79</v>
       </c>
       <c r="K49" t="n">
-        <v>8.73</v>
+        <v>9.44</v>
       </c>
       <c r="L49" t="n">
-        <v>49.57</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-33.29</v>
+        <v>-34.85</v>
       </c>
       <c r="K50" t="n">
-        <v>-125.19</v>
+        <v>-131.02</v>
       </c>
       <c r="L50" t="n">
-        <v>129.54</v>
+        <v>135.58</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>52.59</v>
+        <v>65.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-31.15</v>
+        <v>-38.53</v>
       </c>
       <c r="L51" t="n">
-        <v>61.13</v>
+        <v>75.61</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>26.26</v>
+        <v>29.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-81.01000000000001</v>
+        <v>-91.93000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>85.16</v>
+        <v>96.64</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>101.47</v>
+        <v>119.3</v>
       </c>
       <c r="K53" t="n">
-        <v>-28.67</v>
+        <v>-33.7</v>
       </c>
       <c r="L53" t="n">
-        <v>105.44</v>
+        <v>123.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-72.15000000000001</v>
+        <v>-81.54000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>129.22</v>
+        <v>146.03</v>
       </c>
       <c r="L54" t="n">
-        <v>147.99</v>
+        <v>167.26</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>2.59</v>
+        <v>3.11</v>
       </c>
       <c r="K55" t="n">
-        <v>106.38</v>
+        <v>127.45</v>
       </c>
       <c r="L55" t="n">
-        <v>106.41</v>
+        <v>127.49</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>133.46</v>
+        <v>159.01</v>
       </c>
       <c r="K56" t="n">
-        <v>-135.71</v>
+        <v>-161.69</v>
       </c>
       <c r="L56" t="n">
-        <v>190.34</v>
+        <v>226.78</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-110.39</v>
+        <v>-139.73</v>
       </c>
       <c r="K57" t="n">
-        <v>79.05</v>
+        <v>100.05</v>
       </c>
       <c r="L57" t="n">
-        <v>135.77</v>
+        <v>171.86</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>181.34</v>
+        <v>209.37</v>
       </c>
       <c r="K58" t="n">
-        <v>-79.37</v>
+        <v>-91.64</v>
       </c>
       <c r="L58" t="n">
-        <v>197.95</v>
+        <v>228.55</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>33.03</v>
+        <v>32.34</v>
       </c>
       <c r="K59" t="n">
-        <v>47.16</v>
+        <v>46.19</v>
       </c>
       <c r="L59" t="n">
-        <v>57.57</v>
+        <v>56.39</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-33.65</v>
+        <v>-35.13</v>
       </c>
       <c r="K60" t="n">
-        <v>24.81</v>
+        <v>25.9</v>
       </c>
       <c r="L60" t="n">
-        <v>41.81</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.73</v>
+        <v>-25.13</v>
       </c>
       <c r="K61" t="n">
-        <v>25.72</v>
+        <v>29.74</v>
       </c>
       <c r="L61" t="n">
-        <v>33.67</v>
+        <v>38.93</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="K62" t="n">
-        <v>-51.46</v>
+        <v>-56.43</v>
       </c>
       <c r="L62" t="n">
-        <v>51.53</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>58.54</v>
+        <v>61.95</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.609999999999999</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>59.17</v>
+        <v>62.62</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-52.63</v>
+        <v>-54.2</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.52</v>
+        <v>-14.96</v>
       </c>
       <c r="L64" t="n">
-        <v>54.59</v>
+        <v>56.23</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>56.92</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.34</v>
+        <v>-4.21</v>
       </c>
       <c r="L65" t="n">
-        <v>57.02</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>93.41</v>
+        <v>100.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-53.8</v>
+        <v>-57.65</v>
       </c>
       <c r="L66" t="n">
-        <v>107.8</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>21.34</v>
+        <v>26.39</v>
       </c>
       <c r="K67" t="n">
-        <v>60.18</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>63.85</v>
+        <v>78.97</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-33.95</v>
+        <v>-42.47</v>
       </c>
       <c r="K68" t="n">
-        <v>87.91</v>
+        <v>110</v>
       </c>
       <c r="L68" t="n">
-        <v>94.23999999999999</v>
+        <v>117.91</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>12.97</v>
+        <v>16.62</v>
       </c>
       <c r="K69" t="n">
-        <v>-79.22</v>
+        <v>-101.49</v>
       </c>
       <c r="L69" t="n">
-        <v>80.28</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-105.1</v>
+        <v>-115.37</v>
       </c>
       <c r="K70" t="n">
-        <v>-113.99</v>
+        <v>-125.12</v>
       </c>
       <c r="L70" t="n">
-        <v>155.05</v>
+        <v>170.19</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>72.17</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-111.14</v>
+        <v>-148.67</v>
       </c>
       <c r="L71" t="n">
-        <v>132.52</v>
+        <v>177.27</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>122.3</v>
+        <v>142.01</v>
       </c>
       <c r="K72" t="n">
-        <v>-152.87</v>
+        <v>-177.5</v>
       </c>
       <c r="L72" t="n">
-        <v>195.77</v>
+        <v>227.31</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>26.44</v>
+        <v>33.93</v>
       </c>
       <c r="K73" t="n">
-        <v>109.21</v>
+        <v>140.13</v>
       </c>
       <c r="L73" t="n">
-        <v>112.37</v>
+        <v>144.18</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>19.19</v>
+        <v>19.86</v>
       </c>
       <c r="K74" t="n">
-        <v>41.57</v>
+        <v>43.01</v>
       </c>
       <c r="L74" t="n">
-        <v>45.79</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>19.65</v>
+        <v>21.42</v>
       </c>
       <c r="K75" t="n">
-        <v>-35.43</v>
+        <v>-38.62</v>
       </c>
       <c r="L75" t="n">
-        <v>40.51</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>36.15</v>
+        <v>37.78</v>
       </c>
       <c r="K76" t="n">
-        <v>29.35</v>
+        <v>30.67</v>
       </c>
       <c r="L76" t="n">
-        <v>46.57</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-23.85</v>
+        <v>-24.19</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.66</v>
+        <v>-57.46</v>
       </c>
       <c r="L77" t="n">
-        <v>61.48</v>
+        <v>62.34</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>3.62</v>
+        <v>3.98</v>
       </c>
       <c r="K78" t="n">
-        <v>53.46</v>
+        <v>58.76</v>
       </c>
       <c r="L78" t="n">
-        <v>53.58</v>
+        <v>58.89</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>42.44</v>
+        <v>45.12</v>
       </c>
       <c r="K79" t="n">
-        <v>42.96</v>
+        <v>45.67</v>
       </c>
       <c r="L79" t="n">
-        <v>60.39</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>64.11</v>
+        <v>76.73</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.37</v>
+        <v>-1.64</v>
       </c>
       <c r="L80" t="n">
-        <v>64.12</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.63</v>
+        <v>-22.23</v>
       </c>
       <c r="K81" t="n">
-        <v>-60.35</v>
+        <v>-72.04000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>63.16</v>
+        <v>75.39</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>60.47</v>
+        <v>70.37</v>
       </c>
       <c r="K82" t="n">
-        <v>-42.67</v>
+        <v>-49.66</v>
       </c>
       <c r="L82" t="n">
-        <v>74.01000000000001</v>
+        <v>86.13</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>31.1</v>
+        <v>38.5</v>
       </c>
       <c r="K83" t="n">
-        <v>-89.53</v>
+        <v>-110.83</v>
       </c>
       <c r="L83" t="n">
-        <v>94.78</v>
+        <v>117.32</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>59.25</v>
+        <v>74.63</v>
       </c>
       <c r="K84" t="n">
-        <v>-62.22</v>
+        <v>-78.37</v>
       </c>
       <c r="L84" t="n">
-        <v>85.92</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-71.09</v>
+        <v>-83.11</v>
       </c>
       <c r="K85" t="n">
-        <v>-89.69</v>
+        <v>-104.86</v>
       </c>
       <c r="L85" t="n">
-        <v>114.45</v>
+        <v>133.81</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-117.17</v>
+        <v>-158.6</v>
       </c>
       <c r="K86" t="n">
-        <v>-12.39</v>
+        <v>-16.77</v>
       </c>
       <c r="L86" t="n">
-        <v>117.83</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-37.03</v>
+        <v>-47.55</v>
       </c>
       <c r="K87" t="n">
-        <v>-140.32</v>
+        <v>-180.15</v>
       </c>
       <c r="L87" t="n">
-        <v>145.13</v>
+        <v>186.32</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-81.40000000000001</v>
+        <v>-101.16</v>
       </c>
       <c r="K88" t="n">
-        <v>154.31</v>
+        <v>191.76</v>
       </c>
       <c r="L88" t="n">
-        <v>174.47</v>
+        <v>216.8</v>
       </c>
     </row>
   </sheetData>
